--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <v>Generated: 26/10/2026, 10:17:55 pm IST</v>
+        <v>Generated: 26/10/2026, 10:19:26 pm IST</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         <v>Commit</v>
       </c>
       <c r="B8" s="8" t="str">
-        <v>cdb6a7f0fe1bf656314e7a24a24500e0d876d031</v>
+        <v>a43b1df99d3267c68f009a15759c0e21930f23b0</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +585,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40362324115</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40362633560</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B14" s="8">
-        <v>51.07</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="16">
@@ -994,7 +994,7 @@
         <v>PASS</v>
       </c>
       <c r="I2" s="8">
-        <v>0.068</v>
+        <v>0.03</v>
       </c>
       <c r="J2" s="8">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>PASS</v>
       </c>
       <c r="I3" s="8">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="J3" s="8">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>PASS</v>
       </c>
       <c r="I4" s="8">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J4" s="8">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>PASS</v>
       </c>
       <c r="I5" s="8">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>PASS</v>
       </c>
       <c r="I6" s="8">
-        <v>0.03</v>
+        <v>0.014</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1199,7 +1199,7 @@
         <v>PASS</v>
       </c>
       <c r="I7" s="8">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
@@ -1240,7 +1240,7 @@
         <v>PASS</v>
       </c>
       <c r="I8" s="8">
-        <v>0.009</v>
+        <v>0.052</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1281,7 +1281,7 @@
         <v>PASS</v>
       </c>
       <c r="I9" s="8">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>PASS</v>
       </c>
       <c r="I10" s="8">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1363,7 +1363,7 @@
         <v>PASS</v>
       </c>
       <c r="I11" s="8">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -1404,7 +1404,7 @@
         <v>PASS</v>
       </c>
       <c r="I12" s="8">
-        <v>0.043</v>
+        <v>0.009</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>PASS</v>
       </c>
       <c r="I13" s="8">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>PASS</v>
       </c>
       <c r="I14" s="8">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>PASS</v>
       </c>
       <c r="I15" s="8">
-        <v>0.033</v>
+        <v>0.014</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
@@ -1568,7 +1568,7 @@
         <v>PASS</v>
       </c>
       <c r="I16" s="8">
-        <v>0.027</v>
+        <v>0.007</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1609,7 +1609,7 @@
         <v>PASS</v>
       </c>
       <c r="I17" s="8">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>PASS</v>
       </c>
       <c r="I18" s="8">
-        <v>0.031</v>
+        <v>0.004</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>PASS</v>
       </c>
       <c r="I19" s="8">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         <v>PASS</v>
       </c>
       <c r="I21" s="8">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>PASS</v>
       </c>
       <c r="I22" s="8">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         <v>PASS</v>
       </c>
       <c r="I23" s="8">
-        <v>0.026</v>
+        <v>0.005</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
@@ -1896,7 +1896,7 @@
         <v>PASS</v>
       </c>
       <c r="I24" s="8">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -1937,7 +1937,7 @@
         <v>PASS</v>
       </c>
       <c r="I25" s="8">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>PASS</v>
       </c>
       <c r="I26" s="8">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2019,7 +2019,7 @@
         <v>PASS</v>
       </c>
       <c r="I27" s="8">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -2101,7 +2101,7 @@
         <v>PASS</v>
       </c>
       <c r="I29" s="8">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="J29" s="8">
         <v>1</v>
@@ -2142,7 +2142,7 @@
         <v>PASS</v>
       </c>
       <c r="I30" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J30" s="8">
         <v>1</v>
@@ -2183,7 +2183,7 @@
         <v>PASS</v>
       </c>
       <c r="I31" s="8">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>PASS</v>
       </c>
       <c r="I32" s="8">
-        <v>0.103</v>
+        <v>0.003</v>
       </c>
       <c r="J32" s="8">
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>PASS</v>
       </c>
       <c r="I33" s="8">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="J33" s="8">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>PASS</v>
       </c>
       <c r="I34" s="8">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2347,7 +2347,7 @@
         <v>PASS</v>
       </c>
       <c r="I35" s="8">
-        <v>0.051</v>
+        <v>0.009</v>
       </c>
       <c r="J35" s="8">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>PASS</v>
       </c>
       <c r="I36" s="8">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2429,7 +2429,7 @@
         <v>PASS</v>
       </c>
       <c r="I37" s="8">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="J37" s="8">
         <v>1</v>
@@ -2470,7 +2470,7 @@
         <v>PASS</v>
       </c>
       <c r="I38" s="8">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="J38" s="8">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>PASS</v>
       </c>
       <c r="I39" s="8">
-        <v>0.045</v>
+        <v>0.004</v>
       </c>
       <c r="J39" s="8">
         <v>1</v>
@@ -2552,7 +2552,7 @@
         <v>PASS</v>
       </c>
       <c r="I40" s="8">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2593,7 +2593,7 @@
         <v>PASS</v>
       </c>
       <c r="I41" s="8">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="J41" s="8">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>PASS</v>
       </c>
       <c r="I42" s="8">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="J42" s="8">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>PASS</v>
       </c>
       <c r="I44" s="8">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="J44" s="8">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>PASS</v>
       </c>
       <c r="I45" s="8">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="J45" s="8">
         <v>1</v>
@@ -2798,7 +2798,7 @@
         <v>PASS</v>
       </c>
       <c r="I46" s="8">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="J46" s="8">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>PASS</v>
       </c>
       <c r="I47" s="8">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="J47" s="8">
         <v>1</v>
@@ -2880,7 +2880,7 @@
         <v>PASS</v>
       </c>
       <c r="I48" s="8">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="J48" s="8">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>PASS</v>
       </c>
       <c r="I49" s="8">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>PASS</v>
       </c>
       <c r="I50" s="8">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="J50" s="8">
         <v>1</v>
@@ -3003,7 +3003,7 @@
         <v>PASS</v>
       </c>
       <c r="I51" s="8">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="J51" s="8">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>PASS</v>
       </c>
       <c r="I52" s="8">
-        <v>0.059</v>
+        <v>0.021</v>
       </c>
       <c r="J52" s="8">
         <v>1</v>
@@ -3085,7 +3085,7 @@
         <v>PASS</v>
       </c>
       <c r="I53" s="8">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>PASS</v>
       </c>
       <c r="I54" s="8">
-        <v>0.039</v>
+        <v>0.007</v>
       </c>
       <c r="J54" s="8">
         <v>1</v>
@@ -3167,7 +3167,7 @@
         <v>PASS</v>
       </c>
       <c r="I55" s="8">
-        <v>0.027</v>
+        <v>0.017</v>
       </c>
       <c r="J55" s="8">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>PASS</v>
       </c>
       <c r="I56" s="8">
-        <v>0.021</v>
+        <v>0.006</v>
       </c>
       <c r="J56" s="8">
         <v>1</v>
@@ -3249,7 +3249,7 @@
         <v>PASS</v>
       </c>
       <c r="I57" s="8">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J57" s="8">
         <v>1</v>
@@ -3290,7 +3290,7 @@
         <v>PASS</v>
       </c>
       <c r="I58" s="8">
-        <v>0.009</v>
+        <v>0.017</v>
       </c>
       <c r="J58" s="8">
         <v>1</v>
@@ -3331,7 +3331,7 @@
         <v>PASS</v>
       </c>
       <c r="I59" s="8">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="J59" s="8">
         <v>1</v>
@@ -3372,7 +3372,7 @@
         <v>PASS</v>
       </c>
       <c r="I60" s="8">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="J60" s="8">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>PASS</v>
       </c>
       <c r="I61" s="8">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="J61" s="8">
         <v>1</v>
@@ -3454,7 +3454,7 @@
         <v>PASS</v>
       </c>
       <c r="I62" s="8">
-        <v>0.062</v>
+        <v>0.003</v>
       </c>
       <c r="J62" s="8">
         <v>1</v>
@@ -3495,7 +3495,7 @@
         <v>PASS</v>
       </c>
       <c r="I63" s="8">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="J63" s="8">
         <v>1</v>
@@ -3536,7 +3536,7 @@
         <v>PASS</v>
       </c>
       <c r="I64" s="8">
-        <v>0.031</v>
+        <v>0.002</v>
       </c>
       <c r="J64" s="8">
         <v>1</v>
@@ -3577,7 +3577,7 @@
         <v>PASS</v>
       </c>
       <c r="I65" s="8">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="J65" s="8">
         <v>1</v>
@@ -3618,7 +3618,7 @@
         <v>PASS</v>
       </c>
       <c r="I66" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J66" s="8">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>PASS</v>
       </c>
       <c r="I67" s="8">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J67" s="8">
         <v>1</v>
@@ -3700,7 +3700,7 @@
         <v>PASS</v>
       </c>
       <c r="I68" s="8">
-        <v>0.029</v>
+        <v>0.006</v>
       </c>
       <c r="J68" s="8">
         <v>1</v>
@@ -3741,7 +3741,7 @@
         <v>PASS</v>
       </c>
       <c r="I69" s="8">
-        <v>0.035</v>
+        <v>0.003</v>
       </c>
       <c r="J69" s="8">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>PASS</v>
       </c>
       <c r="I70" s="8">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="J70" s="8">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>PASS</v>
       </c>
       <c r="I71" s="8">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="J71" s="8">
         <v>1</v>
@@ -3864,7 +3864,7 @@
         <v>PASS</v>
       </c>
       <c r="I72" s="8">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="J72" s="8">
         <v>1</v>
@@ -3905,7 +3905,7 @@
         <v>PASS</v>
       </c>
       <c r="I73" s="8">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="J73" s="8">
         <v>1</v>
@@ -3946,7 +3946,7 @@
         <v>PASS</v>
       </c>
       <c r="I74" s="8">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="J74" s="8">
         <v>1</v>
@@ -3987,7 +3987,7 @@
         <v>PASS</v>
       </c>
       <c r="I75" s="8">
-        <v>0.014</v>
+        <v>0.067</v>
       </c>
       <c r="J75" s="8">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>PASS</v>
       </c>
       <c r="I76" s="8">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="J76" s="8">
         <v>1</v>
@@ -4069,7 +4069,7 @@
         <v>PASS</v>
       </c>
       <c r="I77" s="8">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="J77" s="8">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>PASS</v>
       </c>
       <c r="I78" s="8">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="J78" s="8">
         <v>1</v>
@@ -4151,7 +4151,7 @@
         <v>PASS</v>
       </c>
       <c r="I79" s="8">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="J79" s="8">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         <v>PASS</v>
       </c>
       <c r="I80" s="8">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="J80" s="8">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>PASS</v>
       </c>
       <c r="I81" s="8">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="J81" s="8">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>PASS</v>
       </c>
       <c r="I82" s="8">
-        <v>0.083</v>
+        <v>0.05</v>
       </c>
       <c r="J82" s="8">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>PASS</v>
       </c>
       <c r="I83" s="8">
-        <v>0.027</v>
+        <v>0.033</v>
       </c>
       <c r="J83" s="8">
         <v>1</v>
@@ -4356,7 +4356,7 @@
         <v>PASS</v>
       </c>
       <c r="I84" s="8">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="J84" s="8">
         <v>1</v>
@@ -4397,7 +4397,7 @@
         <v>PASS</v>
       </c>
       <c r="I85" s="8">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="J85" s="8">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>PASS</v>
       </c>
       <c r="I86" s="8">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="J86" s="8">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>PASS</v>
       </c>
       <c r="I87" s="8">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="J87" s="8">
         <v>1</v>
@@ -4520,7 +4520,7 @@
         <v>PASS</v>
       </c>
       <c r="I88" s="8">
-        <v>0.04</v>
+        <v>0.002</v>
       </c>
       <c r="J88" s="8">
         <v>1</v>
@@ -4561,7 +4561,7 @@
         <v>PASS</v>
       </c>
       <c r="I89" s="8">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J89" s="8">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>PASS</v>
       </c>
       <c r="I90" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J90" s="8">
         <v>1</v>
@@ -4643,7 +4643,7 @@
         <v>PASS</v>
       </c>
       <c r="I91" s="8">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="J91" s="8">
         <v>1</v>
@@ -4684,7 +4684,7 @@
         <v>PASS</v>
       </c>
       <c r="I92" s="8">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="J92" s="8">
         <v>1</v>
@@ -4725,7 +4725,7 @@
         <v>PASS</v>
       </c>
       <c r="I93" s="8">
-        <v>0.101</v>
+        <v>0.038</v>
       </c>
       <c r="J93" s="8">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>PASS</v>
       </c>
       <c r="I94" s="8">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="J94" s="8">
         <v>1</v>
@@ -4807,7 +4807,7 @@
         <v>PASS</v>
       </c>
       <c r="I95" s="8">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="J95" s="8">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         <v>PASS</v>
       </c>
       <c r="I96" s="8">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J96" s="8">
         <v>1</v>
@@ -4889,7 +4889,7 @@
         <v>PASS</v>
       </c>
       <c r="I97" s="8">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="J97" s="8">
         <v>1</v>
@@ -4930,7 +4930,7 @@
         <v>PASS</v>
       </c>
       <c r="I98" s="8">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="J98" s="8">
         <v>1</v>
@@ -4971,7 +4971,7 @@
         <v>PASS</v>
       </c>
       <c r="I99" s="8">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="J99" s="8">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>PASS</v>
       </c>
       <c r="I100" s="8">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="J100" s="8">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>PASS</v>
       </c>
       <c r="I101" s="8">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="J101" s="8">
         <v>1</v>
@@ -5094,7 +5094,7 @@
         <v>PASS</v>
       </c>
       <c r="I102" s="8">
-        <v>0.035</v>
+        <v>0.001</v>
       </c>
       <c r="J102" s="8">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         <v>PASS</v>
       </c>
       <c r="I103" s="8">
-        <v>0.054</v>
+        <v>0.009</v>
       </c>
       <c r="J103" s="8">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>PASS</v>
       </c>
       <c r="I104" s="8">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="J104" s="8">
         <v>1</v>
@@ -5217,7 +5217,7 @@
         <v>PASS</v>
       </c>
       <c r="I105" s="8">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="J105" s="8">
         <v>1</v>
@@ -5258,7 +5258,7 @@
         <v>PASS</v>
       </c>
       <c r="I106" s="8">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="J106" s="8">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         <v>PASS</v>
       </c>
       <c r="I107" s="8">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="J107" s="8">
         <v>1</v>
@@ -5340,7 +5340,7 @@
         <v>PASS</v>
       </c>
       <c r="I108" s="8">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="J108" s="8">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>PASS</v>
       </c>
       <c r="I109" s="8">
-        <v>0.031</v>
+        <v>0.002</v>
       </c>
       <c r="J109" s="8">
         <v>1</v>
@@ -5422,7 +5422,7 @@
         <v>PASS</v>
       </c>
       <c r="I110" s="8">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="J110" s="8">
         <v>1</v>
@@ -5463,7 +5463,7 @@
         <v>PASS</v>
       </c>
       <c r="I111" s="8">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="J111" s="8">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>PASS</v>
       </c>
       <c r="I112" s="8">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="J112" s="8">
         <v>1</v>
@@ -5545,7 +5545,7 @@
         <v>PASS</v>
       </c>
       <c r="I113" s="8">
-        <v>0.088</v>
+        <v>0.049</v>
       </c>
       <c r="J113" s="8">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         <v>PASS</v>
       </c>
       <c r="I114" s="8">
-        <v>0.035</v>
+        <v>0.017</v>
       </c>
       <c r="J114" s="8">
         <v>1</v>
@@ -5627,7 +5627,7 @@
         <v>PASS</v>
       </c>
       <c r="I115" s="8">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="J115" s="8">
         <v>1</v>
@@ -5668,7 +5668,7 @@
         <v>PASS</v>
       </c>
       <c r="I116" s="8">
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
       <c r="J116" s="8">
         <v>1</v>
@@ -5709,7 +5709,7 @@
         <v>PASS</v>
       </c>
       <c r="I117" s="8">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="J117" s="8">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>PASS</v>
       </c>
       <c r="I118" s="8">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J118" s="8">
         <v>1</v>
@@ -5791,7 +5791,7 @@
         <v>PASS</v>
       </c>
       <c r="I119" s="8">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="J119" s="8">
         <v>1</v>
@@ -5873,7 +5873,7 @@
         <v>PASS</v>
       </c>
       <c r="I121" s="8">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="J121" s="8">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>PASS</v>
       </c>
       <c r="I122" s="8">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="J122" s="8">
         <v>1</v>
@@ -5955,7 +5955,7 @@
         <v>PASS</v>
       </c>
       <c r="I123" s="8">
-        <v>0.08</v>
+        <v>0.039</v>
       </c>
       <c r="J123" s="8">
         <v>1</v>
@@ -5996,7 +5996,7 @@
         <v>PASS</v>
       </c>
       <c r="I124" s="8">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="J124" s="8">
         <v>1</v>
@@ -6037,7 +6037,7 @@
         <v>PASS</v>
       </c>
       <c r="I125" s="8">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="J125" s="8">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         <v>PASS</v>
       </c>
       <c r="I126" s="8">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="J126" s="8">
         <v>1</v>
@@ -6119,7 +6119,7 @@
         <v>PASS</v>
       </c>
       <c r="I127" s="8">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J127" s="8">
         <v>1</v>
@@ -6160,7 +6160,7 @@
         <v>PASS</v>
       </c>
       <c r="I128" s="8">
-        <v>0.009</v>
+        <v>0.019</v>
       </c>
       <c r="J128" s="8">
         <v>1</v>
@@ -6201,7 +6201,7 @@
         <v>PASS</v>
       </c>
       <c r="I129" s="8">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="J129" s="8">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         <v>PASS</v>
       </c>
       <c r="I130" s="8">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="J130" s="8">
         <v>1</v>
@@ -6283,7 +6283,7 @@
         <v>PASS</v>
       </c>
       <c r="I131" s="8">
-        <v>0.006</v>
+        <v>0.046</v>
       </c>
       <c r="J131" s="8">
         <v>1</v>
@@ -6324,7 +6324,7 @@
         <v>PASS</v>
       </c>
       <c r="I132" s="8">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="J132" s="8">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         <v>PASS</v>
       </c>
       <c r="I133" s="8">
-        <v>0.07</v>
+        <v>0.064</v>
       </c>
       <c r="J133" s="8">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>PASS</v>
       </c>
       <c r="I134" s="8">
-        <v>0.033</v>
+        <v>0.064</v>
       </c>
       <c r="J134" s="8">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>PASS</v>
       </c>
       <c r="I135" s="8">
-        <v>0.016</v>
+        <v>0.032</v>
       </c>
       <c r="J135" s="8">
         <v>1</v>
@@ -6488,7 +6488,7 @@
         <v>PASS</v>
       </c>
       <c r="I136" s="8">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="J136" s="8">
         <v>1</v>
@@ -6529,7 +6529,7 @@
         <v>PASS</v>
       </c>
       <c r="I137" s="8">
-        <v>0.038</v>
+        <v>0.013</v>
       </c>
       <c r="J137" s="8">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>PASS</v>
       </c>
       <c r="I138" s="8">
-        <v>0.067</v>
+        <v>0.034</v>
       </c>
       <c r="J138" s="8">
         <v>1</v>
@@ -6611,7 +6611,7 @@
         <v>PASS</v>
       </c>
       <c r="I139" s="8">
-        <v>0.053</v>
+        <v>0.014</v>
       </c>
       <c r="J139" s="8">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>PASS</v>
       </c>
       <c r="I140" s="8">
-        <v>0.041</v>
+        <v>0.014</v>
       </c>
       <c r="J140" s="8">
         <v>1</v>
@@ -6693,7 +6693,7 @@
         <v>PASS</v>
       </c>
       <c r="I141" s="8">
-        <v>0.053</v>
+        <v>0.004</v>
       </c>
       <c r="J141" s="8">
         <v>1</v>
@@ -6734,7 +6734,7 @@
         <v>PASS</v>
       </c>
       <c r="I142" s="8">
-        <v>0.061</v>
+        <v>0.028</v>
       </c>
       <c r="J142" s="8">
         <v>1</v>
@@ -6775,7 +6775,7 @@
         <v>PASS</v>
       </c>
       <c r="I143" s="8">
-        <v>0.013</v>
+        <v>0.125</v>
       </c>
       <c r="J143" s="8">
         <v>1</v>
@@ -6816,7 +6816,7 @@
         <v>PASS</v>
       </c>
       <c r="I144" s="8">
-        <v>0.04</v>
+        <v>0.062</v>
       </c>
       <c r="J144" s="8">
         <v>1</v>
@@ -6857,7 +6857,7 @@
         <v>PASS</v>
       </c>
       <c r="I145" s="8">
-        <v>0.033</v>
+        <v>0.049</v>
       </c>
       <c r="J145" s="8">
         <v>1</v>
@@ -6898,7 +6898,7 @@
         <v>PASS</v>
       </c>
       <c r="I146" s="8">
-        <v>0.038</v>
+        <v>0.047</v>
       </c>
       <c r="J146" s="8">
         <v>1</v>
@@ -6939,7 +6939,7 @@
         <v>PASS</v>
       </c>
       <c r="I147" s="8">
-        <v>0.032</v>
+        <v>0.021</v>
       </c>
       <c r="J147" s="8">
         <v>1</v>
@@ -6980,7 +6980,7 @@
         <v>PASS</v>
       </c>
       <c r="I148" s="8">
-        <v>0.149</v>
+        <v>0.061</v>
       </c>
       <c r="J148" s="8">
         <v>1</v>
@@ -7021,7 +7021,7 @@
         <v>PASS</v>
       </c>
       <c r="I149" s="8">
-        <v>0.021</v>
+        <v>0.059</v>
       </c>
       <c r="J149" s="8">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>PASS</v>
       </c>
       <c r="I150" s="8">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="J150" s="8">
         <v>1</v>
@@ -7103,7 +7103,7 @@
         <v>PASS</v>
       </c>
       <c r="I151" s="8">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="J151" s="8">
         <v>1</v>
@@ -7185,7 +7185,7 @@
         <v>PASS</v>
       </c>
       <c r="I153" s="8">
-        <v>0.312</v>
+        <v>0.095</v>
       </c>
       <c r="J153" s="8">
         <v>1</v>
@@ -7226,7 +7226,7 @@
         <v>PASS</v>
       </c>
       <c r="I154" s="8">
-        <v>0.024</v>
+        <v>0.038</v>
       </c>
       <c r="J154" s="8">
         <v>1</v>
@@ -7267,7 +7267,7 @@
         <v>PASS</v>
       </c>
       <c r="I155" s="8">
-        <v>0.075</v>
+        <v>0.029</v>
       </c>
       <c r="J155" s="8">
         <v>1</v>
@@ -7308,7 +7308,7 @@
         <v>PASS</v>
       </c>
       <c r="I156" s="8">
-        <v>0.088</v>
+        <v>0.035</v>
       </c>
       <c r="J156" s="8">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>PASS</v>
       </c>
       <c r="I157" s="8">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="J157" s="8">
         <v>1</v>
@@ -7390,7 +7390,7 @@
         <v>PASS</v>
       </c>
       <c r="I158" s="8">
-        <v>0.009</v>
+        <v>0.111</v>
       </c>
       <c r="J158" s="8">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         <v>PASS</v>
       </c>
       <c r="I159" s="8">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="J159" s="8">
         <v>1</v>
@@ -7472,7 +7472,7 @@
         <v>PASS</v>
       </c>
       <c r="I160" s="8">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="J160" s="8">
         <v>1</v>
@@ -7513,7 +7513,7 @@
         <v>PASS</v>
       </c>
       <c r="I161" s="8">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="J161" s="8">
         <v>1</v>
@@ -7554,7 +7554,7 @@
         <v>PASS</v>
       </c>
       <c r="I162" s="8">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="J162" s="8">
         <v>1</v>
@@ -7595,7 +7595,7 @@
         <v>PASS</v>
       </c>
       <c r="I163" s="8">
-        <v>0.053</v>
+        <v>0.02</v>
       </c>
       <c r="J163" s="8">
         <v>1</v>
@@ -7636,7 +7636,7 @@
         <v>PASS</v>
       </c>
       <c r="I164" s="8">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="J164" s="8">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>PASS</v>
       </c>
       <c r="I165" s="8">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="J165" s="8">
         <v>1</v>
@@ -7718,7 +7718,7 @@
         <v>PASS</v>
       </c>
       <c r="I166" s="8">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="J166" s="8">
         <v>1</v>
@@ -7759,7 +7759,7 @@
         <v>PASS</v>
       </c>
       <c r="I167" s="8">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
       <c r="J167" s="8">
         <v>1</v>
@@ -7800,7 +7800,7 @@
         <v>PASS</v>
       </c>
       <c r="I168" s="8">
-        <v>0.073</v>
+        <v>0.021</v>
       </c>
       <c r="J168" s="8">
         <v>1</v>
@@ -7841,7 +7841,7 @@
         <v>PASS</v>
       </c>
       <c r="I169" s="8">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="J169" s="8">
         <v>1</v>
@@ -7882,7 +7882,7 @@
         <v>PASS</v>
       </c>
       <c r="I170" s="8">
-        <v>0.033</v>
+        <v>0.014</v>
       </c>
       <c r="J170" s="8">
         <v>1</v>
@@ -7923,7 +7923,7 @@
         <v>PASS</v>
       </c>
       <c r="I171" s="8">
-        <v>0.034</v>
+        <v>0.004</v>
       </c>
       <c r="J171" s="8">
         <v>1</v>
@@ -7964,7 +7964,7 @@
         <v>PASS</v>
       </c>
       <c r="I172" s="8">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="J172" s="8">
         <v>1</v>
@@ -8005,7 +8005,7 @@
         <v>PASS</v>
       </c>
       <c r="I173" s="8">
-        <v>0.006</v>
+        <v>0.08</v>
       </c>
       <c r="J173" s="8">
         <v>1</v>
@@ -8046,7 +8046,7 @@
         <v>PASS</v>
       </c>
       <c r="I174" s="8">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J174" s="8">
         <v>1</v>
@@ -8087,7 +8087,7 @@
         <v>PASS</v>
       </c>
       <c r="I175" s="8">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="J175" s="8">
         <v>1</v>
@@ -8128,7 +8128,7 @@
         <v>PASS</v>
       </c>
       <c r="I176" s="8">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="J176" s="8">
         <v>1</v>
@@ -8169,7 +8169,7 @@
         <v>PASS</v>
       </c>
       <c r="I177" s="8">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="J177" s="8">
         <v>1</v>
@@ -8210,7 +8210,7 @@
         <v>PASS</v>
       </c>
       <c r="I178" s="8">
-        <v>0.108</v>
+        <v>0.009</v>
       </c>
       <c r="J178" s="8">
         <v>1</v>
@@ -8251,7 +8251,7 @@
         <v>PASS</v>
       </c>
       <c r="I179" s="8">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="J179" s="8">
         <v>1</v>
@@ -8292,7 +8292,7 @@
         <v>PASS</v>
       </c>
       <c r="I180" s="8">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="J180" s="8">
         <v>1</v>
@@ -8374,7 +8374,7 @@
         <v>PASS</v>
       </c>
       <c r="I182" s="8">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="J182" s="8">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         <v>PASS</v>
       </c>
       <c r="I183" s="8">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="J183" s="8">
         <v>1</v>
@@ -8456,7 +8456,7 @@
         <v>PASS</v>
       </c>
       <c r="I184" s="8">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="J184" s="8">
         <v>1</v>
@@ -8497,7 +8497,7 @@
         <v>PASS</v>
       </c>
       <c r="I185" s="8">
-        <v>0.931</v>
+        <v>0.886</v>
       </c>
       <c r="J185" s="8">
         <v>1</v>
@@ -8538,7 +8538,7 @@
         <v>PASS</v>
       </c>
       <c r="I186" s="8">
-        <v>0.963</v>
+        <v>0.875</v>
       </c>
       <c r="J186" s="8">
         <v>1</v>
@@ -8579,7 +8579,7 @@
         <v>PASS</v>
       </c>
       <c r="I187" s="8">
-        <v>0.543</v>
+        <v>0.508</v>
       </c>
       <c r="J187" s="8">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>PASS</v>
       </c>
       <c r="I188" s="8">
-        <v>0.974</v>
+        <v>0.598</v>
       </c>
       <c r="J188" s="8">
         <v>1</v>
@@ -8661,7 +8661,7 @@
         <v>PASS</v>
       </c>
       <c r="I189" s="8">
-        <v>1.325</v>
+        <v>0.922</v>
       </c>
       <c r="J189" s="8">
         <v>1</v>
@@ -8702,7 +8702,7 @@
         <v>PASS</v>
       </c>
       <c r="I190" s="8">
-        <v>1.003</v>
+        <v>0.57</v>
       </c>
       <c r="J190" s="8">
         <v>1</v>
@@ -8743,7 +8743,7 @@
         <v>PASS</v>
       </c>
       <c r="I191" s="8">
-        <v>1.822</v>
+        <v>1.302</v>
       </c>
       <c r="J191" s="8">
         <v>1</v>
@@ -8784,7 +8784,7 @@
         <v>PASS</v>
       </c>
       <c r="I192" s="8">
-        <v>1.255</v>
+        <v>0.738</v>
       </c>
       <c r="J192" s="8">
         <v>1</v>
@@ -8825,7 +8825,7 @@
         <v>PASS</v>
       </c>
       <c r="I193" s="8">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="J193" s="8">
         <v>1</v>
@@ -8866,7 +8866,7 @@
         <v>PASS</v>
       </c>
       <c r="I194" s="8">
-        <v>0.017</v>
+        <v>0.053</v>
       </c>
       <c r="J194" s="8">
         <v>1</v>
@@ -8907,7 +8907,7 @@
         <v>PASS</v>
       </c>
       <c r="I195" s="8">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="J195" s="8">
         <v>1</v>
@@ -8948,7 +8948,7 @@
         <v>PASS</v>
       </c>
       <c r="I196" s="8">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="J196" s="8">
         <v>1</v>
@@ -8989,7 +8989,7 @@
         <v>PASS</v>
       </c>
       <c r="I197" s="8">
-        <v>1.019</v>
+        <v>0.888</v>
       </c>
       <c r="J197" s="8">
         <v>1</v>
@@ -9030,7 +9030,7 @@
         <v>PASS</v>
       </c>
       <c r="I198" s="8">
-        <v>1.452</v>
+        <v>1.157</v>
       </c>
       <c r="J198" s="8">
         <v>1</v>
@@ -9071,7 +9071,7 @@
         <v>PASS</v>
       </c>
       <c r="I199" s="8">
-        <v>1.829</v>
+        <v>1.512</v>
       </c>
       <c r="J199" s="8">
         <v>1</v>
@@ -9112,7 +9112,7 @@
         <v>PASS</v>
       </c>
       <c r="I200" s="8">
-        <v>1.481</v>
+        <v>1.317</v>
       </c>
       <c r="J200" s="8">
         <v>1</v>
@@ -9153,7 +9153,7 @@
         <v>PASS</v>
       </c>
       <c r="I201" s="8">
-        <v>1.965</v>
+        <v>1.646</v>
       </c>
       <c r="J201" s="8">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>PASS</v>
       </c>
       <c r="I202" s="8">
-        <v>1.799</v>
+        <v>1.72</v>
       </c>
       <c r="J202" s="8">
         <v>1</v>
@@ -9235,7 +9235,7 @@
         <v>PASS</v>
       </c>
       <c r="I203" s="8">
-        <v>0.913</v>
+        <v>0.715</v>
       </c>
       <c r="J203" s="8">
         <v>1</v>
@@ -9276,7 +9276,7 @@
         <v>PASS</v>
       </c>
       <c r="I204" s="8">
-        <v>0.087</v>
+        <v>0.004</v>
       </c>
       <c r="J204" s="8">
         <v>1</v>
@@ -9317,7 +9317,7 @@
         <v>PASS</v>
       </c>
       <c r="I205" s="8">
-        <v>0.049</v>
+        <v>0.01</v>
       </c>
       <c r="J205" s="8">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         <v>PASS</v>
       </c>
       <c r="I206" s="8">
-        <v>0.106</v>
+        <v>0.004</v>
       </c>
       <c r="J206" s="8">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         <v>PASS</v>
       </c>
       <c r="I207" s="8">
-        <v>0.033</v>
+        <v>0.012</v>
       </c>
       <c r="J207" s="8">
         <v>1</v>
@@ -9440,7 +9440,7 @@
         <v>PASS</v>
       </c>
       <c r="I208" s="8">
-        <v>0.053</v>
+        <v>0.006</v>
       </c>
       <c r="J208" s="8">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>PASS</v>
       </c>
       <c r="I209" s="8">
-        <v>0.042</v>
+        <v>0.011</v>
       </c>
       <c r="J209" s="8">
         <v>1</v>
@@ -9522,7 +9522,7 @@
         <v>PASS</v>
       </c>
       <c r="I210" s="8">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="J210" s="8">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>PASS</v>
       </c>
       <c r="I211" s="8">
-        <v>1.445</v>
+        <v>1.165</v>
       </c>
       <c r="J211" s="8">
         <v>1</v>
@@ -9604,7 +9604,7 @@
         <v>PASS</v>
       </c>
       <c r="I212" s="8">
-        <v>1.237</v>
+        <v>0.803</v>
       </c>
       <c r="J212" s="8">
         <v>1</v>
@@ -9645,7 +9645,7 @@
         <v>PASS</v>
       </c>
       <c r="I213" s="8">
-        <v>2.087</v>
+        <v>1.247</v>
       </c>
       <c r="J213" s="8">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         <v>PASS</v>
       </c>
       <c r="I214" s="8">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="J214" s="8">
         <v>1</v>
@@ -9727,7 +9727,7 @@
         <v>PASS</v>
       </c>
       <c r="I215" s="8">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="J215" s="8">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         <v>PASS</v>
       </c>
       <c r="I216" s="8">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="J216" s="8">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         <v>PASS</v>
       </c>
       <c r="I217" s="8">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="J217" s="8">
         <v>1</v>
@@ -9850,7 +9850,7 @@
         <v>PASS</v>
       </c>
       <c r="I218" s="8">
-        <v>0.027</v>
+        <v>0.006</v>
       </c>
       <c r="J218" s="8">
         <v>1</v>
@@ -9891,7 +9891,7 @@
         <v>PASS</v>
       </c>
       <c r="I219" s="8">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="J219" s="8">
         <v>1</v>
@@ -9932,7 +9932,7 @@
         <v>PASS</v>
       </c>
       <c r="I220" s="8">
-        <v>0.027</v>
+        <v>0.006</v>
       </c>
       <c r="J220" s="8">
         <v>1</v>
@@ -9973,7 +9973,7 @@
         <v>PASS</v>
       </c>
       <c r="I221" s="8">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="J221" s="8">
         <v>1</v>
@@ -10014,7 +10014,7 @@
         <v>PASS</v>
       </c>
       <c r="I222" s="8">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="J222" s="8">
         <v>1</v>
@@ -10055,7 +10055,7 @@
         <v>PASS</v>
       </c>
       <c r="I223" s="8">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="J223" s="8">
         <v>1</v>
@@ -10096,7 +10096,7 @@
         <v>PASS</v>
       </c>
       <c r="I224" s="8">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J224" s="8">
         <v>1</v>
@@ -10137,7 +10137,7 @@
         <v>PASS</v>
       </c>
       <c r="I225" s="8">
-        <v>0.05</v>
+        <v>0.015</v>
       </c>
       <c r="J225" s="8">
         <v>1</v>
@@ -10178,7 +10178,7 @@
         <v>PASS</v>
       </c>
       <c r="I226" s="8">
-        <v>0.045</v>
+        <v>0.003</v>
       </c>
       <c r="J226" s="8">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>PASS</v>
       </c>
       <c r="I227" s="8">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="J227" s="8">
         <v>1</v>
@@ -10260,7 +10260,7 @@
         <v>PASS</v>
       </c>
       <c r="I228" s="8">
-        <v>0.038</v>
+        <v>0.007</v>
       </c>
       <c r="J228" s="8">
         <v>1</v>
@@ -10301,7 +10301,7 @@
         <v>PASS</v>
       </c>
       <c r="I229" s="8">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="J229" s="8">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         <v>PASS</v>
       </c>
       <c r="I230" s="8">
-        <v>0.062</v>
+        <v>0.013</v>
       </c>
       <c r="J230" s="8">
         <v>1</v>
@@ -10383,7 +10383,7 @@
         <v>PASS</v>
       </c>
       <c r="I231" s="8">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="J231" s="8">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         <v>PASS</v>
       </c>
       <c r="I232" s="8">
-        <v>0.022</v>
+        <v>0.009</v>
       </c>
       <c r="J232" s="8">
         <v>1</v>
@@ -10465,7 +10465,7 @@
         <v>PASS</v>
       </c>
       <c r="I233" s="8">
-        <v>0.016</v>
+        <v>0.023</v>
       </c>
       <c r="J233" s="8">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>PASS</v>
       </c>
       <c r="I234" s="8">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="J234" s="8">
         <v>1</v>
@@ -10547,7 +10547,7 @@
         <v>PASS</v>
       </c>
       <c r="I235" s="8">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="J235" s="8">
         <v>1</v>
@@ -10588,7 +10588,7 @@
         <v>PASS</v>
       </c>
       <c r="I236" s="8">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="J236" s="8">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         <v>PASS</v>
       </c>
       <c r="I237" s="8">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="J237" s="8">
         <v>1</v>
@@ -10670,7 +10670,7 @@
         <v>PASS</v>
       </c>
       <c r="I238" s="8">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J238" s="8">
         <v>1</v>
@@ -10711,7 +10711,7 @@
         <v>PASS</v>
       </c>
       <c r="I239" s="8">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="J239" s="8">
         <v>1</v>
@@ -10752,7 +10752,7 @@
         <v>PASS</v>
       </c>
       <c r="I240" s="8">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="J240" s="8">
         <v>1</v>
@@ -10793,7 +10793,7 @@
         <v>PASS</v>
       </c>
       <c r="I241" s="8">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="J241" s="8">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         <v>PASS</v>
       </c>
       <c r="I242" s="8">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J242" s="8">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>PASS</v>
       </c>
       <c r="I243" s="8">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="J243" s="8">
         <v>1</v>
@@ -10916,7 +10916,7 @@
         <v>PASS</v>
       </c>
       <c r="I244" s="8">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="J244" s="8">
         <v>1</v>
@@ -10957,7 +10957,7 @@
         <v>PASS</v>
       </c>
       <c r="I245" s="8">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="J245" s="8">
         <v>1</v>
@@ -10998,7 +10998,7 @@
         <v>PASS</v>
       </c>
       <c r="I246" s="8">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="J246" s="8">
         <v>1</v>
@@ -11039,7 +11039,7 @@
         <v>PASS</v>
       </c>
       <c r="I247" s="8">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="J247" s="8">
         <v>1</v>
@@ -11080,7 +11080,7 @@
         <v>PASS</v>
       </c>
       <c r="I248" s="8">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="J248" s="8">
         <v>1</v>
@@ -11121,7 +11121,7 @@
         <v>PASS</v>
       </c>
       <c r="I249" s="8">
-        <v>0.048</v>
+        <v>0.012</v>
       </c>
       <c r="J249" s="8">
         <v>1</v>
@@ -11162,7 +11162,7 @@
         <v>PASS</v>
       </c>
       <c r="I250" s="8">
-        <v>0.022</v>
+        <v>0.004</v>
       </c>
       <c r="J250" s="8">
         <v>1</v>
@@ -11203,7 +11203,7 @@
         <v>PASS</v>
       </c>
       <c r="I251" s="8">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="J251" s="8">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>PASS</v>
       </c>
       <c r="I253" s="8">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="J253" s="8">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>PASS</v>
       </c>
       <c r="I254" s="8">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
       <c r="J254" s="8">
         <v>1</v>
@@ -11367,7 +11367,7 @@
         <v>PASS</v>
       </c>
       <c r="I255" s="8">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="J255" s="8">
         <v>1</v>
@@ -11408,7 +11408,7 @@
         <v>PASS</v>
       </c>
       <c r="I256" s="8">
-        <v>0.166</v>
+        <v>0.007</v>
       </c>
       <c r="J256" s="8">
         <v>1</v>
@@ -11449,7 +11449,7 @@
         <v>PASS</v>
       </c>
       <c r="I257" s="8">
-        <v>0.037</v>
+        <v>0.007</v>
       </c>
       <c r="J257" s="8">
         <v>1</v>
@@ -11490,7 +11490,7 @@
         <v>PASS</v>
       </c>
       <c r="I258" s="8">
-        <v>0.021</v>
+        <v>0.041</v>
       </c>
       <c r="J258" s="8">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>PASS</v>
       </c>
       <c r="I259" s="8">
-        <v>0.025</v>
+        <v>0.013</v>
       </c>
       <c r="J259" s="8">
         <v>1</v>
@@ -11572,7 +11572,7 @@
         <v>PASS</v>
       </c>
       <c r="I260" s="8">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J260" s="8">
         <v>1</v>
@@ -11613,7 +11613,7 @@
         <v>PASS</v>
       </c>
       <c r="I261" s="8">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="J261" s="8">
         <v>1</v>
@@ -11654,7 +11654,7 @@
         <v>PASS</v>
       </c>
       <c r="I262" s="8">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="J262" s="8">
         <v>1</v>
@@ -11695,7 +11695,7 @@
         <v>PASS</v>
       </c>
       <c r="I263" s="8">
-        <v>0.021</v>
+        <v>0.036</v>
       </c>
       <c r="J263" s="8">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>PASS</v>
       </c>
       <c r="I265" s="8">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="J265" s="8">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>PASS</v>
       </c>
       <c r="I266" s="8">
-        <v>0.166</v>
+        <v>0.139</v>
       </c>
       <c r="J266" s="8">
         <v>1</v>
@@ -11859,7 +11859,7 @@
         <v>PASS</v>
       </c>
       <c r="I267" s="8">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="J267" s="8">
         <v>1</v>
@@ -11900,7 +11900,7 @@
         <v>PASS</v>
       </c>
       <c r="I268" s="8">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="J268" s="8">
         <v>1</v>
@@ -11941,7 +11941,7 @@
         <v>PASS</v>
       </c>
       <c r="I269" s="8">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="J269" s="8">
         <v>1</v>
@@ -11982,7 +11982,7 @@
         <v>PASS</v>
       </c>
       <c r="I270" s="8">
-        <v>0.026</v>
+        <v>0.004</v>
       </c>
       <c r="J270" s="8">
         <v>1</v>
@@ -12023,7 +12023,7 @@
         <v>PASS</v>
       </c>
       <c r="I271" s="8">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="J271" s="8">
         <v>1</v>
@@ -12064,7 +12064,7 @@
         <v>PASS</v>
       </c>
       <c r="I272" s="8">
-        <v>0.049</v>
+        <v>0.003</v>
       </c>
       <c r="J272" s="8">
         <v>1</v>
@@ -12105,7 +12105,7 @@
         <v>PASS</v>
       </c>
       <c r="I273" s="8">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="J273" s="8">
         <v>1</v>
@@ -12146,7 +12146,7 @@
         <v>PASS</v>
       </c>
       <c r="I274" s="8">
-        <v>0.041</v>
+        <v>0.01</v>
       </c>
       <c r="J274" s="8">
         <v>1</v>
@@ -12187,7 +12187,7 @@
         <v>PASS</v>
       </c>
       <c r="I275" s="8">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="J275" s="8">
         <v>1</v>
@@ -12269,7 +12269,7 @@
         <v>PASS</v>
       </c>
       <c r="I277" s="8">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="J277" s="8">
         <v>1</v>
@@ -12351,7 +12351,7 @@
         <v>PASS</v>
       </c>
       <c r="I279" s="8">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="J279" s="8">
         <v>1</v>
@@ -12392,7 +12392,7 @@
         <v>PASS</v>
       </c>
       <c r="I280" s="8">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="J280" s="8">
         <v>1</v>
@@ -12433,7 +12433,7 @@
         <v>PASS</v>
       </c>
       <c r="I281" s="8">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="J281" s="8">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         <v>PASS</v>
       </c>
       <c r="I282" s="8">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J282" s="8">
         <v>1</v>
@@ -12515,7 +12515,7 @@
         <v>PASS</v>
       </c>
       <c r="I283" s="8">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="J283" s="8">
         <v>1</v>
@@ -12556,7 +12556,7 @@
         <v>PASS</v>
       </c>
       <c r="I284" s="8">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="J284" s="8">
         <v>1</v>
@@ -12597,7 +12597,7 @@
         <v>PASS</v>
       </c>
       <c r="I285" s="8">
-        <v>0.113</v>
+        <v>0.008</v>
       </c>
       <c r="J285" s="8">
         <v>1</v>
@@ -12638,7 +12638,7 @@
         <v>PASS</v>
       </c>
       <c r="I286" s="8">
-        <v>0.079</v>
+        <v>0.012</v>
       </c>
       <c r="J286" s="8">
         <v>1</v>
@@ -12679,7 +12679,7 @@
         <v>PASS</v>
       </c>
       <c r="I287" s="8">
-        <v>0.754</v>
+        <v>0.67</v>
       </c>
       <c r="J287" s="8">
         <v>1</v>
@@ -12720,7 +12720,7 @@
         <v>PASS</v>
       </c>
       <c r="I288" s="8">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J288" s="8">
         <v>1</v>
@@ -12761,7 +12761,7 @@
         <v>PASS</v>
       </c>
       <c r="I289" s="8">
-        <v>0.062</v>
+        <v>0.023</v>
       </c>
       <c r="J289" s="8">
         <v>1</v>
@@ -12802,7 +12802,7 @@
         <v>PASS</v>
       </c>
       <c r="I290" s="8">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="J290" s="8">
         <v>1</v>
@@ -12843,7 +12843,7 @@
         <v>PASS</v>
       </c>
       <c r="I291" s="8">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="J291" s="8">
         <v>1</v>
@@ -12884,7 +12884,7 @@
         <v>PASS</v>
       </c>
       <c r="I292" s="8">
-        <v>0.035</v>
+        <v>0.006</v>
       </c>
       <c r="J292" s="8">
         <v>1</v>
@@ -12925,7 +12925,7 @@
         <v>PASS</v>
       </c>
       <c r="I293" s="8">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J293" s="8">
         <v>1</v>
@@ -12966,7 +12966,7 @@
         <v>PASS</v>
       </c>
       <c r="I294" s="8">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="J294" s="8">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>PASS</v>
       </c>
       <c r="I295" s="8">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="J295" s="8">
         <v>1</v>
@@ -13048,7 +13048,7 @@
         <v>PASS</v>
       </c>
       <c r="I296" s="8">
-        <v>0.037</v>
+        <v>0.024</v>
       </c>
       <c r="J296" s="8">
         <v>1</v>
@@ -13089,7 +13089,7 @@
         <v>PASS</v>
       </c>
       <c r="I297" s="8">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="J297" s="8">
         <v>1</v>
@@ -13130,7 +13130,7 @@
         <v>PASS</v>
       </c>
       <c r="I298" s="8">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="J298" s="8">
         <v>1</v>
@@ -13171,7 +13171,7 @@
         <v>PASS</v>
       </c>
       <c r="I299" s="8">
-        <v>0.071</v>
+        <v>0.004</v>
       </c>
       <c r="J299" s="8">
         <v>1</v>
@@ -13212,7 +13212,7 @@
         <v>PASS</v>
       </c>
       <c r="I300" s="8">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="J300" s="8">
         <v>1</v>
@@ -13253,7 +13253,7 @@
         <v>PASS</v>
       </c>
       <c r="I301" s="8">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="J301" s="8">
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>PASS</v>
       </c>
       <c r="I302" s="8">
-        <v>0.034</v>
+        <v>0.002</v>
       </c>
       <c r="J302" s="8">
         <v>1</v>
@@ -13335,7 +13335,7 @@
         <v>PASS</v>
       </c>
       <c r="I303" s="8">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="J303" s="8">
         <v>1</v>
@@ -13376,7 +13376,7 @@
         <v>PASS</v>
       </c>
       <c r="I304" s="8">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="J304" s="8">
         <v>1</v>
@@ -13417,7 +13417,7 @@
         <v>PASS</v>
       </c>
       <c r="I305" s="8">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="J305" s="8">
         <v>1</v>
@@ -13458,7 +13458,7 @@
         <v>PASS</v>
       </c>
       <c r="I306" s="8">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J306" s="8">
         <v>1</v>
@@ -13499,7 +13499,7 @@
         <v>PASS</v>
       </c>
       <c r="I307" s="8">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="J307" s="8">
         <v>1</v>
@@ -13540,7 +13540,7 @@
         <v>PASS</v>
       </c>
       <c r="I308" s="8">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
       <c r="J308" s="8">
         <v>1</v>
@@ -13581,7 +13581,7 @@
         <v>PASS</v>
       </c>
       <c r="I309" s="8">
-        <v>0.067</v>
+        <v>0.006</v>
       </c>
       <c r="J309" s="8">
         <v>1</v>
@@ -13622,7 +13622,7 @@
         <v>PASS</v>
       </c>
       <c r="I310" s="8">
-        <v>0.033</v>
+        <v>0.007</v>
       </c>
       <c r="J310" s="8">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         <v>PASS</v>
       </c>
       <c r="I311" s="8">
-        <v>0.038</v>
+        <v>0.006</v>
       </c>
       <c r="J311" s="8">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>PASS</v>
       </c>
       <c r="I312" s="8">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="J312" s="8">
         <v>1</v>
@@ -13745,7 +13745,7 @@
         <v>PASS</v>
       </c>
       <c r="I313" s="8">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J313" s="8">
         <v>1</v>
@@ -13786,7 +13786,7 @@
         <v>PASS</v>
       </c>
       <c r="I314" s="8">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="J314" s="8">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         <v>PASS</v>
       </c>
       <c r="I315" s="8">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="J315" s="8">
         <v>1</v>
@@ -13868,7 +13868,7 @@
         <v>PASS</v>
       </c>
       <c r="I316" s="8">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="J316" s="8">
         <v>1</v>
@@ -13909,7 +13909,7 @@
         <v>PASS</v>
       </c>
       <c r="I317" s="8">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="J317" s="8">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         <v>PASS</v>
       </c>
       <c r="I318" s="8">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="J318" s="8">
         <v>1</v>
@@ -13991,7 +13991,7 @@
         <v>PASS</v>
       </c>
       <c r="I319" s="8">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="J319" s="8">
         <v>1</v>
@@ -14032,7 +14032,7 @@
         <v>PASS</v>
       </c>
       <c r="I320" s="8">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="J320" s="8">
         <v>1</v>
@@ -14073,7 +14073,7 @@
         <v>PASS</v>
       </c>
       <c r="I321" s="8">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="J321" s="8">
         <v>1</v>
@@ -14114,7 +14114,7 @@
         <v>PASS</v>
       </c>
       <c r="I322" s="8">
-        <v>0.031</v>
+        <v>0.013</v>
       </c>
       <c r="J322" s="8">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>PASS</v>
       </c>
       <c r="I323" s="8">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="J323" s="8">
         <v>1</v>
@@ -14196,7 +14196,7 @@
         <v>PASS</v>
       </c>
       <c r="I324" s="8">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="J324" s="8">
         <v>1</v>
@@ -14237,7 +14237,7 @@
         <v>PASS</v>
       </c>
       <c r="I325" s="8">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="J325" s="8">
         <v>1</v>
@@ -14278,7 +14278,7 @@
         <v>PASS</v>
       </c>
       <c r="I326" s="8">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="J326" s="8">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         <v>PASS</v>
       </c>
       <c r="I327" s="8">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="J327" s="8">
         <v>1</v>
@@ -14442,7 +14442,7 @@
         <v>PASS</v>
       </c>
       <c r="I330" s="8">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="J330" s="8">
         <v>1</v>
@@ -14514,7 +14514,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="8">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
@@ -14534,7 +14534,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="8">
-        <v>0.023</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="4">
@@ -14554,7 +14554,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="8">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
@@ -14574,7 +14574,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="8">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="6">
@@ -14594,7 +14594,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="8">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="7">
@@ -14614,7 +14614,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="8">
-        <v>0.963</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="8">
@@ -14634,7 +14634,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="8">
-        <v>0.028</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="9">
@@ -14654,7 +14654,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="8">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="10">
@@ -14674,7 +14674,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="8">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="11">
@@ -14694,7 +14694,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="8">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12">
@@ -14714,7 +14714,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="8">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
     </row>
   </sheetData>
@@ -22451,7 +22451,7 @@
         <v>GITHUB_RUN_ID</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>40362324115</v>
+        <v>40362633560</v>
       </c>
     </row>
     <row r="11">

--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <v>Generated: 26/10/2026, 10:19:26 pm IST</v>
+        <v>Generated: 26/10/2026, 10:30:18 pm IST</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         <v>Commit</v>
       </c>
       <c r="B8" s="8" t="str">
-        <v>a43b1df99d3267c68f009a15759c0e21930f23b0</v>
+        <v>41454daad15a94ce5eaca991b54b523052b296ff</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +585,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40362633560</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40364302150</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B14" s="8">
-        <v>36.43</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="16">
@@ -994,7 +994,7 @@
         <v>PASS</v>
       </c>
       <c r="I2" s="8">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="J2" s="8">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>PASS</v>
       </c>
       <c r="I3" s="8">
-        <v>0.013</v>
+        <v>0.027</v>
       </c>
       <c r="J3" s="8">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>PASS</v>
       </c>
       <c r="I4" s="8">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="J4" s="8">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>PASS</v>
       </c>
       <c r="I5" s="8">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>PASS</v>
       </c>
       <c r="I6" s="8">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1199,7 +1199,7 @@
         <v>PASS</v>
       </c>
       <c r="I7" s="8">
-        <v>0.017</v>
+        <v>0.029</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
@@ -1240,7 +1240,7 @@
         <v>PASS</v>
       </c>
       <c r="I8" s="8">
-        <v>0.052</v>
+        <v>0.025</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1281,7 +1281,7 @@
         <v>PASS</v>
       </c>
       <c r="I9" s="8">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>PASS</v>
       </c>
       <c r="I10" s="8">
-        <v>0.009</v>
+        <v>0.022</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1363,7 +1363,7 @@
         <v>PASS</v>
       </c>
       <c r="I11" s="8">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -1404,7 +1404,7 @@
         <v>PASS</v>
       </c>
       <c r="I12" s="8">
-        <v>0.009</v>
+        <v>0.05</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>PASS</v>
       </c>
       <c r="I13" s="8">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>PASS</v>
       </c>
       <c r="I14" s="8">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>PASS</v>
       </c>
       <c r="I15" s="8">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
@@ -1568,7 +1568,7 @@
         <v>PASS</v>
       </c>
       <c r="I16" s="8">
-        <v>0.007</v>
+        <v>0.035</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1609,7 +1609,7 @@
         <v>PASS</v>
       </c>
       <c r="I17" s="8">
-        <v>0.006</v>
+        <v>0.048</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>PASS</v>
       </c>
       <c r="I18" s="8">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>PASS</v>
       </c>
       <c r="I19" s="8">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>PASS</v>
       </c>
       <c r="I20" s="8">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         <v>PASS</v>
       </c>
       <c r="I21" s="8">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>PASS</v>
       </c>
       <c r="I22" s="8">
-        <v>0.011</v>
+        <v>0.069</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         <v>PASS</v>
       </c>
       <c r="I23" s="8">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
@@ -1896,7 +1896,7 @@
         <v>PASS</v>
       </c>
       <c r="I24" s="8">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -1937,7 +1937,7 @@
         <v>PASS</v>
       </c>
       <c r="I25" s="8">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>PASS</v>
       </c>
       <c r="I26" s="8">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2019,7 +2019,7 @@
         <v>PASS</v>
       </c>
       <c r="I27" s="8">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         <v>PASS</v>
       </c>
       <c r="I28" s="8">
-        <v>0.004</v>
+        <v>0.027</v>
       </c>
       <c r="J28" s="8">
         <v>1</v>
@@ -2101,7 +2101,7 @@
         <v>PASS</v>
       </c>
       <c r="I29" s="8">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="J29" s="8">
         <v>1</v>
@@ -2142,7 +2142,7 @@
         <v>PASS</v>
       </c>
       <c r="I30" s="8">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J30" s="8">
         <v>1</v>
@@ -2183,7 +2183,7 @@
         <v>PASS</v>
       </c>
       <c r="I31" s="8">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>PASS</v>
       </c>
       <c r="I32" s="8">
-        <v>0.003</v>
+        <v>0.051</v>
       </c>
       <c r="J32" s="8">
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>PASS</v>
       </c>
       <c r="I33" s="8">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J33" s="8">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>PASS</v>
       </c>
       <c r="I34" s="8">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2347,7 +2347,7 @@
         <v>PASS</v>
       </c>
       <c r="I35" s="8">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="J35" s="8">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>PASS</v>
       </c>
       <c r="I36" s="8">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2429,7 +2429,7 @@
         <v>PASS</v>
       </c>
       <c r="I37" s="8">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J37" s="8">
         <v>1</v>
@@ -2470,7 +2470,7 @@
         <v>PASS</v>
       </c>
       <c r="I38" s="8">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="J38" s="8">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>PASS</v>
       </c>
       <c r="I39" s="8">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J39" s="8">
         <v>1</v>
@@ -2552,7 +2552,7 @@
         <v>PASS</v>
       </c>
       <c r="I40" s="8">
-        <v>0.003</v>
+        <v>0.046</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2593,7 +2593,7 @@
         <v>PASS</v>
       </c>
       <c r="I41" s="8">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="J41" s="8">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>PASS</v>
       </c>
       <c r="I42" s="8">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="J42" s="8">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>PASS</v>
       </c>
       <c r="I43" s="8">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J43" s="8">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>PASS</v>
       </c>
       <c r="I44" s="8">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="J44" s="8">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>PASS</v>
       </c>
       <c r="I45" s="8">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="J45" s="8">
         <v>1</v>
@@ -2798,7 +2798,7 @@
         <v>PASS</v>
       </c>
       <c r="I46" s="8">
-        <v>0.009</v>
+        <v>0.017</v>
       </c>
       <c r="J46" s="8">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>PASS</v>
       </c>
       <c r="I47" s="8">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="J47" s="8">
         <v>1</v>
@@ -2880,7 +2880,7 @@
         <v>PASS</v>
       </c>
       <c r="I48" s="8">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="J48" s="8">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>PASS</v>
       </c>
       <c r="I49" s="8">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>PASS</v>
       </c>
       <c r="I50" s="8">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="J50" s="8">
         <v>1</v>
@@ -3003,7 +3003,7 @@
         <v>PASS</v>
       </c>
       <c r="I51" s="8">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="J51" s="8">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>PASS</v>
       </c>
       <c r="I52" s="8">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="J52" s="8">
         <v>1</v>
@@ -3085,7 +3085,7 @@
         <v>PASS</v>
       </c>
       <c r="I53" s="8">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>PASS</v>
       </c>
       <c r="I54" s="8">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="J54" s="8">
         <v>1</v>
@@ -3167,7 +3167,7 @@
         <v>PASS</v>
       </c>
       <c r="I55" s="8">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="J55" s="8">
         <v>1</v>
@@ -3249,7 +3249,7 @@
         <v>PASS</v>
       </c>
       <c r="I57" s="8">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="J57" s="8">
         <v>1</v>
@@ -3290,7 +3290,7 @@
         <v>PASS</v>
       </c>
       <c r="I58" s="8">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="J58" s="8">
         <v>1</v>
@@ -3372,7 +3372,7 @@
         <v>PASS</v>
       </c>
       <c r="I60" s="8">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J60" s="8">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>PASS</v>
       </c>
       <c r="I61" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J61" s="8">
         <v>1</v>
@@ -3454,7 +3454,7 @@
         <v>PASS</v>
       </c>
       <c r="I62" s="8">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="J62" s="8">
         <v>1</v>
@@ -3495,7 +3495,7 @@
         <v>PASS</v>
       </c>
       <c r="I63" s="8">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J63" s="8">
         <v>1</v>
@@ -3536,7 +3536,7 @@
         <v>PASS</v>
       </c>
       <c r="I64" s="8">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="J64" s="8">
         <v>1</v>
@@ -3577,7 +3577,7 @@
         <v>PASS</v>
       </c>
       <c r="I65" s="8">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="J65" s="8">
         <v>1</v>
@@ -3618,7 +3618,7 @@
         <v>PASS</v>
       </c>
       <c r="I66" s="8">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J66" s="8">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>PASS</v>
       </c>
       <c r="I67" s="8">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="J67" s="8">
         <v>1</v>
@@ -3700,7 +3700,7 @@
         <v>PASS</v>
       </c>
       <c r="I68" s="8">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="J68" s="8">
         <v>1</v>
@@ -3741,7 +3741,7 @@
         <v>PASS</v>
       </c>
       <c r="I69" s="8">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J69" s="8">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>PASS</v>
       </c>
       <c r="I70" s="8">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="J70" s="8">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>PASS</v>
       </c>
       <c r="I71" s="8">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="J71" s="8">
         <v>1</v>
@@ -3864,7 +3864,7 @@
         <v>PASS</v>
       </c>
       <c r="I72" s="8">
-        <v>0.031</v>
+        <v>0.007</v>
       </c>
       <c r="J72" s="8">
         <v>1</v>
@@ -3905,7 +3905,7 @@
         <v>PASS</v>
       </c>
       <c r="I73" s="8">
-        <v>0.027</v>
+        <v>0.074</v>
       </c>
       <c r="J73" s="8">
         <v>1</v>
@@ -3946,7 +3946,7 @@
         <v>PASS</v>
       </c>
       <c r="I74" s="8">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="J74" s="8">
         <v>1</v>
@@ -3987,7 +3987,7 @@
         <v>PASS</v>
       </c>
       <c r="I75" s="8">
-        <v>0.067</v>
+        <v>0.044</v>
       </c>
       <c r="J75" s="8">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>PASS</v>
       </c>
       <c r="I76" s="8">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="J76" s="8">
         <v>1</v>
@@ -4069,7 +4069,7 @@
         <v>PASS</v>
       </c>
       <c r="I77" s="8">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="J77" s="8">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>PASS</v>
       </c>
       <c r="I78" s="8">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="J78" s="8">
         <v>1</v>
@@ -4151,7 +4151,7 @@
         <v>PASS</v>
       </c>
       <c r="I79" s="8">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="J79" s="8">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         <v>PASS</v>
       </c>
       <c r="I80" s="8">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="J80" s="8">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>PASS</v>
       </c>
       <c r="I81" s="8">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J81" s="8">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>PASS</v>
       </c>
       <c r="I82" s="8">
-        <v>0.05</v>
+        <v>0.033</v>
       </c>
       <c r="J82" s="8">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>PASS</v>
       </c>
       <c r="I83" s="8">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="J83" s="8">
         <v>1</v>
@@ -4356,7 +4356,7 @@
         <v>PASS</v>
       </c>
       <c r="I84" s="8">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="J84" s="8">
         <v>1</v>
@@ -4397,7 +4397,7 @@
         <v>PASS</v>
       </c>
       <c r="I85" s="8">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J85" s="8">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>PASS</v>
       </c>
       <c r="I86" s="8">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="J86" s="8">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>PASS</v>
       </c>
       <c r="I87" s="8">
-        <v>0.008</v>
+        <v>0.027</v>
       </c>
       <c r="J87" s="8">
         <v>1</v>
@@ -4520,7 +4520,7 @@
         <v>PASS</v>
       </c>
       <c r="I88" s="8">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="J88" s="8">
         <v>1</v>
@@ -4561,7 +4561,7 @@
         <v>PASS</v>
       </c>
       <c r="I89" s="8">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="J89" s="8">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>PASS</v>
       </c>
       <c r="I90" s="8">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="J90" s="8">
         <v>1</v>
@@ -4643,7 +4643,7 @@
         <v>PASS</v>
       </c>
       <c r="I91" s="8">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J91" s="8">
         <v>1</v>
@@ -4684,7 +4684,7 @@
         <v>PASS</v>
       </c>
       <c r="I92" s="8">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="J92" s="8">
         <v>1</v>
@@ -4725,7 +4725,7 @@
         <v>PASS</v>
       </c>
       <c r="I93" s="8">
-        <v>0.038</v>
+        <v>0.05</v>
       </c>
       <c r="J93" s="8">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>PASS</v>
       </c>
       <c r="I94" s="8">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="J94" s="8">
         <v>1</v>
@@ -4807,7 +4807,7 @@
         <v>PASS</v>
       </c>
       <c r="I95" s="8">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="J95" s="8">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         <v>PASS</v>
       </c>
       <c r="I96" s="8">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="J96" s="8">
         <v>1</v>
@@ -4889,7 +4889,7 @@
         <v>PASS</v>
       </c>
       <c r="I97" s="8">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="J97" s="8">
         <v>1</v>
@@ -4930,7 +4930,7 @@
         <v>PASS</v>
       </c>
       <c r="I98" s="8">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J98" s="8">
         <v>1</v>
@@ -4971,7 +4971,7 @@
         <v>PASS</v>
       </c>
       <c r="I99" s="8">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="J99" s="8">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>PASS</v>
       </c>
       <c r="I100" s="8">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J100" s="8">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>PASS</v>
       </c>
       <c r="I101" s="8">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="J101" s="8">
         <v>1</v>
@@ -5094,7 +5094,7 @@
         <v>PASS</v>
       </c>
       <c r="I102" s="8">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="J102" s="8">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         <v>PASS</v>
       </c>
       <c r="I103" s="8">
-        <v>0.009</v>
+        <v>0.05</v>
       </c>
       <c r="J103" s="8">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>PASS</v>
       </c>
       <c r="I104" s="8">
-        <v>0.002</v>
+        <v>0.047</v>
       </c>
       <c r="J104" s="8">
         <v>1</v>
@@ -5217,7 +5217,7 @@
         <v>PASS</v>
       </c>
       <c r="I105" s="8">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="J105" s="8">
         <v>1</v>
@@ -5258,7 +5258,7 @@
         <v>PASS</v>
       </c>
       <c r="I106" s="8">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="J106" s="8">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         <v>PASS</v>
       </c>
       <c r="I107" s="8">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="J107" s="8">
         <v>1</v>
@@ -5340,7 +5340,7 @@
         <v>PASS</v>
       </c>
       <c r="I108" s="8">
-        <v>0.003</v>
+        <v>0.05</v>
       </c>
       <c r="J108" s="8">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>PASS</v>
       </c>
       <c r="I109" s="8">
-        <v>0.002</v>
+        <v>0.034</v>
       </c>
       <c r="J109" s="8">
         <v>1</v>
@@ -5422,7 +5422,7 @@
         <v>PASS</v>
       </c>
       <c r="I110" s="8">
-        <v>0.002</v>
+        <v>0.043</v>
       </c>
       <c r="J110" s="8">
         <v>1</v>
@@ -5463,7 +5463,7 @@
         <v>PASS</v>
       </c>
       <c r="I111" s="8">
-        <v>0.003</v>
+        <v>0.035</v>
       </c>
       <c r="J111" s="8">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>PASS</v>
       </c>
       <c r="I112" s="8">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J112" s="8">
         <v>1</v>
@@ -5545,7 +5545,7 @@
         <v>PASS</v>
       </c>
       <c r="I113" s="8">
-        <v>0.049</v>
+        <v>0.063</v>
       </c>
       <c r="J113" s="8">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         <v>PASS</v>
       </c>
       <c r="I114" s="8">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="J114" s="8">
         <v>1</v>
@@ -5627,7 +5627,7 @@
         <v>PASS</v>
       </c>
       <c r="I115" s="8">
-        <v>0.031</v>
+        <v>0.017</v>
       </c>
       <c r="J115" s="8">
         <v>1</v>
@@ -5668,7 +5668,7 @@
         <v>PASS</v>
       </c>
       <c r="I116" s="8">
-        <v>0.038</v>
+        <v>0.026</v>
       </c>
       <c r="J116" s="8">
         <v>1</v>
@@ -5709,7 +5709,7 @@
         <v>PASS</v>
       </c>
       <c r="I117" s="8">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="J117" s="8">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>PASS</v>
       </c>
       <c r="I118" s="8">
-        <v>0.003</v>
+        <v>0.081</v>
       </c>
       <c r="J118" s="8">
         <v>1</v>
@@ -5791,7 +5791,7 @@
         <v>PASS</v>
       </c>
       <c r="I119" s="8">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="J119" s="8">
         <v>1</v>
@@ -5832,7 +5832,7 @@
         <v>PASS</v>
       </c>
       <c r="I120" s="8">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="J120" s="8">
         <v>1</v>
@@ -5873,7 +5873,7 @@
         <v>PASS</v>
       </c>
       <c r="I121" s="8">
-        <v>0.002</v>
+        <v>0.033</v>
       </c>
       <c r="J121" s="8">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>PASS</v>
       </c>
       <c r="I122" s="8">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="J122" s="8">
         <v>1</v>
@@ -5955,7 +5955,7 @@
         <v>PASS</v>
       </c>
       <c r="I123" s="8">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="J123" s="8">
         <v>1</v>
@@ -5996,7 +5996,7 @@
         <v>PASS</v>
       </c>
       <c r="I124" s="8">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="J124" s="8">
         <v>1</v>
@@ -6037,7 +6037,7 @@
         <v>PASS</v>
       </c>
       <c r="I125" s="8">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="J125" s="8">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         <v>PASS</v>
       </c>
       <c r="I126" s="8">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="J126" s="8">
         <v>1</v>
@@ -6119,7 +6119,7 @@
         <v>PASS</v>
       </c>
       <c r="I127" s="8">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="J127" s="8">
         <v>1</v>
@@ -6160,7 +6160,7 @@
         <v>PASS</v>
       </c>
       <c r="I128" s="8">
-        <v>0.019</v>
+        <v>0.056</v>
       </c>
       <c r="J128" s="8">
         <v>1</v>
@@ -6201,7 +6201,7 @@
         <v>PASS</v>
       </c>
       <c r="I129" s="8">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="J129" s="8">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         <v>PASS</v>
       </c>
       <c r="I130" s="8">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J130" s="8">
         <v>1</v>
@@ -6283,7 +6283,7 @@
         <v>PASS</v>
       </c>
       <c r="I131" s="8">
-        <v>0.046</v>
+        <v>0.032</v>
       </c>
       <c r="J131" s="8">
         <v>1</v>
@@ -6324,7 +6324,7 @@
         <v>PASS</v>
       </c>
       <c r="I132" s="8">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="J132" s="8">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         <v>PASS</v>
       </c>
       <c r="I133" s="8">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
       <c r="J133" s="8">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>PASS</v>
       </c>
       <c r="I134" s="8">
-        <v>0.064</v>
+        <v>0.094</v>
       </c>
       <c r="J134" s="8">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>PASS</v>
       </c>
       <c r="I135" s="8">
-        <v>0.032</v>
+        <v>0.015</v>
       </c>
       <c r="J135" s="8">
         <v>1</v>
@@ -6488,7 +6488,7 @@
         <v>PASS</v>
       </c>
       <c r="I136" s="8">
-        <v>0.01</v>
+        <v>0.051</v>
       </c>
       <c r="J136" s="8">
         <v>1</v>
@@ -6529,7 +6529,7 @@
         <v>PASS</v>
       </c>
       <c r="I137" s="8">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="J137" s="8">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>PASS</v>
       </c>
       <c r="I138" s="8">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="J138" s="8">
         <v>1</v>
@@ -6611,7 +6611,7 @@
         <v>PASS</v>
       </c>
       <c r="I139" s="8">
-        <v>0.014</v>
+        <v>0.041</v>
       </c>
       <c r="J139" s="8">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>PASS</v>
       </c>
       <c r="I140" s="8">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="J140" s="8">
         <v>1</v>
@@ -6693,7 +6693,7 @@
         <v>PASS</v>
       </c>
       <c r="I141" s="8">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J141" s="8">
         <v>1</v>
@@ -6734,7 +6734,7 @@
         <v>PASS</v>
       </c>
       <c r="I142" s="8">
-        <v>0.028</v>
+        <v>0.062</v>
       </c>
       <c r="J142" s="8">
         <v>1</v>
@@ -6775,7 +6775,7 @@
         <v>PASS</v>
       </c>
       <c r="I143" s="8">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
       <c r="J143" s="8">
         <v>1</v>
@@ -6816,7 +6816,7 @@
         <v>PASS</v>
       </c>
       <c r="I144" s="8">
-        <v>0.062</v>
+        <v>0.014</v>
       </c>
       <c r="J144" s="8">
         <v>1</v>
@@ -6857,7 +6857,7 @@
         <v>PASS</v>
       </c>
       <c r="I145" s="8">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="J145" s="8">
         <v>1</v>
@@ -6898,7 +6898,7 @@
         <v>PASS</v>
       </c>
       <c r="I146" s="8">
-        <v>0.047</v>
+        <v>0.07</v>
       </c>
       <c r="J146" s="8">
         <v>1</v>
@@ -6939,7 +6939,7 @@
         <v>PASS</v>
       </c>
       <c r="I147" s="8">
-        <v>0.021</v>
+        <v>0.048</v>
       </c>
       <c r="J147" s="8">
         <v>1</v>
@@ -6980,7 +6980,7 @@
         <v>PASS</v>
       </c>
       <c r="I148" s="8">
-        <v>0.061</v>
+        <v>0.018</v>
       </c>
       <c r="J148" s="8">
         <v>1</v>
@@ -7021,7 +7021,7 @@
         <v>PASS</v>
       </c>
       <c r="I149" s="8">
-        <v>0.059</v>
+        <v>0.042</v>
       </c>
       <c r="J149" s="8">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>PASS</v>
       </c>
       <c r="I150" s="8">
-        <v>0.013</v>
+        <v>0.044</v>
       </c>
       <c r="J150" s="8">
         <v>1</v>
@@ -7103,7 +7103,7 @@
         <v>PASS</v>
       </c>
       <c r="I151" s="8">
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
       <c r="J151" s="8">
         <v>1</v>
@@ -7144,7 +7144,7 @@
         <v>PASS</v>
       </c>
       <c r="I152" s="8">
-        <v>0.027</v>
+        <v>0.016</v>
       </c>
       <c r="J152" s="8">
         <v>1</v>
@@ -7185,7 +7185,7 @@
         <v>PASS</v>
       </c>
       <c r="I153" s="8">
-        <v>0.095</v>
+        <v>0.638</v>
       </c>
       <c r="J153" s="8">
         <v>1</v>
@@ -7226,7 +7226,7 @@
         <v>PASS</v>
       </c>
       <c r="I154" s="8">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="J154" s="8">
         <v>1</v>
@@ -7267,7 +7267,7 @@
         <v>PASS</v>
       </c>
       <c r="I155" s="8">
-        <v>0.029</v>
+        <v>0.057</v>
       </c>
       <c r="J155" s="8">
         <v>1</v>
@@ -7308,7 +7308,7 @@
         <v>PASS</v>
       </c>
       <c r="I156" s="8">
-        <v>0.035</v>
+        <v>0.057</v>
       </c>
       <c r="J156" s="8">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>PASS</v>
       </c>
       <c r="I157" s="8">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="J157" s="8">
         <v>1</v>
@@ -7390,7 +7390,7 @@
         <v>PASS</v>
       </c>
       <c r="I158" s="8">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="J158" s="8">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         <v>PASS</v>
       </c>
       <c r="I159" s="8">
-        <v>0.011</v>
+        <v>0.205</v>
       </c>
       <c r="J159" s="8">
         <v>1</v>
@@ -7472,7 +7472,7 @@
         <v>PASS</v>
       </c>
       <c r="I160" s="8">
-        <v>0.028</v>
+        <v>0.047</v>
       </c>
       <c r="J160" s="8">
         <v>1</v>
@@ -7513,7 +7513,7 @@
         <v>PASS</v>
       </c>
       <c r="I161" s="8">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="J161" s="8">
         <v>1</v>
@@ -7554,7 +7554,7 @@
         <v>PASS</v>
       </c>
       <c r="I162" s="8">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="J162" s="8">
         <v>1</v>
@@ -7595,7 +7595,7 @@
         <v>PASS</v>
       </c>
       <c r="I163" s="8">
-        <v>0.02</v>
+        <v>0.343</v>
       </c>
       <c r="J163" s="8">
         <v>1</v>
@@ -7636,7 +7636,7 @@
         <v>PASS</v>
       </c>
       <c r="I164" s="8">
-        <v>0.058</v>
+        <v>0.038</v>
       </c>
       <c r="J164" s="8">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>PASS</v>
       </c>
       <c r="I165" s="8">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="J165" s="8">
         <v>1</v>
@@ -7718,7 +7718,7 @@
         <v>PASS</v>
       </c>
       <c r="I166" s="8">
-        <v>0.018</v>
+        <v>0.045</v>
       </c>
       <c r="J166" s="8">
         <v>1</v>
@@ -7759,7 +7759,7 @@
         <v>PASS</v>
       </c>
       <c r="I167" s="8">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="J167" s="8">
         <v>1</v>
@@ -7800,7 +7800,7 @@
         <v>PASS</v>
       </c>
       <c r="I168" s="8">
-        <v>0.021</v>
+        <v>0.054</v>
       </c>
       <c r="J168" s="8">
         <v>1</v>
@@ -7841,7 +7841,7 @@
         <v>PASS</v>
       </c>
       <c r="I169" s="8">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="J169" s="8">
         <v>1</v>
@@ -7882,7 +7882,7 @@
         <v>PASS</v>
       </c>
       <c r="I170" s="8">
-        <v>0.014</v>
+        <v>0.047</v>
       </c>
       <c r="J170" s="8">
         <v>1</v>
@@ -7923,7 +7923,7 @@
         <v>PASS</v>
       </c>
       <c r="I171" s="8">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J171" s="8">
         <v>1</v>
@@ -7964,7 +7964,7 @@
         <v>PASS</v>
       </c>
       <c r="I172" s="8">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="J172" s="8">
         <v>1</v>
@@ -8005,7 +8005,7 @@
         <v>PASS</v>
       </c>
       <c r="I173" s="8">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="J173" s="8">
         <v>1</v>
@@ -8046,7 +8046,7 @@
         <v>PASS</v>
       </c>
       <c r="I174" s="8">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="J174" s="8">
         <v>1</v>
@@ -8087,7 +8087,7 @@
         <v>PASS</v>
       </c>
       <c r="I175" s="8">
-        <v>0.016</v>
+        <v>0.05</v>
       </c>
       <c r="J175" s="8">
         <v>1</v>
@@ -8128,7 +8128,7 @@
         <v>PASS</v>
       </c>
       <c r="I176" s="8">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="J176" s="8">
         <v>1</v>
@@ -8169,7 +8169,7 @@
         <v>PASS</v>
       </c>
       <c r="I177" s="8">
-        <v>0.029</v>
+        <v>0.024</v>
       </c>
       <c r="J177" s="8">
         <v>1</v>
@@ -8210,7 +8210,7 @@
         <v>PASS</v>
       </c>
       <c r="I178" s="8">
-        <v>0.009</v>
+        <v>0.032</v>
       </c>
       <c r="J178" s="8">
         <v>1</v>
@@ -8251,7 +8251,7 @@
         <v>PASS</v>
       </c>
       <c r="I179" s="8">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J179" s="8">
         <v>1</v>
@@ -8292,7 +8292,7 @@
         <v>PASS</v>
       </c>
       <c r="I180" s="8">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J180" s="8">
         <v>1</v>
@@ -8333,7 +8333,7 @@
         <v>PASS</v>
       </c>
       <c r="I181" s="8">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="J181" s="8">
         <v>1</v>
@@ -8374,7 +8374,7 @@
         <v>PASS</v>
       </c>
       <c r="I182" s="8">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="J182" s="8">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         <v>PASS</v>
       </c>
       <c r="I183" s="8">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J183" s="8">
         <v>1</v>
@@ -8456,7 +8456,7 @@
         <v>PASS</v>
       </c>
       <c r="I184" s="8">
-        <v>0.554</v>
+        <v>0.621</v>
       </c>
       <c r="J184" s="8">
         <v>1</v>
@@ -8497,7 +8497,7 @@
         <v>PASS</v>
       </c>
       <c r="I185" s="8">
-        <v>0.886</v>
+        <v>0.928</v>
       </c>
       <c r="J185" s="8">
         <v>1</v>
@@ -8538,7 +8538,7 @@
         <v>PASS</v>
       </c>
       <c r="I186" s="8">
-        <v>0.875</v>
+        <v>0.963</v>
       </c>
       <c r="J186" s="8">
         <v>1</v>
@@ -8579,7 +8579,7 @@
         <v>PASS</v>
       </c>
       <c r="I187" s="8">
-        <v>0.508</v>
+        <v>0.536</v>
       </c>
       <c r="J187" s="8">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>PASS</v>
       </c>
       <c r="I188" s="8">
-        <v>0.598</v>
+        <v>0.829</v>
       </c>
       <c r="J188" s="8">
         <v>1</v>
@@ -8661,7 +8661,7 @@
         <v>PASS</v>
       </c>
       <c r="I189" s="8">
-        <v>0.922</v>
+        <v>1.485</v>
       </c>
       <c r="J189" s="8">
         <v>1</v>
@@ -8702,7 +8702,7 @@
         <v>PASS</v>
       </c>
       <c r="I190" s="8">
-        <v>0.57</v>
+        <v>1.106</v>
       </c>
       <c r="J190" s="8">
         <v>1</v>
@@ -8743,7 +8743,7 @@
         <v>PASS</v>
       </c>
       <c r="I191" s="8">
-        <v>1.302</v>
+        <v>1.71</v>
       </c>
       <c r="J191" s="8">
         <v>1</v>
@@ -8784,7 +8784,7 @@
         <v>PASS</v>
       </c>
       <c r="I192" s="8">
-        <v>0.738</v>
+        <v>1.16</v>
       </c>
       <c r="J192" s="8">
         <v>1</v>
@@ -8825,7 +8825,7 @@
         <v>PASS</v>
       </c>
       <c r="I193" s="8">
-        <v>0.015</v>
+        <v>0.058</v>
       </c>
       <c r="J193" s="8">
         <v>1</v>
@@ -8866,7 +8866,7 @@
         <v>PASS</v>
       </c>
       <c r="I194" s="8">
-        <v>0.053</v>
+        <v>0.073</v>
       </c>
       <c r="J194" s="8">
         <v>1</v>
@@ -8948,7 +8948,7 @@
         <v>PASS</v>
       </c>
       <c r="I196" s="8">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="J196" s="8">
         <v>1</v>
@@ -8989,7 +8989,7 @@
         <v>PASS</v>
       </c>
       <c r="I197" s="8">
-        <v>0.888</v>
+        <v>1.534</v>
       </c>
       <c r="J197" s="8">
         <v>1</v>
@@ -9030,7 +9030,7 @@
         <v>PASS</v>
       </c>
       <c r="I198" s="8">
-        <v>1.157</v>
+        <v>1.288</v>
       </c>
       <c r="J198" s="8">
         <v>1</v>
@@ -9071,7 +9071,7 @@
         <v>PASS</v>
       </c>
       <c r="I199" s="8">
-        <v>1.512</v>
+        <v>1.861</v>
       </c>
       <c r="J199" s="8">
         <v>1</v>
@@ -9112,7 +9112,7 @@
         <v>PASS</v>
       </c>
       <c r="I200" s="8">
-        <v>1.317</v>
+        <v>1.53</v>
       </c>
       <c r="J200" s="8">
         <v>1</v>
@@ -9153,7 +9153,7 @@
         <v>PASS</v>
       </c>
       <c r="I201" s="8">
-        <v>1.646</v>
+        <v>2.207</v>
       </c>
       <c r="J201" s="8">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>PASS</v>
       </c>
       <c r="I202" s="8">
-        <v>1.72</v>
+        <v>1.949</v>
       </c>
       <c r="J202" s="8">
         <v>1</v>
@@ -9235,7 +9235,7 @@
         <v>PASS</v>
       </c>
       <c r="I203" s="8">
-        <v>0.715</v>
+        <v>0.819</v>
       </c>
       <c r="J203" s="8">
         <v>1</v>
@@ -9276,7 +9276,7 @@
         <v>PASS</v>
       </c>
       <c r="I204" s="8">
-        <v>0.004</v>
+        <v>0.091</v>
       </c>
       <c r="J204" s="8">
         <v>1</v>
@@ -9317,7 +9317,7 @@
         <v>PASS</v>
       </c>
       <c r="I205" s="8">
-        <v>0.01</v>
+        <v>0.051</v>
       </c>
       <c r="J205" s="8">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         <v>PASS</v>
       </c>
       <c r="I206" s="8">
-        <v>0.004</v>
+        <v>0.051</v>
       </c>
       <c r="J206" s="8">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         <v>PASS</v>
       </c>
       <c r="I207" s="8">
-        <v>0.012</v>
+        <v>0.061</v>
       </c>
       <c r="J207" s="8">
         <v>1</v>
@@ -9440,7 +9440,7 @@
         <v>PASS</v>
       </c>
       <c r="I208" s="8">
-        <v>0.006</v>
+        <v>0.146</v>
       </c>
       <c r="J208" s="8">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>PASS</v>
       </c>
       <c r="I209" s="8">
-        <v>0.011</v>
+        <v>0.037</v>
       </c>
       <c r="J209" s="8">
         <v>1</v>
@@ -9522,7 +9522,7 @@
         <v>PASS</v>
       </c>
       <c r="I210" s="8">
-        <v>0.041</v>
+        <v>0.099</v>
       </c>
       <c r="J210" s="8">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>PASS</v>
       </c>
       <c r="I211" s="8">
-        <v>1.165</v>
+        <v>1.427</v>
       </c>
       <c r="J211" s="8">
         <v>1</v>
@@ -9604,7 +9604,7 @@
         <v>PASS</v>
       </c>
       <c r="I212" s="8">
-        <v>0.803</v>
+        <v>1.022</v>
       </c>
       <c r="J212" s="8">
         <v>1</v>
@@ -9645,7 +9645,7 @@
         <v>PASS</v>
       </c>
       <c r="I213" s="8">
-        <v>1.247</v>
+        <v>1.983</v>
       </c>
       <c r="J213" s="8">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         <v>PASS</v>
       </c>
       <c r="I214" s="8">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="J214" s="8">
         <v>1</v>
@@ -9727,7 +9727,7 @@
         <v>PASS</v>
       </c>
       <c r="I215" s="8">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="J215" s="8">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         <v>PASS</v>
       </c>
       <c r="I216" s="8">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="J216" s="8">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         <v>PASS</v>
       </c>
       <c r="I217" s="8">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="J217" s="8">
         <v>1</v>
@@ -9850,7 +9850,7 @@
         <v>PASS</v>
       </c>
       <c r="I218" s="8">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="J218" s="8">
         <v>1</v>
@@ -9891,7 +9891,7 @@
         <v>PASS</v>
       </c>
       <c r="I219" s="8">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="J219" s="8">
         <v>1</v>
@@ -9932,7 +9932,7 @@
         <v>PASS</v>
       </c>
       <c r="I220" s="8">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="J220" s="8">
         <v>1</v>
@@ -9973,7 +9973,7 @@
         <v>PASS</v>
       </c>
       <c r="I221" s="8">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="J221" s="8">
         <v>1</v>
@@ -10014,7 +10014,7 @@
         <v>PASS</v>
       </c>
       <c r="I222" s="8">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J222" s="8">
         <v>1</v>
@@ -10055,7 +10055,7 @@
         <v>PASS</v>
       </c>
       <c r="I223" s="8">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="J223" s="8">
         <v>1</v>
@@ -10096,7 +10096,7 @@
         <v>PASS</v>
       </c>
       <c r="I224" s="8">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="J224" s="8">
         <v>1</v>
@@ -10137,7 +10137,7 @@
         <v>PASS</v>
       </c>
       <c r="I225" s="8">
-        <v>0.015</v>
+        <v>0.043</v>
       </c>
       <c r="J225" s="8">
         <v>1</v>
@@ -10178,7 +10178,7 @@
         <v>PASS</v>
       </c>
       <c r="I226" s="8">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="J226" s="8">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>PASS</v>
       </c>
       <c r="I227" s="8">
-        <v>0.003</v>
+        <v>0.031</v>
       </c>
       <c r="J227" s="8">
         <v>1</v>
@@ -10260,7 +10260,7 @@
         <v>PASS</v>
       </c>
       <c r="I228" s="8">
-        <v>0.007</v>
+        <v>0.105</v>
       </c>
       <c r="J228" s="8">
         <v>1</v>
@@ -10301,7 +10301,7 @@
         <v>PASS</v>
       </c>
       <c r="I229" s="8">
-        <v>0.006</v>
+        <v>0.047</v>
       </c>
       <c r="J229" s="8">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         <v>PASS</v>
       </c>
       <c r="I230" s="8">
-        <v>0.013</v>
+        <v>0.037</v>
       </c>
       <c r="J230" s="8">
         <v>1</v>
@@ -10383,7 +10383,7 @@
         <v>PASS</v>
       </c>
       <c r="I231" s="8">
-        <v>0.004</v>
+        <v>0.058</v>
       </c>
       <c r="J231" s="8">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         <v>PASS</v>
       </c>
       <c r="I232" s="8">
-        <v>0.009</v>
+        <v>0.111</v>
       </c>
       <c r="J232" s="8">
         <v>1</v>
@@ -10465,7 +10465,7 @@
         <v>PASS</v>
       </c>
       <c r="I233" s="8">
-        <v>0.023</v>
+        <v>0.062</v>
       </c>
       <c r="J233" s="8">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>PASS</v>
       </c>
       <c r="I234" s="8">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="J234" s="8">
         <v>1</v>
@@ -10547,7 +10547,7 @@
         <v>PASS</v>
       </c>
       <c r="I235" s="8">
-        <v>0.064</v>
+        <v>0.01</v>
       </c>
       <c r="J235" s="8">
         <v>1</v>
@@ -10588,7 +10588,7 @@
         <v>PASS</v>
       </c>
       <c r="I236" s="8">
-        <v>0.033</v>
+        <v>0.089</v>
       </c>
       <c r="J236" s="8">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         <v>PASS</v>
       </c>
       <c r="I237" s="8">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
       <c r="J237" s="8">
         <v>1</v>
@@ -10670,7 +10670,7 @@
         <v>PASS</v>
       </c>
       <c r="I238" s="8">
-        <v>0.016</v>
+        <v>0.029</v>
       </c>
       <c r="J238" s="8">
         <v>1</v>
@@ -10711,7 +10711,7 @@
         <v>PASS</v>
       </c>
       <c r="I239" s="8">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="J239" s="8">
         <v>1</v>
@@ -10752,7 +10752,7 @@
         <v>PASS</v>
       </c>
       <c r="I240" s="8">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="J240" s="8">
         <v>1</v>
@@ -10793,7 +10793,7 @@
         <v>PASS</v>
       </c>
       <c r="I241" s="8">
-        <v>0.012</v>
+        <v>0.028</v>
       </c>
       <c r="J241" s="8">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         <v>PASS</v>
       </c>
       <c r="I242" s="8">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="J242" s="8">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>PASS</v>
       </c>
       <c r="I243" s="8">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="J243" s="8">
         <v>1</v>
@@ -10916,7 +10916,7 @@
         <v>PASS</v>
       </c>
       <c r="I244" s="8">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="J244" s="8">
         <v>1</v>
@@ -10957,7 +10957,7 @@
         <v>PASS</v>
       </c>
       <c r="I245" s="8">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="J245" s="8">
         <v>1</v>
@@ -10998,7 +10998,7 @@
         <v>PASS</v>
       </c>
       <c r="I246" s="8">
-        <v>0.018</v>
+        <v>0.04</v>
       </c>
       <c r="J246" s="8">
         <v>1</v>
@@ -11039,7 +11039,7 @@
         <v>PASS</v>
       </c>
       <c r="I247" s="8">
-        <v>0.017</v>
+        <v>0.051</v>
       </c>
       <c r="J247" s="8">
         <v>1</v>
@@ -11080,7 +11080,7 @@
         <v>PASS</v>
       </c>
       <c r="I248" s="8">
-        <v>0.005</v>
+        <v>0.049</v>
       </c>
       <c r="J248" s="8">
         <v>1</v>
@@ -11121,7 +11121,7 @@
         <v>PASS</v>
       </c>
       <c r="I249" s="8">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="J249" s="8">
         <v>1</v>
@@ -11162,7 +11162,7 @@
         <v>PASS</v>
       </c>
       <c r="I250" s="8">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="J250" s="8">
         <v>1</v>
@@ -11203,7 +11203,7 @@
         <v>PASS</v>
       </c>
       <c r="I251" s="8">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="J251" s="8">
         <v>1</v>
@@ -11244,7 +11244,7 @@
         <v>PASS</v>
       </c>
       <c r="I252" s="8">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="J252" s="8">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>PASS</v>
       </c>
       <c r="I253" s="8">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="J253" s="8">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>PASS</v>
       </c>
       <c r="I254" s="8">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
       <c r="J254" s="8">
         <v>1</v>
@@ -11408,7 +11408,7 @@
         <v>PASS</v>
       </c>
       <c r="I256" s="8">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="J256" s="8">
         <v>1</v>
@@ -11449,7 +11449,7 @@
         <v>PASS</v>
       </c>
       <c r="I257" s="8">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="J257" s="8">
         <v>1</v>
@@ -11490,7 +11490,7 @@
         <v>PASS</v>
       </c>
       <c r="I258" s="8">
-        <v>0.041</v>
+        <v>0.02</v>
       </c>
       <c r="J258" s="8">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>PASS</v>
       </c>
       <c r="I259" s="8">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="J259" s="8">
         <v>1</v>
@@ -11572,7 +11572,7 @@
         <v>PASS</v>
       </c>
       <c r="I260" s="8">
-        <v>0.003</v>
+        <v>0.027</v>
       </c>
       <c r="J260" s="8">
         <v>1</v>
@@ -11613,7 +11613,7 @@
         <v>PASS</v>
       </c>
       <c r="I261" s="8">
-        <v>0.005</v>
+        <v>0.034</v>
       </c>
       <c r="J261" s="8">
         <v>1</v>
@@ -11654,7 +11654,7 @@
         <v>PASS</v>
       </c>
       <c r="I262" s="8">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="J262" s="8">
         <v>1</v>
@@ -11695,7 +11695,7 @@
         <v>PASS</v>
       </c>
       <c r="I263" s="8">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="J263" s="8">
         <v>1</v>
@@ -11736,7 +11736,7 @@
         <v>PASS</v>
       </c>
       <c r="I264" s="8">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="J264" s="8">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>PASS</v>
       </c>
       <c r="I265" s="8">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="J265" s="8">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>PASS</v>
       </c>
       <c r="I266" s="8">
-        <v>0.139</v>
+        <v>0.021</v>
       </c>
       <c r="J266" s="8">
         <v>1</v>
@@ -11859,7 +11859,7 @@
         <v>PASS</v>
       </c>
       <c r="I267" s="8">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="J267" s="8">
         <v>1</v>
@@ -11900,7 +11900,7 @@
         <v>PASS</v>
       </c>
       <c r="I268" s="8">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="J268" s="8">
         <v>1</v>
@@ -11941,7 +11941,7 @@
         <v>PASS</v>
       </c>
       <c r="I269" s="8">
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
       <c r="J269" s="8">
         <v>1</v>
@@ -11982,7 +11982,7 @@
         <v>PASS</v>
       </c>
       <c r="I270" s="8">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J270" s="8">
         <v>1</v>
@@ -12023,7 +12023,7 @@
         <v>PASS</v>
       </c>
       <c r="I271" s="8">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="J271" s="8">
         <v>1</v>
@@ -12064,7 +12064,7 @@
         <v>PASS</v>
       </c>
       <c r="I272" s="8">
-        <v>0.003</v>
+        <v>0.029</v>
       </c>
       <c r="J272" s="8">
         <v>1</v>
@@ -12105,7 +12105,7 @@
         <v>PASS</v>
       </c>
       <c r="I273" s="8">
-        <v>0.002</v>
+        <v>0.025</v>
       </c>
       <c r="J273" s="8">
         <v>1</v>
@@ -12146,7 +12146,7 @@
         <v>PASS</v>
       </c>
       <c r="I274" s="8">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="J274" s="8">
         <v>1</v>
@@ -12187,7 +12187,7 @@
         <v>PASS</v>
       </c>
       <c r="I275" s="8">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="J275" s="8">
         <v>1</v>
@@ -12228,7 +12228,7 @@
         <v>PASS</v>
       </c>
       <c r="I276" s="8">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="J276" s="8">
         <v>1</v>
@@ -12269,7 +12269,7 @@
         <v>PASS</v>
       </c>
       <c r="I277" s="8">
-        <v>0.003</v>
+        <v>0.016</v>
       </c>
       <c r="J277" s="8">
         <v>1</v>
@@ -12310,7 +12310,7 @@
         <v>PASS</v>
       </c>
       <c r="I278" s="8">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="J278" s="8">
         <v>1</v>
@@ -12351,7 +12351,7 @@
         <v>PASS</v>
       </c>
       <c r="I279" s="8">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J279" s="8">
         <v>1</v>
@@ -12392,7 +12392,7 @@
         <v>PASS</v>
       </c>
       <c r="I280" s="8">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J280" s="8">
         <v>1</v>
@@ -12433,7 +12433,7 @@
         <v>PASS</v>
       </c>
       <c r="I281" s="8">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="J281" s="8">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         <v>PASS</v>
       </c>
       <c r="I282" s="8">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J282" s="8">
         <v>1</v>
@@ -12515,7 +12515,7 @@
         <v>PASS</v>
       </c>
       <c r="I283" s="8">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="J283" s="8">
         <v>1</v>
@@ -12556,7 +12556,7 @@
         <v>PASS</v>
       </c>
       <c r="I284" s="8">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="J284" s="8">
         <v>1</v>
@@ -12597,7 +12597,7 @@
         <v>PASS</v>
       </c>
       <c r="I285" s="8">
-        <v>0.008</v>
+        <v>0.081</v>
       </c>
       <c r="J285" s="8">
         <v>1</v>
@@ -12638,7 +12638,7 @@
         <v>PASS</v>
       </c>
       <c r="I286" s="8">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J286" s="8">
         <v>1</v>
@@ -12679,7 +12679,7 @@
         <v>PASS</v>
       </c>
       <c r="I287" s="8">
-        <v>0.67</v>
+        <v>0.706</v>
       </c>
       <c r="J287" s="8">
         <v>1</v>
@@ -12720,7 +12720,7 @@
         <v>PASS</v>
       </c>
       <c r="I288" s="8">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="J288" s="8">
         <v>1</v>
@@ -12761,7 +12761,7 @@
         <v>PASS</v>
       </c>
       <c r="I289" s="8">
-        <v>0.023</v>
+        <v>0.098</v>
       </c>
       <c r="J289" s="8">
         <v>1</v>
@@ -12802,7 +12802,7 @@
         <v>PASS</v>
       </c>
       <c r="I290" s="8">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="J290" s="8">
         <v>1</v>
@@ -12843,7 +12843,7 @@
         <v>PASS</v>
       </c>
       <c r="I291" s="8">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="J291" s="8">
         <v>1</v>
@@ -12884,7 +12884,7 @@
         <v>PASS</v>
       </c>
       <c r="I292" s="8">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="J292" s="8">
         <v>1</v>
@@ -12925,7 +12925,7 @@
         <v>PASS</v>
       </c>
       <c r="I293" s="8">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J293" s="8">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>PASS</v>
       </c>
       <c r="I295" s="8">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="J295" s="8">
         <v>1</v>
@@ -13048,7 +13048,7 @@
         <v>PASS</v>
       </c>
       <c r="I296" s="8">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J296" s="8">
         <v>1</v>
@@ -13130,7 +13130,7 @@
         <v>PASS</v>
       </c>
       <c r="I298" s="8">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J298" s="8">
         <v>1</v>
@@ -13171,7 +13171,7 @@
         <v>PASS</v>
       </c>
       <c r="I299" s="8">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="J299" s="8">
         <v>1</v>
@@ -13212,7 +13212,7 @@
         <v>PASS</v>
       </c>
       <c r="I300" s="8">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="J300" s="8">
         <v>1</v>
@@ -13253,7 +13253,7 @@
         <v>PASS</v>
       </c>
       <c r="I301" s="8">
-        <v>0.003</v>
+        <v>0.05</v>
       </c>
       <c r="J301" s="8">
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>PASS</v>
       </c>
       <c r="I302" s="8">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="J302" s="8">
         <v>1</v>
@@ -13335,7 +13335,7 @@
         <v>PASS</v>
       </c>
       <c r="I303" s="8">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="J303" s="8">
         <v>1</v>
@@ -13376,7 +13376,7 @@
         <v>PASS</v>
       </c>
       <c r="I304" s="8">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="J304" s="8">
         <v>1</v>
@@ -13417,7 +13417,7 @@
         <v>PASS</v>
       </c>
       <c r="I305" s="8">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J305" s="8">
         <v>1</v>
@@ -13458,7 +13458,7 @@
         <v>PASS</v>
       </c>
       <c r="I306" s="8">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="J306" s="8">
         <v>1</v>
@@ -13499,7 +13499,7 @@
         <v>PASS</v>
       </c>
       <c r="I307" s="8">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="J307" s="8">
         <v>1</v>
@@ -13540,7 +13540,7 @@
         <v>PASS</v>
       </c>
       <c r="I308" s="8">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J308" s="8">
         <v>1</v>
@@ -13581,7 +13581,7 @@
         <v>PASS</v>
       </c>
       <c r="I309" s="8">
-        <v>0.006</v>
+        <v>0.05</v>
       </c>
       <c r="J309" s="8">
         <v>1</v>
@@ -13622,7 +13622,7 @@
         <v>PASS</v>
       </c>
       <c r="I310" s="8">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="J310" s="8">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         <v>PASS</v>
       </c>
       <c r="I311" s="8">
-        <v>0.006</v>
+        <v>0.051</v>
       </c>
       <c r="J311" s="8">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>PASS</v>
       </c>
       <c r="I312" s="8">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="J312" s="8">
         <v>1</v>
@@ -13745,7 +13745,7 @@
         <v>PASS</v>
       </c>
       <c r="I313" s="8">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="J313" s="8">
         <v>1</v>
@@ -13786,7 +13786,7 @@
         <v>PASS</v>
       </c>
       <c r="I314" s="8">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J314" s="8">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         <v>PASS</v>
       </c>
       <c r="I315" s="8">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="J315" s="8">
         <v>1</v>
@@ -13868,7 +13868,7 @@
         <v>PASS</v>
       </c>
       <c r="I316" s="8">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="J316" s="8">
         <v>1</v>
@@ -13909,7 +13909,7 @@
         <v>PASS</v>
       </c>
       <c r="I317" s="8">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="J317" s="8">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         <v>PASS</v>
       </c>
       <c r="I318" s="8">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="J318" s="8">
         <v>1</v>
@@ -13991,7 +13991,7 @@
         <v>PASS</v>
       </c>
       <c r="I319" s="8">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="J319" s="8">
         <v>1</v>
@@ -14032,7 +14032,7 @@
         <v>PASS</v>
       </c>
       <c r="I320" s="8">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="J320" s="8">
         <v>1</v>
@@ -14073,7 +14073,7 @@
         <v>PASS</v>
       </c>
       <c r="I321" s="8">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="J321" s="8">
         <v>1</v>
@@ -14114,7 +14114,7 @@
         <v>PASS</v>
       </c>
       <c r="I322" s="8">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="J322" s="8">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>PASS</v>
       </c>
       <c r="I323" s="8">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="J323" s="8">
         <v>1</v>
@@ -14196,7 +14196,7 @@
         <v>PASS</v>
       </c>
       <c r="I324" s="8">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="J324" s="8">
         <v>1</v>
@@ -14237,7 +14237,7 @@
         <v>PASS</v>
       </c>
       <c r="I325" s="8">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="J325" s="8">
         <v>1</v>
@@ -14278,7 +14278,7 @@
         <v>PASS</v>
       </c>
       <c r="I326" s="8">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="J326" s="8">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         <v>PASS</v>
       </c>
       <c r="I327" s="8">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="J327" s="8">
         <v>1</v>
@@ -14360,7 +14360,7 @@
         <v>PASS</v>
       </c>
       <c r="I328" s="8">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="J328" s="8">
         <v>1</v>
@@ -14401,7 +14401,7 @@
         <v>PASS</v>
       </c>
       <c r="I329" s="8">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
       <c r="J329" s="8">
         <v>1</v>
@@ -14442,7 +14442,7 @@
         <v>PASS</v>
       </c>
       <c r="I330" s="8">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="J330" s="8">
         <v>1</v>
@@ -14514,7 +14514,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="8">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="3">
@@ -14534,7 +14534,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="8">
-        <v>0.009</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="4">
@@ -14554,7 +14554,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="8">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="5">
@@ -14574,7 +14574,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="8">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="6">
@@ -14594,7 +14594,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="8">
-        <v>0.029</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="7">
@@ -14614,7 +14614,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="8">
-        <v>0.739</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="8">
@@ -14634,7 +14634,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="8">
-        <v>0.014</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="9">
@@ -14654,7 +14654,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="8">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="10">
@@ -14674,7 +14674,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="8">
-        <v>0.059</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="11">
@@ -14694,7 +14694,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="8">
-        <v>0.006</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="12">
@@ -14714,7 +14714,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="8">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -22451,7 +22451,7 @@
         <v>GITHUB_RUN_ID</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>40362633560</v>
+        <v>40364302150</v>
       </c>
     </row>
     <row r="11">

--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <v>Generated: 26/10/2026, 10:30:18 pm IST</v>
+        <v>Generated: 26/10/2026, 10:32:06 pm IST</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         <v>Commit</v>
       </c>
       <c r="B8" s="8" t="str">
-        <v>41454daad15a94ce5eaca991b54b523052b296ff</v>
+        <v>581c970de9af2d7e09f13baaa13080e887b56f2a</v>
       </c>
     </row>
     <row r="9">
@@ -585,7 +585,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40364302150</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40364632127</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B14" s="8">
-        <v>44.54</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
         <v>Flaky (passed on retry)</v>
       </c>
       <c r="B21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1035,7 +1035,7 @@
         <v>PASS</v>
       </c>
       <c r="I3" s="8">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="J3" s="8">
         <v>1</v>
@@ -1076,7 +1076,7 @@
         <v>PASS</v>
       </c>
       <c r="I4" s="8">
-        <v>0.08</v>
+        <v>0.011</v>
       </c>
       <c r="J4" s="8">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>PASS</v>
       </c>
       <c r="I5" s="8">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
@@ -1199,7 +1199,7 @@
         <v>PASS</v>
       </c>
       <c r="I7" s="8">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
@@ -1240,7 +1240,7 @@
         <v>PASS</v>
       </c>
       <c r="I8" s="8">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1281,7 +1281,7 @@
         <v>PASS</v>
       </c>
       <c r="I9" s="8">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>PASS</v>
       </c>
       <c r="I10" s="8">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1363,7 +1363,7 @@
         <v>PASS</v>
       </c>
       <c r="I11" s="8">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -1404,7 +1404,7 @@
         <v>PASS</v>
       </c>
       <c r="I12" s="8">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>PASS</v>
       </c>
       <c r="I13" s="8">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>PASS</v>
       </c>
       <c r="I14" s="8">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>PASS</v>
       </c>
       <c r="I15" s="8">
-        <v>0.025</v>
+        <v>0.032</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
@@ -1568,7 +1568,7 @@
         <v>PASS</v>
       </c>
       <c r="I16" s="8">
-        <v>0.035</v>
+        <v>0.011</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1609,7 +1609,7 @@
         <v>PASS</v>
       </c>
       <c r="I17" s="8">
-        <v>0.048</v>
+        <v>0.01</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>PASS</v>
       </c>
       <c r="I18" s="8">
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>PASS</v>
       </c>
       <c r="I19" s="8">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>PASS</v>
       </c>
       <c r="I20" s="8">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         <v>PASS</v>
       </c>
       <c r="I21" s="8">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>PASS</v>
       </c>
       <c r="I22" s="8">
-        <v>0.069</v>
+        <v>0.004</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         <v>PASS</v>
       </c>
       <c r="I23" s="8">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
@@ -1896,7 +1896,7 @@
         <v>PASS</v>
       </c>
       <c r="I24" s="8">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -1937,7 +1937,7 @@
         <v>PASS</v>
       </c>
       <c r="I25" s="8">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>PASS</v>
       </c>
       <c r="I26" s="8">
-        <v>0.029</v>
+        <v>0.002</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2019,7 +2019,7 @@
         <v>PASS</v>
       </c>
       <c r="I27" s="8">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         <v>PASS</v>
       </c>
       <c r="I28" s="8">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="J28" s="8">
         <v>1</v>
@@ -2101,7 +2101,7 @@
         <v>PASS</v>
       </c>
       <c r="I29" s="8">
-        <v>0.047</v>
+        <v>0.003</v>
       </c>
       <c r="J29" s="8">
         <v>1</v>
@@ -2142,7 +2142,7 @@
         <v>PASS</v>
       </c>
       <c r="I30" s="8">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="J30" s="8">
         <v>1</v>
@@ -2183,7 +2183,7 @@
         <v>PASS</v>
       </c>
       <c r="I31" s="8">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>PASS</v>
       </c>
       <c r="I32" s="8">
-        <v>0.051</v>
+        <v>0.021</v>
       </c>
       <c r="J32" s="8">
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>PASS</v>
       </c>
       <c r="I33" s="8">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="J33" s="8">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>PASS</v>
       </c>
       <c r="I34" s="8">
-        <v>0.005</v>
+        <v>0.065</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2347,7 +2347,7 @@
         <v>PASS</v>
       </c>
       <c r="I35" s="8">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J35" s="8">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>PASS</v>
       </c>
       <c r="I36" s="8">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2429,7 +2429,7 @@
         <v>PASS</v>
       </c>
       <c r="I37" s="8">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="J37" s="8">
         <v>1</v>
@@ -2470,7 +2470,7 @@
         <v>PASS</v>
       </c>
       <c r="I38" s="8">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="J38" s="8">
         <v>1</v>
@@ -2511,7 +2511,7 @@
         <v>PASS</v>
       </c>
       <c r="I39" s="8">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="J39" s="8">
         <v>1</v>
@@ -2552,7 +2552,7 @@
         <v>PASS</v>
       </c>
       <c r="I40" s="8">
-        <v>0.046</v>
+        <v>0.003</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2593,7 +2593,7 @@
         <v>PASS</v>
       </c>
       <c r="I41" s="8">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="J41" s="8">
         <v>1</v>
@@ -2634,7 +2634,7 @@
         <v>PASS</v>
       </c>
       <c r="I42" s="8">
-        <v>0.04</v>
+        <v>0.034</v>
       </c>
       <c r="J42" s="8">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>PASS</v>
       </c>
       <c r="I43" s="8">
-        <v>0.009</v>
+        <v>0.031</v>
       </c>
       <c r="J43" s="8">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>PASS</v>
       </c>
       <c r="I44" s="8">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="J44" s="8">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>PASS</v>
       </c>
       <c r="I45" s="8">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
       <c r="J45" s="8">
         <v>1</v>
@@ -2798,7 +2798,7 @@
         <v>PASS</v>
       </c>
       <c r="I46" s="8">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="J46" s="8">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>PASS</v>
       </c>
       <c r="I47" s="8">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="J47" s="8">
         <v>1</v>
@@ -2880,7 +2880,7 @@
         <v>PASS</v>
       </c>
       <c r="I48" s="8">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="J48" s="8">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>PASS</v>
       </c>
       <c r="I49" s="8">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>PASS</v>
       </c>
       <c r="I50" s="8">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="J50" s="8">
         <v>1</v>
@@ -3003,7 +3003,7 @@
         <v>PASS</v>
       </c>
       <c r="I51" s="8">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J51" s="8">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>PASS</v>
       </c>
       <c r="I52" s="8">
-        <v>0.027</v>
+        <v>0.051</v>
       </c>
       <c r="J52" s="8">
         <v>1</v>
@@ -3085,7 +3085,7 @@
         <v>PASS</v>
       </c>
       <c r="I53" s="8">
-        <v>0.028</v>
+        <v>0.048</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>PASS</v>
       </c>
       <c r="I54" s="8">
-        <v>0.016</v>
+        <v>0.041</v>
       </c>
       <c r="J54" s="8">
         <v>1</v>
@@ -3167,7 +3167,7 @@
         <v>PASS</v>
       </c>
       <c r="I55" s="8">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="J55" s="8">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>PASS</v>
       </c>
       <c r="I56" s="8">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J56" s="8">
         <v>1</v>
@@ -3249,7 +3249,7 @@
         <v>PASS</v>
       </c>
       <c r="I57" s="8">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J57" s="8">
         <v>1</v>
@@ -3290,7 +3290,7 @@
         <v>PASS</v>
       </c>
       <c r="I58" s="8">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J58" s="8">
         <v>1</v>
@@ -3331,7 +3331,7 @@
         <v>PASS</v>
       </c>
       <c r="I59" s="8">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="J59" s="8">
         <v>1</v>
@@ -3372,7 +3372,7 @@
         <v>PASS</v>
       </c>
       <c r="I60" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J60" s="8">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>PASS</v>
       </c>
       <c r="I61" s="8">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="J61" s="8">
         <v>1</v>
@@ -3454,7 +3454,7 @@
         <v>PASS</v>
       </c>
       <c r="I62" s="8">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="J62" s="8">
         <v>1</v>
@@ -3495,7 +3495,7 @@
         <v>PASS</v>
       </c>
       <c r="I63" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J63" s="8">
         <v>1</v>
@@ -3536,7 +3536,7 @@
         <v>PASS</v>
       </c>
       <c r="I64" s="8">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="J64" s="8">
         <v>1</v>
@@ -3577,7 +3577,7 @@
         <v>PASS</v>
       </c>
       <c r="I65" s="8">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="J65" s="8">
         <v>1</v>
@@ -3618,7 +3618,7 @@
         <v>PASS</v>
       </c>
       <c r="I66" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J66" s="8">
         <v>1</v>
@@ -3659,7 +3659,7 @@
         <v>PASS</v>
       </c>
       <c r="I67" s="8">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J67" s="8">
         <v>1</v>
@@ -3700,7 +3700,7 @@
         <v>PASS</v>
       </c>
       <c r="I68" s="8">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="J68" s="8">
         <v>1</v>
@@ -3741,7 +3741,7 @@
         <v>PASS</v>
       </c>
       <c r="I69" s="8">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="J69" s="8">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>PASS</v>
       </c>
       <c r="I70" s="8">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="J70" s="8">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>PASS</v>
       </c>
       <c r="I71" s="8">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="J71" s="8">
         <v>1</v>
@@ -3864,7 +3864,7 @@
         <v>PASS</v>
       </c>
       <c r="I72" s="8">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="J72" s="8">
         <v>1</v>
@@ -3905,7 +3905,7 @@
         <v>PASS</v>
       </c>
       <c r="I73" s="8">
-        <v>0.074</v>
+        <v>0.031</v>
       </c>
       <c r="J73" s="8">
         <v>1</v>
@@ -3946,7 +3946,7 @@
         <v>PASS</v>
       </c>
       <c r="I74" s="8">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="J74" s="8">
         <v>1</v>
@@ -3987,7 +3987,7 @@
         <v>PASS</v>
       </c>
       <c r="I75" s="8">
-        <v>0.044</v>
+        <v>0.016</v>
       </c>
       <c r="J75" s="8">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>PASS</v>
       </c>
       <c r="I76" s="8">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="J76" s="8">
         <v>1</v>
@@ -4069,7 +4069,7 @@
         <v>PASS</v>
       </c>
       <c r="I77" s="8">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="J77" s="8">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>PASS</v>
       </c>
       <c r="I78" s="8">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="J78" s="8">
         <v>1</v>
@@ -4151,7 +4151,7 @@
         <v>PASS</v>
       </c>
       <c r="I79" s="8">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="J79" s="8">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         <v>PASS</v>
       </c>
       <c r="I80" s="8">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J80" s="8">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>PASS</v>
       </c>
       <c r="I81" s="8">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="J81" s="8">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>PASS</v>
       </c>
       <c r="I82" s="8">
-        <v>0.033</v>
+        <v>0.007</v>
       </c>
       <c r="J82" s="8">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>PASS</v>
       </c>
       <c r="I83" s="8">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="J83" s="8">
         <v>1</v>
@@ -4356,7 +4356,7 @@
         <v>PASS</v>
       </c>
       <c r="I84" s="8">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="J84" s="8">
         <v>1</v>
@@ -4397,7 +4397,7 @@
         <v>PASS</v>
       </c>
       <c r="I85" s="8">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J85" s="8">
         <v>1</v>
@@ -4438,7 +4438,7 @@
         <v>PASS</v>
       </c>
       <c r="I86" s="8">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="J86" s="8">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>PASS</v>
       </c>
       <c r="I87" s="8">
-        <v>0.027</v>
+        <v>0.004</v>
       </c>
       <c r="J87" s="8">
         <v>1</v>
@@ -4520,7 +4520,7 @@
         <v>PASS</v>
       </c>
       <c r="I88" s="8">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="J88" s="8">
         <v>1</v>
@@ -4561,7 +4561,7 @@
         <v>PASS</v>
       </c>
       <c r="I89" s="8">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="J89" s="8">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>PASS</v>
       </c>
       <c r="I90" s="8">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="J90" s="8">
         <v>1</v>
@@ -4643,7 +4643,7 @@
         <v>PASS</v>
       </c>
       <c r="I91" s="8">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="J91" s="8">
         <v>1</v>
@@ -4684,7 +4684,7 @@
         <v>PASS</v>
       </c>
       <c r="I92" s="8">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="J92" s="8">
         <v>1</v>
@@ -4725,7 +4725,7 @@
         <v>PASS</v>
       </c>
       <c r="I93" s="8">
-        <v>0.05</v>
+        <v>0.014</v>
       </c>
       <c r="J93" s="8">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>PASS</v>
       </c>
       <c r="I94" s="8">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="J94" s="8">
         <v>1</v>
@@ -4807,7 +4807,7 @@
         <v>PASS</v>
       </c>
       <c r="I95" s="8">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="J95" s="8">
         <v>1</v>
@@ -4848,7 +4848,7 @@
         <v>PASS</v>
       </c>
       <c r="I96" s="8">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="J96" s="8">
         <v>1</v>
@@ -4889,7 +4889,7 @@
         <v>PASS</v>
       </c>
       <c r="I97" s="8">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="J97" s="8">
         <v>1</v>
@@ -4930,7 +4930,7 @@
         <v>PASS</v>
       </c>
       <c r="I98" s="8">
-        <v>0.004</v>
+        <v>0.025</v>
       </c>
       <c r="J98" s="8">
         <v>1</v>
@@ -4971,7 +4971,7 @@
         <v>PASS</v>
       </c>
       <c r="I99" s="8">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="J99" s="8">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>PASS</v>
       </c>
       <c r="I100" s="8">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="J100" s="8">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>PASS</v>
       </c>
       <c r="I101" s="8">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="J101" s="8">
         <v>1</v>
@@ -5094,7 +5094,7 @@
         <v>PASS</v>
       </c>
       <c r="I102" s="8">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J102" s="8">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         <v>PASS</v>
       </c>
       <c r="I103" s="8">
-        <v>0.05</v>
+        <v>0.012</v>
       </c>
       <c r="J103" s="8">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>PASS</v>
       </c>
       <c r="I104" s="8">
-        <v>0.047</v>
+        <v>0.015</v>
       </c>
       <c r="J104" s="8">
         <v>1</v>
@@ -5217,7 +5217,7 @@
         <v>PASS</v>
       </c>
       <c r="I105" s="8">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="J105" s="8">
         <v>1</v>
@@ -5258,7 +5258,7 @@
         <v>PASS</v>
       </c>
       <c r="I106" s="8">
-        <v>0.028</v>
+        <v>0.016</v>
       </c>
       <c r="J106" s="8">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         <v>PASS</v>
       </c>
       <c r="I107" s="8">
-        <v>0.028</v>
+        <v>0.005</v>
       </c>
       <c r="J107" s="8">
         <v>1</v>
@@ -5340,7 +5340,7 @@
         <v>PASS</v>
       </c>
       <c r="I108" s="8">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="J108" s="8">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>PASS</v>
       </c>
       <c r="I109" s="8">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J109" s="8">
         <v>1</v>
@@ -5422,7 +5422,7 @@
         <v>PASS</v>
       </c>
       <c r="I110" s="8">
-        <v>0.043</v>
+        <v>0.012</v>
       </c>
       <c r="J110" s="8">
         <v>1</v>
@@ -5463,7 +5463,7 @@
         <v>PASS</v>
       </c>
       <c r="I111" s="8">
-        <v>0.035</v>
+        <v>0.018</v>
       </c>
       <c r="J111" s="8">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>PASS</v>
       </c>
       <c r="I112" s="8">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="J112" s="8">
         <v>1</v>
@@ -5545,7 +5545,7 @@
         <v>PASS</v>
       </c>
       <c r="I113" s="8">
-        <v>0.063</v>
+        <v>0.016</v>
       </c>
       <c r="J113" s="8">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         <v>PASS</v>
       </c>
       <c r="I114" s="8">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="J114" s="8">
         <v>1</v>
@@ -5627,7 +5627,7 @@
         <v>PASS</v>
       </c>
       <c r="I115" s="8">
-        <v>0.017</v>
+        <v>0.075</v>
       </c>
       <c r="J115" s="8">
         <v>1</v>
@@ -5668,7 +5668,7 @@
         <v>PASS</v>
       </c>
       <c r="I116" s="8">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="J116" s="8">
         <v>1</v>
@@ -5709,7 +5709,7 @@
         <v>PASS</v>
       </c>
       <c r="I117" s="8">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="J117" s="8">
         <v>1</v>
@@ -5750,7 +5750,7 @@
         <v>PASS</v>
       </c>
       <c r="I118" s="8">
-        <v>0.081</v>
+        <v>0.033</v>
       </c>
       <c r="J118" s="8">
         <v>1</v>
@@ -5791,7 +5791,7 @@
         <v>PASS</v>
       </c>
       <c r="I119" s="8">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="J119" s="8">
         <v>1</v>
@@ -5832,7 +5832,7 @@
         <v>PASS</v>
       </c>
       <c r="I120" s="8">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="J120" s="8">
         <v>1</v>
@@ -5873,7 +5873,7 @@
         <v>PASS</v>
       </c>
       <c r="I121" s="8">
-        <v>0.033</v>
+        <v>0.017</v>
       </c>
       <c r="J121" s="8">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>PASS</v>
       </c>
       <c r="I122" s="8">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J122" s="8">
         <v>1</v>
@@ -5955,7 +5955,7 @@
         <v>PASS</v>
       </c>
       <c r="I123" s="8">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="J123" s="8">
         <v>1</v>
@@ -5996,7 +5996,7 @@
         <v>PASS</v>
       </c>
       <c r="I124" s="8">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="J124" s="8">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         <v>PASS</v>
       </c>
       <c r="I126" s="8">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="J126" s="8">
         <v>1</v>
@@ -6119,7 +6119,7 @@
         <v>PASS</v>
       </c>
       <c r="I127" s="8">
-        <v>0.014</v>
+        <v>0.102</v>
       </c>
       <c r="J127" s="8">
         <v>1</v>
@@ -6160,7 +6160,7 @@
         <v>PASS</v>
       </c>
       <c r="I128" s="8">
-        <v>0.056</v>
+        <v>0.034</v>
       </c>
       <c r="J128" s="8">
         <v>1</v>
@@ -6201,7 +6201,7 @@
         <v>PASS</v>
       </c>
       <c r="I129" s="8">
-        <v>0.016</v>
+        <v>0.031</v>
       </c>
       <c r="J129" s="8">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         <v>PASS</v>
       </c>
       <c r="I130" s="8">
-        <v>0.016</v>
+        <v>0.031</v>
       </c>
       <c r="J130" s="8">
         <v>1</v>
@@ -6283,7 +6283,7 @@
         <v>PASS</v>
       </c>
       <c r="I131" s="8">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="J131" s="8">
         <v>1</v>
@@ -6324,7 +6324,7 @@
         <v>PASS</v>
       </c>
       <c r="I132" s="8">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="J132" s="8">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         <v>PASS</v>
       </c>
       <c r="I133" s="8">
-        <v>0.048</v>
+        <v>0.07</v>
       </c>
       <c r="J133" s="8">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>PASS</v>
       </c>
       <c r="I134" s="8">
-        <v>0.094</v>
+        <v>0.07</v>
       </c>
       <c r="J134" s="8">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>PASS</v>
       </c>
       <c r="I135" s="8">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="J135" s="8">
         <v>1</v>
@@ -6488,7 +6488,7 @@
         <v>PASS</v>
       </c>
       <c r="I136" s="8">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="J136" s="8">
         <v>1</v>
@@ -6529,7 +6529,7 @@
         <v>PASS</v>
       </c>
       <c r="I137" s="8">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="J137" s="8">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>PASS</v>
       </c>
       <c r="I138" s="8">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="J138" s="8">
         <v>1</v>
@@ -6611,7 +6611,7 @@
         <v>PASS</v>
       </c>
       <c r="I139" s="8">
-        <v>0.041</v>
+        <v>0.009</v>
       </c>
       <c r="J139" s="8">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>PASS</v>
       </c>
       <c r="I140" s="8">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="J140" s="8">
         <v>1</v>
@@ -6693,7 +6693,7 @@
         <v>PASS</v>
       </c>
       <c r="I141" s="8">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="J141" s="8">
         <v>1</v>
@@ -6734,7 +6734,7 @@
         <v>PASS</v>
       </c>
       <c r="I142" s="8">
-        <v>0.062</v>
+        <v>0.034</v>
       </c>
       <c r="J142" s="8">
         <v>1</v>
@@ -6775,7 +6775,7 @@
         <v>PASS</v>
       </c>
       <c r="I143" s="8">
-        <v>0.105</v>
+        <v>0.015</v>
       </c>
       <c r="J143" s="8">
         <v>1</v>
@@ -6816,7 +6816,7 @@
         <v>PASS</v>
       </c>
       <c r="I144" s="8">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="J144" s="8">
         <v>1</v>
@@ -6857,7 +6857,7 @@
         <v>PASS</v>
       </c>
       <c r="I145" s="8">
-        <v>0.056</v>
+        <v>0.008</v>
       </c>
       <c r="J145" s="8">
         <v>1</v>
@@ -6898,7 +6898,7 @@
         <v>PASS</v>
       </c>
       <c r="I146" s="8">
-        <v>0.07</v>
+        <v>0.015</v>
       </c>
       <c r="J146" s="8">
         <v>1</v>
@@ -6939,7 +6939,7 @@
         <v>PASS</v>
       </c>
       <c r="I147" s="8">
-        <v>0.048</v>
+        <v>0.028</v>
       </c>
       <c r="J147" s="8">
         <v>1</v>
@@ -6980,7 +6980,7 @@
         <v>PASS</v>
       </c>
       <c r="I148" s="8">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="J148" s="8">
         <v>1</v>
@@ -7021,7 +7021,7 @@
         <v>PASS</v>
       </c>
       <c r="I149" s="8">
-        <v>0.042</v>
+        <v>0.035</v>
       </c>
       <c r="J149" s="8">
         <v>1</v>
@@ -7062,7 +7062,7 @@
         <v>PASS</v>
       </c>
       <c r="I150" s="8">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="J150" s="8">
         <v>1</v>
@@ -7103,7 +7103,7 @@
         <v>PASS</v>
       </c>
       <c r="I151" s="8">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="J151" s="8">
         <v>1</v>
@@ -7144,7 +7144,7 @@
         <v>PASS</v>
       </c>
       <c r="I152" s="8">
-        <v>0.016</v>
+        <v>0.041</v>
       </c>
       <c r="J152" s="8">
         <v>1</v>
@@ -7185,7 +7185,7 @@
         <v>PASS</v>
       </c>
       <c r="I153" s="8">
-        <v>0.638</v>
+        <v>0.02</v>
       </c>
       <c r="J153" s="8">
         <v>1</v>
@@ -7226,7 +7226,7 @@
         <v>PASS</v>
       </c>
       <c r="I154" s="8">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="J154" s="8">
         <v>1</v>
@@ -7267,7 +7267,7 @@
         <v>PASS</v>
       </c>
       <c r="I155" s="8">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
       <c r="J155" s="8">
         <v>1</v>
@@ -7308,7 +7308,7 @@
         <v>PASS</v>
       </c>
       <c r="I156" s="8">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="J156" s="8">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>PASS</v>
       </c>
       <c r="I157" s="8">
-        <v>0.045</v>
+        <v>0.02</v>
       </c>
       <c r="J157" s="8">
         <v>1</v>
@@ -7390,7 +7390,7 @@
         <v>PASS</v>
       </c>
       <c r="I158" s="8">
-        <v>0.09</v>
+        <v>0.038</v>
       </c>
       <c r="J158" s="8">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         <v>PASS</v>
       </c>
       <c r="I159" s="8">
-        <v>0.205</v>
+        <v>0.02</v>
       </c>
       <c r="J159" s="8">
         <v>1</v>
@@ -7472,7 +7472,7 @@
         <v>PASS</v>
       </c>
       <c r="I160" s="8">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="J160" s="8">
         <v>1</v>
@@ -7513,7 +7513,7 @@
         <v>PASS</v>
       </c>
       <c r="I161" s="8">
-        <v>0.012</v>
+        <v>0.04</v>
       </c>
       <c r="J161" s="8">
         <v>1</v>
@@ -7554,7 +7554,7 @@
         <v>PASS</v>
       </c>
       <c r="I162" s="8">
-        <v>0.011</v>
+        <v>0.041</v>
       </c>
       <c r="J162" s="8">
         <v>1</v>
@@ -7595,7 +7595,7 @@
         <v>PASS</v>
       </c>
       <c r="I163" s="8">
-        <v>0.343</v>
+        <v>0.021</v>
       </c>
       <c r="J163" s="8">
         <v>1</v>
@@ -7636,7 +7636,7 @@
         <v>PASS</v>
       </c>
       <c r="I164" s="8">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="J164" s="8">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>PASS</v>
       </c>
       <c r="I165" s="8">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="J165" s="8">
         <v>1</v>
@@ -7718,7 +7718,7 @@
         <v>PASS</v>
       </c>
       <c r="I166" s="8">
-        <v>0.045</v>
+        <v>0.018</v>
       </c>
       <c r="J166" s="8">
         <v>1</v>
@@ -7759,7 +7759,7 @@
         <v>PASS</v>
       </c>
       <c r="I167" s="8">
-        <v>0.037</v>
+        <v>0.008</v>
       </c>
       <c r="J167" s="8">
         <v>1</v>
@@ -7800,7 +7800,7 @@
         <v>PASS</v>
       </c>
       <c r="I168" s="8">
-        <v>0.054</v>
+        <v>0.018</v>
       </c>
       <c r="J168" s="8">
         <v>1</v>
@@ -7841,7 +7841,7 @@
         <v>PASS</v>
       </c>
       <c r="I169" s="8">
-        <v>0.031</v>
+        <v>0.014</v>
       </c>
       <c r="J169" s="8">
         <v>1</v>
@@ -7882,7 +7882,7 @@
         <v>PASS</v>
       </c>
       <c r="I170" s="8">
-        <v>0.047</v>
+        <v>0.004</v>
       </c>
       <c r="J170" s="8">
         <v>1</v>
@@ -7923,7 +7923,7 @@
         <v>PASS</v>
       </c>
       <c r="I171" s="8">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J171" s="8">
         <v>1</v>
@@ -7964,7 +7964,7 @@
         <v>PASS</v>
       </c>
       <c r="I172" s="8">
-        <v>0.036</v>
+        <v>0.017</v>
       </c>
       <c r="J172" s="8">
         <v>1</v>
@@ -8005,7 +8005,7 @@
         <v>PASS</v>
       </c>
       <c r="I173" s="8">
-        <v>0.01</v>
+        <v>0.082</v>
       </c>
       <c r="J173" s="8">
         <v>1</v>
@@ -8046,7 +8046,7 @@
         <v>PASS</v>
       </c>
       <c r="I174" s="8">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="J174" s="8">
         <v>1</v>
@@ -8087,7 +8087,7 @@
         <v>PASS</v>
       </c>
       <c r="I175" s="8">
-        <v>0.05</v>
+        <v>0.029</v>
       </c>
       <c r="J175" s="8">
         <v>1</v>
@@ -8128,7 +8128,7 @@
         <v>PASS</v>
       </c>
       <c r="I176" s="8">
-        <v>0.015</v>
+        <v>0.024</v>
       </c>
       <c r="J176" s="8">
         <v>1</v>
@@ -8169,7 +8169,7 @@
         <v>PASS</v>
       </c>
       <c r="I177" s="8">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="J177" s="8">
         <v>1</v>
@@ -8210,7 +8210,7 @@
         <v>PASS</v>
       </c>
       <c r="I178" s="8">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="J178" s="8">
         <v>1</v>
@@ -8251,7 +8251,7 @@
         <v>PASS</v>
       </c>
       <c r="I179" s="8">
-        <v>0.013</v>
+        <v>0.033</v>
       </c>
       <c r="J179" s="8">
         <v>1</v>
@@ -8292,7 +8292,7 @@
         <v>PASS</v>
       </c>
       <c r="I180" s="8">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J180" s="8">
         <v>1</v>
@@ -8333,7 +8333,7 @@
         <v>PASS</v>
       </c>
       <c r="I181" s="8">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="J181" s="8">
         <v>1</v>
@@ -8374,7 +8374,7 @@
         <v>PASS</v>
       </c>
       <c r="I182" s="8">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="J182" s="8">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         <v>PASS</v>
       </c>
       <c r="I183" s="8">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="J183" s="8">
         <v>1</v>
@@ -8456,7 +8456,7 @@
         <v>PASS</v>
       </c>
       <c r="I184" s="8">
-        <v>0.621</v>
+        <v>0.497</v>
       </c>
       <c r="J184" s="8">
         <v>1</v>
@@ -8497,7 +8497,7 @@
         <v>PASS</v>
       </c>
       <c r="I185" s="8">
-        <v>0.928</v>
+        <v>0.867</v>
       </c>
       <c r="J185" s="8">
         <v>1</v>
@@ -8538,7 +8538,7 @@
         <v>PASS</v>
       </c>
       <c r="I186" s="8">
-        <v>0.963</v>
+        <v>0.97</v>
       </c>
       <c r="J186" s="8">
         <v>1</v>
@@ -8579,7 +8579,7 @@
         <v>PASS</v>
       </c>
       <c r="I187" s="8">
-        <v>0.536</v>
+        <v>0.503</v>
       </c>
       <c r="J187" s="8">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>PASS</v>
       </c>
       <c r="I188" s="8">
-        <v>0.829</v>
+        <v>0.813</v>
       </c>
       <c r="J188" s="8">
         <v>1</v>
@@ -8661,7 +8661,7 @@
         <v>PASS</v>
       </c>
       <c r="I189" s="8">
-        <v>1.485</v>
+        <v>0.965</v>
       </c>
       <c r="J189" s="8">
         <v>1</v>
@@ -8702,7 +8702,7 @@
         <v>PASS</v>
       </c>
       <c r="I190" s="8">
-        <v>1.106</v>
+        <v>0.821</v>
       </c>
       <c r="J190" s="8">
         <v>1</v>
@@ -8743,7 +8743,7 @@
         <v>PASS</v>
       </c>
       <c r="I191" s="8">
-        <v>1.71</v>
+        <v>1.195</v>
       </c>
       <c r="J191" s="8">
         <v>1</v>
@@ -8784,7 +8784,7 @@
         <v>PASS</v>
       </c>
       <c r="I192" s="8">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="J192" s="8">
         <v>1</v>
@@ -8825,7 +8825,7 @@
         <v>PASS</v>
       </c>
       <c r="I193" s="8">
-        <v>0.058</v>
+        <v>0.03</v>
       </c>
       <c r="J193" s="8">
         <v>1</v>
@@ -8866,7 +8866,7 @@
         <v>PASS</v>
       </c>
       <c r="I194" s="8">
-        <v>0.073</v>
+        <v>0.013</v>
       </c>
       <c r="J194" s="8">
         <v>1</v>
@@ -8907,7 +8907,7 @@
         <v>PASS</v>
       </c>
       <c r="I195" s="8">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J195" s="8">
         <v>1</v>
@@ -8948,13 +8948,13 @@
         <v>PASS</v>
       </c>
       <c r="I196" s="8">
-        <v>0.019</v>
+        <v>2.135</v>
       </c>
       <c r="J196" s="8">
-        <v>1</v>
-      </c>
-      <c r="K196" s="8" t="str">
-        <v>no</v>
+        <v>2</v>
+      </c>
+      <c r="K196" s="10" t="str">
+        <v>yes</v>
       </c>
       <c r="L196" s="8" t="str">
         <v/>
@@ -8989,7 +8989,7 @@
         <v>PASS</v>
       </c>
       <c r="I197" s="8">
-        <v>1.534</v>
+        <v>0.976</v>
       </c>
       <c r="J197" s="8">
         <v>1</v>
@@ -9030,7 +9030,7 @@
         <v>PASS</v>
       </c>
       <c r="I198" s="8">
-        <v>1.288</v>
+        <v>1.379</v>
       </c>
       <c r="J198" s="8">
         <v>1</v>
@@ -9071,7 +9071,7 @@
         <v>PASS</v>
       </c>
       <c r="I199" s="8">
-        <v>1.861</v>
+        <v>1.711</v>
       </c>
       <c r="J199" s="8">
         <v>1</v>
@@ -9112,7 +9112,7 @@
         <v>PASS</v>
       </c>
       <c r="I200" s="8">
-        <v>1.53</v>
+        <v>1.392</v>
       </c>
       <c r="J200" s="8">
         <v>1</v>
@@ -9153,7 +9153,7 @@
         <v>PASS</v>
       </c>
       <c r="I201" s="8">
-        <v>2.207</v>
+        <v>1.893</v>
       </c>
       <c r="J201" s="8">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>PASS</v>
       </c>
       <c r="I202" s="8">
-        <v>1.949</v>
+        <v>1.766</v>
       </c>
       <c r="J202" s="8">
         <v>1</v>
@@ -9235,7 +9235,7 @@
         <v>PASS</v>
       </c>
       <c r="I203" s="8">
-        <v>0.819</v>
+        <v>0.765</v>
       </c>
       <c r="J203" s="8">
         <v>1</v>
@@ -9276,7 +9276,7 @@
         <v>PASS</v>
       </c>
       <c r="I204" s="8">
-        <v>0.091</v>
+        <v>0.12</v>
       </c>
       <c r="J204" s="8">
         <v>1</v>
@@ -9317,7 +9317,7 @@
         <v>PASS</v>
       </c>
       <c r="I205" s="8">
-        <v>0.051</v>
+        <v>0.033</v>
       </c>
       <c r="J205" s="8">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         <v>PASS</v>
       </c>
       <c r="I206" s="8">
-        <v>0.051</v>
+        <v>0.029</v>
       </c>
       <c r="J206" s="8">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         <v>PASS</v>
       </c>
       <c r="I207" s="8">
-        <v>0.061</v>
+        <v>0.028</v>
       </c>
       <c r="J207" s="8">
         <v>1</v>
@@ -9440,7 +9440,7 @@
         <v>PASS</v>
       </c>
       <c r="I208" s="8">
-        <v>0.146</v>
+        <v>0.033</v>
       </c>
       <c r="J208" s="8">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>PASS</v>
       </c>
       <c r="I209" s="8">
-        <v>0.037</v>
+        <v>0.025</v>
       </c>
       <c r="J209" s="8">
         <v>1</v>
@@ -9522,7 +9522,7 @@
         <v>PASS</v>
       </c>
       <c r="I210" s="8">
-        <v>0.099</v>
+        <v>0.061</v>
       </c>
       <c r="J210" s="8">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>PASS</v>
       </c>
       <c r="I211" s="8">
-        <v>1.427</v>
+        <v>1.159</v>
       </c>
       <c r="J211" s="8">
         <v>1</v>
@@ -9604,7 +9604,7 @@
         <v>PASS</v>
       </c>
       <c r="I212" s="8">
-        <v>1.022</v>
+        <v>0.835</v>
       </c>
       <c r="J212" s="8">
         <v>1</v>
@@ -9645,7 +9645,7 @@
         <v>PASS</v>
       </c>
       <c r="I213" s="8">
-        <v>1.983</v>
+        <v>1.823</v>
       </c>
       <c r="J213" s="8">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         <v>PASS</v>
       </c>
       <c r="I214" s="8">
-        <v>0.017</v>
+        <v>0.122</v>
       </c>
       <c r="J214" s="8">
         <v>1</v>
@@ -9727,7 +9727,7 @@
         <v>PASS</v>
       </c>
       <c r="I215" s="8">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="J215" s="8">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         <v>PASS</v>
       </c>
       <c r="I216" s="8">
-        <v>0.009</v>
+        <v>0.038</v>
       </c>
       <c r="J216" s="8">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         <v>PASS</v>
       </c>
       <c r="I217" s="8">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="J217" s="8">
         <v>1</v>
@@ -9850,7 +9850,7 @@
         <v>PASS</v>
       </c>
       <c r="I218" s="8">
-        <v>0.037</v>
+        <v>0.009</v>
       </c>
       <c r="J218" s="8">
         <v>1</v>
@@ -9891,7 +9891,7 @@
         <v>PASS</v>
       </c>
       <c r="I219" s="8">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="J219" s="8">
         <v>1</v>
@@ -9932,7 +9932,7 @@
         <v>PASS</v>
       </c>
       <c r="I220" s="8">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="J220" s="8">
         <v>1</v>
@@ -9973,7 +9973,7 @@
         <v>PASS</v>
       </c>
       <c r="I221" s="8">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
       <c r="J221" s="8">
         <v>1</v>
@@ -10014,7 +10014,7 @@
         <v>PASS</v>
       </c>
       <c r="I222" s="8">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J222" s="8">
         <v>1</v>
@@ -10055,7 +10055,7 @@
         <v>PASS</v>
       </c>
       <c r="I223" s="8">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J223" s="8">
         <v>1</v>
@@ -10096,7 +10096,7 @@
         <v>PASS</v>
       </c>
       <c r="I224" s="8">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="J224" s="8">
         <v>1</v>
@@ -10137,7 +10137,7 @@
         <v>PASS</v>
       </c>
       <c r="I225" s="8">
-        <v>0.043</v>
+        <v>0.033</v>
       </c>
       <c r="J225" s="8">
         <v>1</v>
@@ -10178,7 +10178,7 @@
         <v>PASS</v>
       </c>
       <c r="I226" s="8">
-        <v>0.039</v>
+        <v>0.017</v>
       </c>
       <c r="J226" s="8">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>PASS</v>
       </c>
       <c r="I227" s="8">
-        <v>0.031</v>
+        <v>0.005</v>
       </c>
       <c r="J227" s="8">
         <v>1</v>
@@ -10260,7 +10260,7 @@
         <v>PASS</v>
       </c>
       <c r="I228" s="8">
-        <v>0.105</v>
+        <v>0.01</v>
       </c>
       <c r="J228" s="8">
         <v>1</v>
@@ -10301,7 +10301,7 @@
         <v>PASS</v>
       </c>
       <c r="I229" s="8">
-        <v>0.047</v>
+        <v>0.012</v>
       </c>
       <c r="J229" s="8">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         <v>PASS</v>
       </c>
       <c r="I230" s="8">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="J230" s="8">
         <v>1</v>
@@ -10383,7 +10383,7 @@
         <v>PASS</v>
       </c>
       <c r="I231" s="8">
-        <v>0.058</v>
+        <v>0.015</v>
       </c>
       <c r="J231" s="8">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         <v>PASS</v>
       </c>
       <c r="I232" s="8">
-        <v>0.111</v>
+        <v>0.019</v>
       </c>
       <c r="J232" s="8">
         <v>1</v>
@@ -10465,7 +10465,7 @@
         <v>PASS</v>
       </c>
       <c r="I233" s="8">
-        <v>0.062</v>
+        <v>0.013</v>
       </c>
       <c r="J233" s="8">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>PASS</v>
       </c>
       <c r="I234" s="8">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="J234" s="8">
         <v>1</v>
@@ -10547,7 +10547,7 @@
         <v>PASS</v>
       </c>
       <c r="I235" s="8">
-        <v>0.01</v>
+        <v>0.066</v>
       </c>
       <c r="J235" s="8">
         <v>1</v>
@@ -10588,7 +10588,7 @@
         <v>PASS</v>
       </c>
       <c r="I236" s="8">
-        <v>0.089</v>
+        <v>0.019</v>
       </c>
       <c r="J236" s="8">
         <v>1</v>
@@ -10629,7 +10629,7 @@
         <v>PASS</v>
       </c>
       <c r="I237" s="8">
-        <v>0.029</v>
+        <v>0.009</v>
       </c>
       <c r="J237" s="8">
         <v>1</v>
@@ -10670,7 +10670,7 @@
         <v>PASS</v>
       </c>
       <c r="I238" s="8">
-        <v>0.029</v>
+        <v>0.004</v>
       </c>
       <c r="J238" s="8">
         <v>1</v>
@@ -10711,7 +10711,7 @@
         <v>PASS</v>
       </c>
       <c r="I239" s="8">
-        <v>0.027</v>
+        <v>0.009</v>
       </c>
       <c r="J239" s="8">
         <v>1</v>
@@ -10752,7 +10752,7 @@
         <v>PASS</v>
       </c>
       <c r="I240" s="8">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="J240" s="8">
         <v>1</v>
@@ -10793,7 +10793,7 @@
         <v>PASS</v>
       </c>
       <c r="I241" s="8">
-        <v>0.028</v>
+        <v>0.006</v>
       </c>
       <c r="J241" s="8">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         <v>PASS</v>
       </c>
       <c r="I242" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J242" s="8">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>PASS</v>
       </c>
       <c r="I243" s="8">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="J243" s="8">
         <v>1</v>
@@ -10916,7 +10916,7 @@
         <v>PASS</v>
       </c>
       <c r="I244" s="8">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J244" s="8">
         <v>1</v>
@@ -10957,7 +10957,7 @@
         <v>PASS</v>
       </c>
       <c r="I245" s="8">
-        <v>0.032</v>
+        <v>0.164</v>
       </c>
       <c r="J245" s="8">
         <v>1</v>
@@ -11039,7 +11039,7 @@
         <v>PASS</v>
       </c>
       <c r="I247" s="8">
-        <v>0.051</v>
+        <v>0.019</v>
       </c>
       <c r="J247" s="8">
         <v>1</v>
@@ -11080,7 +11080,7 @@
         <v>PASS</v>
       </c>
       <c r="I248" s="8">
-        <v>0.049</v>
+        <v>0.033</v>
       </c>
       <c r="J248" s="8">
         <v>1</v>
@@ -11162,7 +11162,7 @@
         <v>PASS</v>
       </c>
       <c r="I250" s="8">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="J250" s="8">
         <v>1</v>
@@ -11203,7 +11203,7 @@
         <v>PASS</v>
       </c>
       <c r="I251" s="8">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="J251" s="8">
         <v>1</v>
@@ -11244,7 +11244,7 @@
         <v>PASS</v>
       </c>
       <c r="I252" s="8">
-        <v>0.013</v>
+        <v>0.021</v>
       </c>
       <c r="J252" s="8">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>PASS</v>
       </c>
       <c r="I253" s="8">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="J253" s="8">
         <v>1</v>
@@ -11326,7 +11326,7 @@
         <v>PASS</v>
       </c>
       <c r="I254" s="8">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="J254" s="8">
         <v>1</v>
@@ -11367,7 +11367,7 @@
         <v>PASS</v>
       </c>
       <c r="I255" s="8">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="J255" s="8">
         <v>1</v>
@@ -11408,7 +11408,7 @@
         <v>PASS</v>
       </c>
       <c r="I256" s="8">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="J256" s="8">
         <v>1</v>
@@ -11449,7 +11449,7 @@
         <v>PASS</v>
       </c>
       <c r="I257" s="8">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="J257" s="8">
         <v>1</v>
@@ -11490,7 +11490,7 @@
         <v>PASS</v>
       </c>
       <c r="I258" s="8">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="J258" s="8">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>PASS</v>
       </c>
       <c r="I259" s="8">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="J259" s="8">
         <v>1</v>
@@ -11572,7 +11572,7 @@
         <v>PASS</v>
       </c>
       <c r="I260" s="8">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="J260" s="8">
         <v>1</v>
@@ -11613,7 +11613,7 @@
         <v>PASS</v>
       </c>
       <c r="I261" s="8">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
       <c r="J261" s="8">
         <v>1</v>
@@ -11654,7 +11654,7 @@
         <v>PASS</v>
       </c>
       <c r="I262" s="8">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="J262" s="8">
         <v>1</v>
@@ -11695,7 +11695,7 @@
         <v>PASS</v>
       </c>
       <c r="I263" s="8">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="J263" s="8">
         <v>1</v>
@@ -11736,7 +11736,7 @@
         <v>PASS</v>
       </c>
       <c r="I264" s="8">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="J264" s="8">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>PASS</v>
       </c>
       <c r="I265" s="8">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="J265" s="8">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>PASS</v>
       </c>
       <c r="I266" s="8">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="J266" s="8">
         <v>1</v>
@@ -11859,7 +11859,7 @@
         <v>PASS</v>
       </c>
       <c r="I267" s="8">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="J267" s="8">
         <v>1</v>
@@ -11900,7 +11900,7 @@
         <v>PASS</v>
       </c>
       <c r="I268" s="8">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="J268" s="8">
         <v>1</v>
@@ -11982,7 +11982,7 @@
         <v>PASS</v>
       </c>
       <c r="I270" s="8">
-        <v>0.018</v>
+        <v>0.067</v>
       </c>
       <c r="J270" s="8">
         <v>1</v>
@@ -12023,7 +12023,7 @@
         <v>PASS</v>
       </c>
       <c r="I271" s="8">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="J271" s="8">
         <v>1</v>
@@ -12064,7 +12064,7 @@
         <v>PASS</v>
       </c>
       <c r="I272" s="8">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="J272" s="8">
         <v>1</v>
@@ -12105,7 +12105,7 @@
         <v>PASS</v>
       </c>
       <c r="I273" s="8">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="J273" s="8">
         <v>1</v>
@@ -12146,7 +12146,7 @@
         <v>PASS</v>
       </c>
       <c r="I274" s="8">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="J274" s="8">
         <v>1</v>
@@ -12187,7 +12187,7 @@
         <v>PASS</v>
       </c>
       <c r="I275" s="8">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="J275" s="8">
         <v>1</v>
@@ -12228,7 +12228,7 @@
         <v>PASS</v>
       </c>
       <c r="I276" s="8">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="J276" s="8">
         <v>1</v>
@@ -12269,7 +12269,7 @@
         <v>PASS</v>
       </c>
       <c r="I277" s="8">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J277" s="8">
         <v>1</v>
@@ -12310,7 +12310,7 @@
         <v>PASS</v>
       </c>
       <c r="I278" s="8">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="J278" s="8">
         <v>1</v>
@@ -12351,7 +12351,7 @@
         <v>PASS</v>
       </c>
       <c r="I279" s="8">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J279" s="8">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         <v>PASS</v>
       </c>
       <c r="I282" s="8">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="J282" s="8">
         <v>1</v>
@@ -12515,7 +12515,7 @@
         <v>PASS</v>
       </c>
       <c r="I283" s="8">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="J283" s="8">
         <v>1</v>
@@ -12556,7 +12556,7 @@
         <v>PASS</v>
       </c>
       <c r="I284" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J284" s="8">
         <v>1</v>
@@ -12597,7 +12597,7 @@
         <v>PASS</v>
       </c>
       <c r="I285" s="8">
-        <v>0.081</v>
+        <v>0.025</v>
       </c>
       <c r="J285" s="8">
         <v>1</v>
@@ -12638,7 +12638,7 @@
         <v>PASS</v>
       </c>
       <c r="I286" s="8">
-        <v>0.009</v>
+        <v>0.071</v>
       </c>
       <c r="J286" s="8">
         <v>1</v>
@@ -12679,7 +12679,7 @@
         <v>PASS</v>
       </c>
       <c r="I287" s="8">
-        <v>0.706</v>
+        <v>0.743</v>
       </c>
       <c r="J287" s="8">
         <v>1</v>
@@ -12720,7 +12720,7 @@
         <v>PASS</v>
       </c>
       <c r="I288" s="8">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="J288" s="8">
         <v>1</v>
@@ -12761,7 +12761,7 @@
         <v>PASS</v>
       </c>
       <c r="I289" s="8">
-        <v>0.098</v>
+        <v>0.025</v>
       </c>
       <c r="J289" s="8">
         <v>1</v>
@@ -12802,7 +12802,7 @@
         <v>PASS</v>
       </c>
       <c r="I290" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J290" s="8">
         <v>1</v>
@@ -12843,7 +12843,7 @@
         <v>PASS</v>
       </c>
       <c r="I291" s="8">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J291" s="8">
         <v>1</v>
@@ -12884,7 +12884,7 @@
         <v>PASS</v>
       </c>
       <c r="I292" s="8">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J292" s="8">
         <v>1</v>
@@ -12925,7 +12925,7 @@
         <v>PASS</v>
       </c>
       <c r="I293" s="8">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J293" s="8">
         <v>1</v>
@@ -12966,7 +12966,7 @@
         <v>PASS</v>
       </c>
       <c r="I294" s="8">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J294" s="8">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>PASS</v>
       </c>
       <c r="I295" s="8">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J295" s="8">
         <v>1</v>
@@ -13089,7 +13089,7 @@
         <v>PASS</v>
       </c>
       <c r="I297" s="8">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J297" s="8">
         <v>1</v>
@@ -13130,7 +13130,7 @@
         <v>PASS</v>
       </c>
       <c r="I298" s="8">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="J298" s="8">
         <v>1</v>
@@ -13171,7 +13171,7 @@
         <v>PASS</v>
       </c>
       <c r="I299" s="8">
-        <v>0.009</v>
+        <v>0.014</v>
       </c>
       <c r="J299" s="8">
         <v>1</v>
@@ -13212,7 +13212,7 @@
         <v>PASS</v>
       </c>
       <c r="I300" s="8">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="J300" s="8">
         <v>1</v>
@@ -13253,7 +13253,7 @@
         <v>PASS</v>
       </c>
       <c r="I301" s="8">
-        <v>0.05</v>
+        <v>0.008</v>
       </c>
       <c r="J301" s="8">
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>PASS</v>
       </c>
       <c r="I302" s="8">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="J302" s="8">
         <v>1</v>
@@ -13335,7 +13335,7 @@
         <v>PASS</v>
       </c>
       <c r="I303" s="8">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="J303" s="8">
         <v>1</v>
@@ -13376,7 +13376,7 @@
         <v>PASS</v>
       </c>
       <c r="I304" s="8">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="J304" s="8">
         <v>1</v>
@@ -13417,7 +13417,7 @@
         <v>PASS</v>
       </c>
       <c r="I305" s="8">
-        <v>0.005</v>
+        <v>0.053</v>
       </c>
       <c r="J305" s="8">
         <v>1</v>
@@ -13458,7 +13458,7 @@
         <v>PASS</v>
       </c>
       <c r="I306" s="8">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="J306" s="8">
         <v>1</v>
@@ -13499,7 +13499,7 @@
         <v>PASS</v>
       </c>
       <c r="I307" s="8">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="J307" s="8">
         <v>1</v>
@@ -13540,7 +13540,7 @@
         <v>PASS</v>
       </c>
       <c r="I308" s="8">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="J308" s="8">
         <v>1</v>
@@ -13581,7 +13581,7 @@
         <v>PASS</v>
       </c>
       <c r="I309" s="8">
-        <v>0.05</v>
+        <v>0.013</v>
       </c>
       <c r="J309" s="8">
         <v>1</v>
@@ -13622,7 +13622,7 @@
         <v>PASS</v>
       </c>
       <c r="I310" s="8">
-        <v>0.033</v>
+        <v>0.006</v>
       </c>
       <c r="J310" s="8">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         <v>PASS</v>
       </c>
       <c r="I311" s="8">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="J311" s="8">
         <v>1</v>
@@ -13704,7 +13704,7 @@
         <v>PASS</v>
       </c>
       <c r="I312" s="8">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="J312" s="8">
         <v>1</v>
@@ -13786,7 +13786,7 @@
         <v>PASS</v>
       </c>
       <c r="I314" s="8">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="J314" s="8">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         <v>PASS</v>
       </c>
       <c r="I315" s="8">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="J315" s="8">
         <v>1</v>
@@ -13868,7 +13868,7 @@
         <v>PASS</v>
       </c>
       <c r="I316" s="8">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="J316" s="8">
         <v>1</v>
@@ -13909,7 +13909,7 @@
         <v>PASS</v>
       </c>
       <c r="I317" s="8">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J317" s="8">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         <v>PASS</v>
       </c>
       <c r="I318" s="8">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J318" s="8">
         <v>1</v>
@@ -13991,7 +13991,7 @@
         <v>PASS</v>
       </c>
       <c r="I319" s="8">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="J319" s="8">
         <v>1</v>
@@ -14032,7 +14032,7 @@
         <v>PASS</v>
       </c>
       <c r="I320" s="8">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="J320" s="8">
         <v>1</v>
@@ -14073,7 +14073,7 @@
         <v>PASS</v>
       </c>
       <c r="I321" s="8">
-        <v>0.005</v>
+        <v>0.066</v>
       </c>
       <c r="J321" s="8">
         <v>1</v>
@@ -14114,7 +14114,7 @@
         <v>PASS</v>
       </c>
       <c r="I322" s="8">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="J322" s="8">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>PASS</v>
       </c>
       <c r="I323" s="8">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="J323" s="8">
         <v>1</v>
@@ -14196,7 +14196,7 @@
         <v>PASS</v>
       </c>
       <c r="I324" s="8">
-        <v>0.005</v>
+        <v>0.044</v>
       </c>
       <c r="J324" s="8">
         <v>1</v>
@@ -14237,7 +14237,7 @@
         <v>PASS</v>
       </c>
       <c r="I325" s="8">
-        <v>0.005</v>
+        <v>0.042</v>
       </c>
       <c r="J325" s="8">
         <v>1</v>
@@ -14278,7 +14278,7 @@
         <v>PASS</v>
       </c>
       <c r="I326" s="8">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="J326" s="8">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         <v>PASS</v>
       </c>
       <c r="I327" s="8">
-        <v>0.012</v>
+        <v>0.059</v>
       </c>
       <c r="J327" s="8">
         <v>1</v>
@@ -14360,7 +14360,7 @@
         <v>PASS</v>
       </c>
       <c r="I328" s="8">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="J328" s="8">
         <v>1</v>
@@ -14401,7 +14401,7 @@
         <v>PASS</v>
       </c>
       <c r="I329" s="8">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="J329" s="8">
         <v>1</v>
@@ -14442,7 +14442,7 @@
         <v>PASS</v>
       </c>
       <c r="I330" s="8">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="J330" s="8">
         <v>1</v>
@@ -14514,7 +14514,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="8">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="3">
@@ -14534,7 +14534,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="8">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="4">
@@ -14554,7 +14554,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="8">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="5">
@@ -14574,7 +14574,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="8">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="6">
@@ -14594,7 +14594,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="8">
-        <v>0.052</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="7">
@@ -14614,7 +14614,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="8">
-        <v>0.981</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="8">
@@ -14634,7 +14634,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="8">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="9">
@@ -14654,7 +14654,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="8">
-        <v>0.023</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="10">
@@ -14694,7 +14694,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="8">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12">
@@ -14714,7 +14714,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="8">
-        <v>0.01</v>
+        <v>0.032</v>
       </c>
     </row>
   </sheetData>
@@ -22451,7 +22451,7 @@
         <v>GITHUB_RUN_ID</v>
       </c>
       <c r="B9" s="8" t="str">
-        <v>40364302150</v>
+        <v>40364632127</v>
       </c>
     </row>
     <row r="11">

--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -1266,7 +1266,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:04:02</v>
+        <v>26/10/2026, 17:06:00</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1613,7 +1613,7 @@
         <v>Suite duration (s)</v>
       </c>
       <c r="B25" s="5">
-        <v>56.8</v>
+        <v>40.9</v>
       </c>
       <c r="D25" s="25" t="str">
         <v>Responsive viewports</v>
@@ -1664,7 +1664,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B28" s="5" t="str">
-        <v>40364866153</v>
+        <v>40365246107</v>
       </c>
     </row>
     <row r="29">
@@ -1672,7 +1672,7 @@
         <v>Commit</v>
       </c>
       <c r="B29" s="5" t="str">
-        <v>0548411</v>
+        <v>8074ec1</v>
       </c>
     </row>
     <row r="30">
@@ -1792,7 +1792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I3" s="24">
-        <v>0.037</v>
+        <v>0.044</v>
       </c>
       <c r="J3" s="27" t="str">
         <v>PASS</v>
@@ -1827,7 +1827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I4" s="25">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="J4" s="27" t="str">
         <v>PASS</v>
@@ -1862,7 +1862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I5" s="24">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="J5" s="27" t="str">
         <v>PASS</v>
@@ -1897,7 +1897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I6" s="25">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="J6" s="27" t="str">
         <v>PASS</v>
@@ -1932,7 +1932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I7" s="24">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J7" s="27" t="str">
         <v>PASS</v>
@@ -1967,7 +1967,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I8" s="25">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="J8" s="27" t="str">
         <v>PASS</v>
@@ -2002,7 +2002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I9" s="24">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="J9" s="27" t="str">
         <v>PASS</v>
@@ -2037,7 +2037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I10" s="25">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="J10" s="27" t="str">
         <v>PASS</v>
@@ -2072,7 +2072,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I11" s="24">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="J11" s="27" t="str">
         <v>PASS</v>
@@ -2107,7 +2107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I12" s="25">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="J12" s="27" t="str">
         <v>PASS</v>
@@ -2142,7 +2142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I13" s="24">
-        <v>0.009</v>
+        <v>0.034</v>
       </c>
       <c r="J13" s="27" t="str">
         <v>PASS</v>
@@ -2177,7 +2177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I14" s="25">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="J14" s="27" t="str">
         <v>PASS</v>
@@ -2212,7 +2212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I15" s="24">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="J15" s="27" t="str">
         <v>PASS</v>
@@ -2247,7 +2247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I16" s="25">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J16" s="27" t="str">
         <v>PASS</v>
@@ -2282,7 +2282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I17" s="24">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J17" s="27" t="str">
         <v>PASS</v>
@@ -2317,7 +2317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I18" s="25">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="27" t="str">
         <v>PASS</v>
@@ -2352,7 +2352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I19" s="24">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="J19" s="27" t="str">
         <v>PASS</v>
@@ -2387,7 +2387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I20" s="25">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="J20" s="27" t="str">
         <v>PASS</v>
@@ -2422,7 +2422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I21" s="24">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="J21" s="27" t="str">
         <v>PASS</v>
@@ -2457,7 +2457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I22" s="25">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J22" s="27" t="str">
         <v>PASS</v>
@@ -2492,7 +2492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I23" s="24">
-        <v>0.016</v>
+        <v>0.04</v>
       </c>
       <c r="J23" s="27" t="str">
         <v>PASS</v>
@@ -2527,7 +2527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I24" s="25">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="J24" s="27" t="str">
         <v>PASS</v>
@@ -2597,7 +2597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I26" s="25">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J26" s="27" t="str">
         <v>PASS</v>
@@ -2632,7 +2632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I27" s="24">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="J27" s="27" t="str">
         <v>PASS</v>
@@ -2667,7 +2667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I28" s="25">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="J28" s="27" t="str">
         <v>PASS</v>
@@ -2702,7 +2702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I29" s="24">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="J29" s="27" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I30" s="25">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="J30" s="27" t="str">
         <v>PASS</v>
@@ -2772,7 +2772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I31" s="24">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J31" s="27" t="str">
         <v>PASS</v>
@@ -2807,7 +2807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I32" s="25">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J32" s="27" t="str">
         <v>PASS</v>
@@ -2842,7 +2842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I33" s="24">
-        <v>0.057</v>
+        <v>0.097</v>
       </c>
       <c r="J33" s="27" t="str">
         <v>PASS</v>
@@ -2877,7 +2877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I34" s="25">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="J34" s="27" t="str">
         <v>PASS</v>
@@ -2912,7 +2912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I35" s="24">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="J35" s="27" t="str">
         <v>PASS</v>
@@ -2947,7 +2947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I36" s="25">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="J36" s="27" t="str">
         <v>PASS</v>
@@ -2982,7 +2982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I37" s="24">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="J37" s="27" t="str">
         <v>PASS</v>
@@ -3017,7 +3017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I38" s="25">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="J38" s="27" t="str">
         <v>PASS</v>
@@ -3052,7 +3052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I39" s="24">
-        <v>0.037</v>
+        <v>0.004</v>
       </c>
       <c r="J39" s="27" t="str">
         <v>PASS</v>
@@ -3087,7 +3087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I40" s="25">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="J40" s="27" t="str">
         <v>PASS</v>
@@ -3122,7 +3122,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I41" s="24">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="J41" s="27" t="str">
         <v>PASS</v>
@@ -3157,7 +3157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I42" s="25">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="J42" s="27" t="str">
         <v>PASS</v>
@@ -3192,7 +3192,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I43" s="24">
-        <v>0.067</v>
+        <v>0.03</v>
       </c>
       <c r="J43" s="27" t="str">
         <v>PASS</v>
@@ -3227,7 +3227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I44" s="25">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="J44" s="27" t="str">
         <v>PASS</v>
@@ -3262,7 +3262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I45" s="24">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J45" s="27" t="str">
         <v>PASS</v>
@@ -3297,7 +3297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I46" s="25">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="J46" s="27" t="str">
         <v>PASS</v>
@@ -3332,7 +3332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I47" s="24">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="J47" s="27" t="str">
         <v>PASS</v>
@@ -3367,7 +3367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I48" s="25">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J48" s="27" t="str">
         <v>PASS</v>
@@ -3402,7 +3402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I49" s="24">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="J49" s="27" t="str">
         <v>PASS</v>
@@ -3437,7 +3437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I50" s="25">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="J50" s="27" t="str">
         <v>PASS</v>
@@ -3472,7 +3472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I51" s="24">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="J51" s="27" t="str">
         <v>PASS</v>
@@ -3507,7 +3507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I52" s="25">
-        <v>0.037</v>
+        <v>0.004</v>
       </c>
       <c r="J52" s="27" t="str">
         <v>PASS</v>
@@ -3542,7 +3542,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I53" s="24">
-        <v>0.024</v>
+        <v>0.066</v>
       </c>
       <c r="J53" s="27" t="str">
         <v>PASS</v>
@@ -3577,7 +3577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I54" s="25">
-        <v>0.011</v>
+        <v>0.023</v>
       </c>
       <c r="J54" s="27" t="str">
         <v>PASS</v>
@@ -3612,7 +3612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I55" s="24">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="J55" s="27" t="str">
         <v>PASS</v>
@@ -3647,7 +3647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I56" s="25">
-        <v>0.009</v>
+        <v>0.015</v>
       </c>
       <c r="J56" s="27" t="str">
         <v>PASS</v>
@@ -3682,7 +3682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I57" s="24">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="J57" s="27" t="str">
         <v>PASS</v>
@@ -3717,7 +3717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I58" s="25">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="J58" s="27" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I59" s="24">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="J59" s="27" t="str">
         <v>PASS</v>
@@ -3787,7 +3787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I60" s="25">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="J60" s="27" t="str">
         <v>PASS</v>
@@ -3822,7 +3822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I61" s="24">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J61" s="27" t="str">
         <v>PASS</v>
@@ -3857,7 +3857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I62" s="25">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="J62" s="27" t="str">
         <v>PASS</v>
@@ -3892,7 +3892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I63" s="24">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="J63" s="27" t="str">
         <v>PASS</v>
@@ -3927,7 +3927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I64" s="25">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="J64" s="27" t="str">
         <v>PASS</v>
@@ -3962,7 +3962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I65" s="24">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="J65" s="27" t="str">
         <v>PASS</v>
@@ -3997,7 +3997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I66" s="25">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="J66" s="27" t="str">
         <v>PASS</v>
@@ -4032,7 +4032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I67" s="24">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="J67" s="27" t="str">
         <v>PASS</v>
@@ -4067,7 +4067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I68" s="25">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="J68" s="27" t="str">
         <v>PASS</v>
@@ -4102,7 +4102,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I69" s="24">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="J69" s="27" t="str">
         <v>PASS</v>
@@ -4137,7 +4137,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I70" s="25">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="J70" s="27" t="str">
         <v>PASS</v>
@@ -4172,7 +4172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I71" s="24">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="J71" s="27" t="str">
         <v>PASS</v>
@@ -4207,7 +4207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I72" s="25">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="J72" s="27" t="str">
         <v>PASS</v>
@@ -4242,7 +4242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I73" s="24">
-        <v>0.019</v>
+        <v>0.054</v>
       </c>
       <c r="J73" s="27" t="str">
         <v>PASS</v>
@@ -4277,7 +4277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I74" s="25">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="J74" s="27" t="str">
         <v>PASS</v>
@@ -4312,7 +4312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I75" s="24">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
       <c r="J75" s="27" t="str">
         <v>PASS</v>
@@ -4347,7 +4347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I76" s="25">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="J76" s="27" t="str">
         <v>PASS</v>
@@ -4382,7 +4382,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I77" s="24">
-        <v>0.006</v>
+        <v>0.033</v>
       </c>
       <c r="J77" s="27" t="str">
         <v>PASS</v>
@@ -4417,7 +4417,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I78" s="25">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="J78" s="27" t="str">
         <v>PASS</v>
@@ -4452,7 +4452,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I79" s="24">
-        <v>0.005</v>
+        <v>0.026</v>
       </c>
       <c r="J79" s="27" t="str">
         <v>PASS</v>
@@ -4487,7 +4487,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I80" s="25">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J80" s="27" t="str">
         <v>PASS</v>
@@ -4522,7 +4522,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I81" s="24">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="J81" s="27" t="str">
         <v>PASS</v>
@@ -4592,7 +4592,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I83" s="24">
-        <v>0.03</v>
+        <v>0.074</v>
       </c>
       <c r="J83" s="27" t="str">
         <v>PASS</v>
@@ -4627,7 +4627,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I84" s="25">
-        <v>0.026</v>
+        <v>0.011</v>
       </c>
       <c r="J84" s="27" t="str">
         <v>PASS</v>
@@ -4662,7 +4662,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I85" s="24">
-        <v>0.019</v>
+        <v>0.04</v>
       </c>
       <c r="J85" s="27" t="str">
         <v>PASS</v>
@@ -4697,7 +4697,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I86" s="25">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="J86" s="27" t="str">
         <v>PASS</v>
@@ -4732,7 +4732,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I87" s="24">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="J87" s="27" t="str">
         <v>PASS</v>
@@ -4802,7 +4802,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I89" s="24">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="J89" s="27" t="str">
         <v>PASS</v>
@@ -4837,7 +4837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I90" s="25">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="J90" s="27" t="str">
         <v>PASS</v>
@@ -4872,7 +4872,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I91" s="24">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="J91" s="27" t="str">
         <v>PASS</v>
@@ -4907,7 +4907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I92" s="25">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="J92" s="27" t="str">
         <v>PASS</v>
@@ -4942,7 +4942,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I93" s="24">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="J93" s="27" t="str">
         <v>PASS</v>
@@ -4977,7 +4977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I94" s="25">
-        <v>0.091</v>
+        <v>0.006</v>
       </c>
       <c r="J94" s="27" t="str">
         <v>PASS</v>
@@ -5012,7 +5012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I95" s="24">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="J95" s="27" t="str">
         <v>PASS</v>
@@ -5047,7 +5047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I96" s="25">
-        <v>0.023</v>
+        <v>0.04</v>
       </c>
       <c r="J96" s="27" t="str">
         <v>PASS</v>
@@ -5082,7 +5082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I97" s="24">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="J97" s="27" t="str">
         <v>PASS</v>
@@ -5117,7 +5117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I98" s="25">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="J98" s="27" t="str">
         <v>PASS</v>
@@ -5152,7 +5152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I99" s="24">
-        <v>0.04</v>
+        <v>0.007</v>
       </c>
       <c r="J99" s="27" t="str">
         <v>PASS</v>
@@ -5187,7 +5187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I100" s="25">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="J100" s="27" t="str">
         <v>PASS</v>
@@ -5222,7 +5222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I101" s="24">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="J101" s="27" t="str">
         <v>PASS</v>
@@ -5257,7 +5257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I102" s="25">
-        <v>0.013</v>
+        <v>0.035</v>
       </c>
       <c r="J102" s="27" t="str">
         <v>PASS</v>
@@ -5327,7 +5327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I104" s="25">
-        <v>0.033</v>
+        <v>0.016</v>
       </c>
       <c r="J104" s="27" t="str">
         <v>PASS</v>
@@ -5362,7 +5362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I105" s="24">
-        <v>0.052</v>
+        <v>0.014</v>
       </c>
       <c r="J105" s="27" t="str">
         <v>PASS</v>
@@ -5397,7 +5397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I106" s="25">
-        <v>0.026</v>
+        <v>0.009</v>
       </c>
       <c r="J106" s="27" t="str">
         <v>PASS</v>
@@ -5432,7 +5432,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I107" s="24">
-        <v>0.018</v>
+        <v>0.08</v>
       </c>
       <c r="J107" s="27" t="str">
         <v>PASS</v>
@@ -5467,7 +5467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I108" s="25">
-        <v>0.027</v>
+        <v>0.005</v>
       </c>
       <c r="J108" s="27" t="str">
         <v>PASS</v>
@@ -5502,7 +5502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I109" s="24">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J109" s="27" t="str">
         <v>PASS</v>
@@ -5537,7 +5537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I110" s="25">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J110" s="27" t="str">
         <v>PASS</v>
@@ -5572,7 +5572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I111" s="24">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="J111" s="27" t="str">
         <v>PASS</v>
@@ -5607,7 +5607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I112" s="25">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="J112" s="27" t="str">
         <v>PASS</v>
@@ -5642,7 +5642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I113" s="24">
-        <v>0.009</v>
+        <v>0.053</v>
       </c>
       <c r="J113" s="27" t="str">
         <v>PASS</v>
@@ -5677,7 +5677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I114" s="25">
-        <v>0.072</v>
+        <v>0.054</v>
       </c>
       <c r="J114" s="27" t="str">
         <v>PASS</v>
@@ -5712,7 +5712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I115" s="24">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="J115" s="27" t="str">
         <v>PASS</v>
@@ -5747,7 +5747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I116" s="25">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="J116" s="27" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I117" s="24">
-        <v>0.035</v>
+        <v>0.006</v>
       </c>
       <c r="J117" s="27" t="str">
         <v>PASS</v>
@@ -5817,7 +5817,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I118" s="25">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="J118" s="27" t="str">
         <v>PASS</v>
@@ -5852,7 +5852,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I119" s="24">
-        <v>0.015</v>
+        <v>0.062</v>
       </c>
       <c r="J119" s="27" t="str">
         <v>PASS</v>
@@ -5887,7 +5887,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I120" s="25">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="J120" s="27" t="str">
         <v>PASS</v>
@@ -5922,7 +5922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I121" s="24">
-        <v>0.015</v>
+        <v>0.034</v>
       </c>
       <c r="J121" s="27" t="str">
         <v>PASS</v>
@@ -5957,7 +5957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I122" s="25">
-        <v>0.008</v>
+        <v>0.049</v>
       </c>
       <c r="J122" s="27" t="str">
         <v>PASS</v>
@@ -5992,7 +5992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I123" s="24">
-        <v>0.007</v>
+        <v>0.032</v>
       </c>
       <c r="J123" s="27" t="str">
         <v>PASS</v>
@@ -6027,7 +6027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I124" s="25">
-        <v>0.077</v>
+        <v>0.006</v>
       </c>
       <c r="J124" s="27" t="str">
         <v>PASS</v>
@@ -6062,7 +6062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I125" s="24">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="J125" s="27" t="str">
         <v>PASS</v>
@@ -6097,7 +6097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I126" s="25">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="J126" s="27" t="str">
         <v>PASS</v>
@@ -6132,7 +6132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I127" s="24">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="J127" s="27" t="str">
         <v>PASS</v>
@@ -6167,7 +6167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I128" s="25">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="J128" s="27" t="str">
         <v>PASS</v>
@@ -6202,7 +6202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I129" s="24">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="J129" s="27" t="str">
         <v>PASS</v>
@@ -6237,7 +6237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I130" s="25">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J130" s="27" t="str">
         <v>PASS</v>
@@ -6272,7 +6272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I131" s="24">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="J131" s="27" t="str">
         <v>PASS</v>
@@ -6307,7 +6307,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I132" s="25">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="J132" s="27" t="str">
         <v>PASS</v>
@@ -6342,7 +6342,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I133" s="24">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="J133" s="27" t="str">
         <v>PASS</v>
@@ -6377,7 +6377,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I134" s="25">
-        <v>0.293</v>
+        <v>0.098</v>
       </c>
       <c r="J134" s="27" t="str">
         <v>PASS</v>
@@ -6412,7 +6412,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I135" s="24">
-        <v>0.13</v>
+        <v>0.054</v>
       </c>
       <c r="J135" s="27" t="str">
         <v>PASS</v>
@@ -6447,7 +6447,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I136" s="25">
-        <v>0.035</v>
+        <v>0.072</v>
       </c>
       <c r="J136" s="27" t="str">
         <v>PASS</v>
@@ -6482,7 +6482,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I137" s="24">
-        <v>0.027</v>
+        <v>0.048</v>
       </c>
       <c r="J137" s="27" t="str">
         <v>PASS</v>
@@ -6517,7 +6517,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I138" s="25">
-        <v>0.057</v>
+        <v>0.065</v>
       </c>
       <c r="J138" s="27" t="str">
         <v>PASS</v>
@@ -6552,7 +6552,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I139" s="24">
-        <v>0.061</v>
+        <v>0.013</v>
       </c>
       <c r="J139" s="27" t="str">
         <v>PASS</v>
@@ -6587,7 +6587,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I140" s="25">
-        <v>0.078</v>
+        <v>0.039</v>
       </c>
       <c r="J140" s="27" t="str">
         <v>PASS</v>
@@ -6622,7 +6622,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I141" s="24">
-        <v>0.015</v>
+        <v>0.029</v>
       </c>
       <c r="J141" s="27" t="str">
         <v>PASS</v>
@@ -6657,7 +6657,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I142" s="25">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="J142" s="27" t="str">
         <v>PASS</v>
@@ -6692,7 +6692,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I143" s="24">
-        <v>0.01</v>
+        <v>0.036</v>
       </c>
       <c r="J143" s="27" t="str">
         <v>PASS</v>
@@ -6727,7 +6727,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I144" s="25">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="J144" s="27" t="str">
         <v>PASS</v>
@@ -6762,7 +6762,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I145" s="24">
-        <v>0.056</v>
+        <v>0.043</v>
       </c>
       <c r="J145" s="27" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I146" s="25">
-        <v>0.056</v>
+        <v>0.01</v>
       </c>
       <c r="J146" s="27" t="str">
         <v>PASS</v>
@@ -6832,7 +6832,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I147" s="24">
-        <v>0.058</v>
+        <v>0.027</v>
       </c>
       <c r="J147" s="27" t="str">
         <v>PASS</v>
@@ -6867,7 +6867,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I148" s="25">
-        <v>0.041</v>
+        <v>0.02</v>
       </c>
       <c r="J148" s="27" t="str">
         <v>PASS</v>
@@ -6902,7 +6902,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I149" s="24">
-        <v>0.262</v>
+        <v>0.048</v>
       </c>
       <c r="J149" s="27" t="str">
         <v>PASS</v>
@@ -6937,7 +6937,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I150" s="25">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="J150" s="27" t="str">
         <v>PASS</v>
@@ -6972,7 +6972,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I151" s="24">
-        <v>0.129</v>
+        <v>0.037</v>
       </c>
       <c r="J151" s="27" t="str">
         <v>PASS</v>
@@ -7007,7 +7007,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I152" s="25">
-        <v>0.095</v>
+        <v>0.024</v>
       </c>
       <c r="J152" s="27" t="str">
         <v>PASS</v>
@@ -7042,7 +7042,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I153" s="24">
-        <v>0.093</v>
+        <v>0.011</v>
       </c>
       <c r="J153" s="27" t="str">
         <v>PASS</v>
@@ -7077,7 +7077,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I154" s="25">
-        <v>0.423</v>
+        <v>0.064</v>
       </c>
       <c r="J154" s="27" t="str">
         <v>PASS</v>
@@ -7112,7 +7112,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I155" s="24">
-        <v>0.154</v>
+        <v>0.067</v>
       </c>
       <c r="J155" s="27" t="str">
         <v>PASS</v>
@@ -7147,7 +7147,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I156" s="25">
-        <v>0.099</v>
+        <v>0.062</v>
       </c>
       <c r="J156" s="27" t="str">
         <v>PASS</v>
@@ -7182,7 +7182,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I157" s="24">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="J157" s="27" t="str">
         <v>PASS</v>
@@ -7217,7 +7217,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I158" s="25">
-        <v>0.027</v>
+        <v>0.084</v>
       </c>
       <c r="J158" s="27" t="str">
         <v>PASS</v>
@@ -7252,7 +7252,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I159" s="24">
-        <v>0.014</v>
+        <v>0.224</v>
       </c>
       <c r="J159" s="27" t="str">
         <v>PASS</v>
@@ -7287,7 +7287,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I160" s="25">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="J160" s="27" t="str">
         <v>PASS</v>
@@ -7322,7 +7322,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I161" s="24">
-        <v>0.018</v>
+        <v>0.056</v>
       </c>
       <c r="J161" s="27" t="str">
         <v>PASS</v>
@@ -7357,7 +7357,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I162" s="25">
-        <v>0.012</v>
+        <v>0.049</v>
       </c>
       <c r="J162" s="27" t="str">
         <v>PASS</v>
@@ -7392,7 +7392,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I163" s="24">
-        <v>0.01</v>
+        <v>0.052</v>
       </c>
       <c r="J163" s="27" t="str">
         <v>PASS</v>
@@ -7427,7 +7427,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I164" s="25">
-        <v>0.321</v>
+        <v>0.097</v>
       </c>
       <c r="J164" s="27" t="str">
         <v>PASS</v>
@@ -7462,7 +7462,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I165" s="24">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="J165" s="27" t="str">
         <v>PASS</v>
@@ -7497,7 +7497,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I166" s="25">
-        <v>0.036</v>
+        <v>0.064</v>
       </c>
       <c r="J166" s="27" t="str">
         <v>PASS</v>
@@ -7532,7 +7532,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I167" s="24">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="J167" s="27" t="str">
         <v>PASS</v>
@@ -7567,7 +7567,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I168" s="25">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="J168" s="27" t="str">
         <v>PASS</v>
@@ -7602,7 +7602,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I169" s="24">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="J169" s="27" t="str">
         <v>PASS</v>
@@ -7637,7 +7637,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I170" s="25">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="J170" s="27" t="str">
         <v>PASS</v>
@@ -7672,7 +7672,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I171" s="24">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J171" s="27" t="str">
         <v>PASS</v>
@@ -7707,7 +7707,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I172" s="25">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="J172" s="27" t="str">
         <v>PASS</v>
@@ -7742,7 +7742,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I173" s="24">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="J173" s="27" t="str">
         <v>PASS</v>
@@ -7777,7 +7777,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I174" s="25">
-        <v>0.083</v>
+        <v>0.021</v>
       </c>
       <c r="J174" s="27" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I175" s="24">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
       <c r="J175" s="27" t="str">
         <v>PASS</v>
@@ -7847,7 +7847,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I176" s="25">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="J176" s="27" t="str">
         <v>PASS</v>
@@ -7882,7 +7882,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I177" s="24">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="J177" s="27" t="str">
         <v>PASS</v>
@@ -7917,7 +7917,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I178" s="25">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="J178" s="27" t="str">
         <v>PASS</v>
@@ -7952,7 +7952,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I179" s="24">
-        <v>0.048</v>
+        <v>0.072</v>
       </c>
       <c r="J179" s="27" t="str">
         <v>PASS</v>
@@ -7987,7 +7987,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I180" s="25">
-        <v>0.046</v>
+        <v>0.025</v>
       </c>
       <c r="J180" s="27" t="str">
         <v>PASS</v>
@@ -8022,7 +8022,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I181" s="24">
-        <v>0.05</v>
+        <v>0.018</v>
       </c>
       <c r="J181" s="27" t="str">
         <v>PASS</v>
@@ -8057,7 +8057,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I182" s="25">
-        <v>0.134</v>
+        <v>0.042</v>
       </c>
       <c r="J182" s="27" t="str">
         <v>PASS</v>
@@ -8092,7 +8092,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I183" s="24">
-        <v>0.047</v>
+        <v>0.018</v>
       </c>
       <c r="J183" s="27" t="str">
         <v>PASS</v>
@@ -8127,7 +8127,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I184" s="25">
-        <v>0.052</v>
+        <v>0.021</v>
       </c>
       <c r="J184" s="27" t="str">
         <v>PASS</v>
@@ -8162,7 +8162,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I185" s="24">
-        <v>0.552</v>
+        <v>0.496</v>
       </c>
       <c r="J185" s="27" t="str">
         <v>PASS</v>
@@ -8197,7 +8197,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I186" s="25">
-        <v>0.976</v>
+        <v>0.866</v>
       </c>
       <c r="J186" s="27" t="str">
         <v>PASS</v>
@@ -8232,7 +8232,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I187" s="24">
-        <v>1.101</v>
+        <v>0.881</v>
       </c>
       <c r="J187" s="27" t="str">
         <v>PASS</v>
@@ -8267,7 +8267,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I188" s="25">
-        <v>0.541</v>
+        <v>0.506</v>
       </c>
       <c r="J188" s="27" t="str">
         <v>PASS</v>
@@ -8302,7 +8302,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I189" s="24">
-        <v>0.893</v>
+        <v>0.779</v>
       </c>
       <c r="J189" s="27" t="str">
         <v>PASS</v>
@@ -8337,7 +8337,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I190" s="25">
-        <v>1.545</v>
+        <v>0.636</v>
       </c>
       <c r="J190" s="27" t="str">
         <v>PASS</v>
@@ -8372,7 +8372,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I191" s="24">
-        <v>1.429</v>
+        <v>0.97</v>
       </c>
       <c r="J191" s="27" t="str">
         <v>PASS</v>
@@ -8407,7 +8407,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I192" s="25">
-        <v>1.552</v>
+        <v>0.925</v>
       </c>
       <c r="J192" s="27" t="str">
         <v>PASS</v>
@@ -8442,7 +8442,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I193" s="24">
-        <v>1.233</v>
+        <v>0.807</v>
       </c>
       <c r="J193" s="27" t="str">
         <v>PASS</v>
@@ -8477,7 +8477,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I194" s="25">
-        <v>0.054</v>
+        <v>0.004</v>
       </c>
       <c r="J194" s="27" t="str">
         <v>PASS</v>
@@ -8512,7 +8512,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I195" s="24">
-        <v>0.034</v>
+        <v>0.004</v>
       </c>
       <c r="J195" s="27" t="str">
         <v>PASS</v>
@@ -8547,7 +8547,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I196" s="25">
-        <v>0.028</v>
+        <v>0.015</v>
       </c>
       <c r="J196" s="27" t="str">
         <v>PASS</v>
@@ -8582,7 +8582,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I197" s="24">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="J197" s="27" t="str">
         <v>PASS</v>
@@ -8617,7 +8617,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I198" s="25">
-        <v>1.106</v>
+        <v>1.177</v>
       </c>
       <c r="J198" s="27" t="str">
         <v>PASS</v>
@@ -8652,7 +8652,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I199" s="24">
-        <v>1.536</v>
+        <v>1.476</v>
       </c>
       <c r="J199" s="27" t="str">
         <v>PASS</v>
@@ -8687,7 +8687,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I200" s="25">
-        <v>1.841</v>
+        <v>1.54</v>
       </c>
       <c r="J200" s="27" t="str">
         <v>PASS</v>
@@ -8722,7 +8722,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I201" s="24">
-        <v>1.481</v>
+        <v>1.275</v>
       </c>
       <c r="J201" s="27" t="str">
         <v>PASS</v>
@@ -8757,7 +8757,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I202" s="25">
-        <v>2.074</v>
+        <v>1.832</v>
       </c>
       <c r="J202" s="27" t="str">
         <v>PASS</v>
@@ -8792,7 +8792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I203" s="24">
-        <v>1.964</v>
+        <v>1.699</v>
       </c>
       <c r="J203" s="27" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I204" s="25">
-        <v>0.857</v>
+        <v>0.738</v>
       </c>
       <c r="J204" s="27" t="str">
         <v>PASS</v>
@@ -8862,7 +8862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I205" s="24">
-        <v>0.045</v>
+        <v>0.022</v>
       </c>
       <c r="J205" s="27" t="str">
         <v>PASS</v>
@@ -8897,7 +8897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I206" s="25">
-        <v>0.038</v>
+        <v>0.025</v>
       </c>
       <c r="J206" s="27" t="str">
         <v>PASS</v>
@@ -8932,7 +8932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I207" s="24">
-        <v>0.067</v>
+        <v>0.055</v>
       </c>
       <c r="J207" s="27" t="str">
         <v>PASS</v>
@@ -8967,7 +8967,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I208" s="25">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="J208" s="27" t="str">
         <v>PASS</v>
@@ -9002,7 +9002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I209" s="24">
-        <v>0.037</v>
+        <v>0.013</v>
       </c>
       <c r="J209" s="27" t="str">
         <v>PASS</v>
@@ -9037,7 +9037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I210" s="25">
-        <v>0.058</v>
+        <v>0.028</v>
       </c>
       <c r="J210" s="27" t="str">
         <v>PASS</v>
@@ -9072,7 +9072,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I211" s="24">
-        <v>0.111</v>
+        <v>0.104</v>
       </c>
       <c r="J211" s="27" t="str">
         <v>PASS</v>
@@ -9107,7 +9107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I212" s="25">
-        <v>0.838</v>
+        <v>1.377</v>
       </c>
       <c r="J212" s="27" t="str">
         <v>PASS</v>
@@ -9142,7 +9142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I213" s="24">
-        <v>0.632</v>
+        <v>0.679</v>
       </c>
       <c r="J213" s="27" t="str">
         <v>PASS</v>
@@ -9177,7 +9177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I214" s="25">
-        <v>1.174</v>
+        <v>1.357</v>
       </c>
       <c r="J214" s="27" t="str">
         <v>PASS</v>
@@ -9212,7 +9212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I215" s="24">
-        <v>0.046</v>
+        <v>0.006</v>
       </c>
       <c r="J215" s="27" t="str">
         <v>PASS</v>
@@ -9247,7 +9247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I216" s="25">
-        <v>0.049</v>
+        <v>0.003</v>
       </c>
       <c r="J216" s="27" t="str">
         <v>PASS</v>
@@ -9282,7 +9282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I217" s="24">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="J217" s="27" t="str">
         <v>PASS</v>
@@ -9317,7 +9317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I218" s="25">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="J218" s="27" t="str">
         <v>PASS</v>
@@ -9352,7 +9352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I219" s="24">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="J219" s="27" t="str">
         <v>PASS</v>
@@ -9387,7 +9387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I220" s="25">
-        <v>0.023</v>
+        <v>0.005</v>
       </c>
       <c r="J220" s="27" t="str">
         <v>PASS</v>
@@ -9422,7 +9422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I221" s="24">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="J221" s="27" t="str">
         <v>PASS</v>
@@ -9457,7 +9457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I222" s="25">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="J222" s="27" t="str">
         <v>PASS</v>
@@ -9492,7 +9492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I223" s="24">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="J223" s="27" t="str">
         <v>PASS</v>
@@ -9527,7 +9527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I224" s="25">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="J224" s="27" t="str">
         <v>PASS</v>
@@ -9562,7 +9562,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I225" s="24">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="J225" s="27" t="str">
         <v>PASS</v>
@@ -9597,7 +9597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I226" s="25">
-        <v>0.052</v>
+        <v>0.074</v>
       </c>
       <c r="J226" s="27" t="str">
         <v>PASS</v>
@@ -9632,7 +9632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I227" s="24">
-        <v>0.06</v>
+        <v>0.039</v>
       </c>
       <c r="J227" s="27" t="str">
         <v>PASS</v>
@@ -9667,7 +9667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I228" s="25">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="J228" s="27" t="str">
         <v>PASS</v>
@@ -9702,7 +9702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I229" s="24">
-        <v>0.071</v>
+        <v>0.033</v>
       </c>
       <c r="J229" s="27" t="str">
         <v>PASS</v>
@@ -9737,7 +9737,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I230" s="25">
-        <v>0.044</v>
+        <v>0.008</v>
       </c>
       <c r="J230" s="27" t="str">
         <v>PASS</v>
@@ -9772,7 +9772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I231" s="24">
-        <v>0.048</v>
+        <v>0.004</v>
       </c>
       <c r="J231" s="27" t="str">
         <v>PASS</v>
@@ -9807,7 +9807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I232" s="25">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="J232" s="27" t="str">
         <v>PASS</v>
@@ -9842,7 +9842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I233" s="24">
-        <v>0.089</v>
+        <v>0.022</v>
       </c>
       <c r="J233" s="27" t="str">
         <v>PASS</v>
@@ -9877,7 +9877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I234" s="25">
-        <v>0.056</v>
+        <v>0.022</v>
       </c>
       <c r="J234" s="27" t="str">
         <v>PASS</v>
@@ -9912,7 +9912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I235" s="24">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="J235" s="27" t="str">
         <v>PASS</v>
@@ -9947,7 +9947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I236" s="25">
-        <v>0.074</v>
+        <v>0.057</v>
       </c>
       <c r="J236" s="27" t="str">
         <v>PASS</v>
@@ -9982,7 +9982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I237" s="24">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="J237" s="27" t="str">
         <v>PASS</v>
@@ -10017,7 +10017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I238" s="25">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="J238" s="27" t="str">
         <v>PASS</v>
@@ -10052,7 +10052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I239" s="24">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="J239" s="27" t="str">
         <v>PASS</v>
@@ -10087,7 +10087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I240" s="25">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J240" s="27" t="str">
         <v>PASS</v>
@@ -10122,7 +10122,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I241" s="24">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J241" s="27" t="str">
         <v>PASS</v>
@@ -10157,7 +10157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I242" s="25">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="J242" s="27" t="str">
         <v>PASS</v>
@@ -10192,7 +10192,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I243" s="24">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="J243" s="27" t="str">
         <v>PASS</v>
@@ -10227,7 +10227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I244" s="25">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="J244" s="27" t="str">
         <v>PASS</v>
@@ -10262,7 +10262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I245" s="24">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="J245" s="27" t="str">
         <v>PASS</v>
@@ -10297,7 +10297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I246" s="25">
-        <v>0.048</v>
+        <v>0.03</v>
       </c>
       <c r="J246" s="27" t="str">
         <v>PASS</v>
@@ -10332,7 +10332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I247" s="24">
-        <v>0.052</v>
+        <v>0.004</v>
       </c>
       <c r="J247" s="27" t="str">
         <v>PASS</v>
@@ -10367,7 +10367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I248" s="25">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="J248" s="27" t="str">
         <v>PASS</v>
@@ -10402,7 +10402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I249" s="24">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="J249" s="27" t="str">
         <v>PASS</v>
@@ -10437,7 +10437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I250" s="25">
-        <v>0.019</v>
+        <v>0.009</v>
       </c>
       <c r="J250" s="27" t="str">
         <v>PASS</v>
@@ -10472,7 +10472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I251" s="24">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="J251" s="27" t="str">
         <v>PASS</v>
@@ -10507,7 +10507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I252" s="25">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J252" s="27" t="str">
         <v>PASS</v>
@@ -10542,7 +10542,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I253" s="24">
-        <v>0.029</v>
+        <v>0.01</v>
       </c>
       <c r="J253" s="27" t="str">
         <v>PASS</v>
@@ -10577,7 +10577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I254" s="25">
-        <v>0.033</v>
+        <v>0.002</v>
       </c>
       <c r="J254" s="27" t="str">
         <v>PASS</v>
@@ -10612,7 +10612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I255" s="24">
-        <v>0.038</v>
+        <v>0.003</v>
       </c>
       <c r="J255" s="27" t="str">
         <v>PASS</v>
@@ -10647,7 +10647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I256" s="25">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="J256" s="27" t="str">
         <v>PASS</v>
@@ -10682,7 +10682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I257" s="24">
-        <v>0.174</v>
+        <v>0.01</v>
       </c>
       <c r="J257" s="27" t="str">
         <v>PASS</v>
@@ -10717,7 +10717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I258" s="25">
-        <v>0.024</v>
+        <v>0.009</v>
       </c>
       <c r="J258" s="27" t="str">
         <v>PASS</v>
@@ -10752,7 +10752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I259" s="24">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="J259" s="27" t="str">
         <v>PASS</v>
@@ -10787,7 +10787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I260" s="25">
-        <v>0.028</v>
+        <v>0.003</v>
       </c>
       <c r="J260" s="27" t="str">
         <v>PASS</v>
@@ -10822,7 +10822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I261" s="24">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="J261" s="27" t="str">
         <v>PASS</v>
@@ -10857,7 +10857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I262" s="25">
-        <v>0.031</v>
+        <v>0.002</v>
       </c>
       <c r="J262" s="27" t="str">
         <v>PASS</v>
@@ -10892,7 +10892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I263" s="24">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="J263" s="27" t="str">
         <v>PASS</v>
@@ -10927,7 +10927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I264" s="25">
-        <v>0.042</v>
+        <v>0.006</v>
       </c>
       <c r="J264" s="27" t="str">
         <v>PASS</v>
@@ -10962,7 +10962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I265" s="24">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="J265" s="27" t="str">
         <v>PASS</v>
@@ -10997,7 +10997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I266" s="25">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="J266" s="27" t="str">
         <v>PASS</v>
@@ -11032,7 +11032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I267" s="24">
-        <v>0.074</v>
+        <v>0.183</v>
       </c>
       <c r="J267" s="27" t="str">
         <v>PASS</v>
@@ -11067,7 +11067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I268" s="25">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="J268" s="27" t="str">
         <v>PASS</v>
@@ -11102,7 +11102,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I269" s="24">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="J269" s="27" t="str">
         <v>PASS</v>
@@ -11137,7 +11137,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I270" s="25">
-        <v>0.049</v>
+        <v>0.028</v>
       </c>
       <c r="J270" s="27" t="str">
         <v>PASS</v>
@@ -11172,7 +11172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I271" s="24">
-        <v>0.114</v>
+        <v>0.011</v>
       </c>
       <c r="J271" s="27" t="str">
         <v>PASS</v>
@@ -11207,7 +11207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I272" s="25">
-        <v>0.036</v>
+        <v>0.017</v>
       </c>
       <c r="J272" s="27" t="str">
         <v>PASS</v>
@@ -11242,7 +11242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I273" s="24">
-        <v>0.049</v>
+        <v>0.025</v>
       </c>
       <c r="J273" s="27" t="str">
         <v>PASS</v>
@@ -11277,7 +11277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I274" s="25">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="J274" s="27" t="str">
         <v>PASS</v>
@@ -11312,7 +11312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I275" s="24">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="J275" s="27" t="str">
         <v>PASS</v>
@@ -11347,7 +11347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I276" s="25">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="J276" s="27" t="str">
         <v>PASS</v>
@@ -11382,7 +11382,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I277" s="24">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="J277" s="27" t="str">
         <v>PASS</v>
@@ -11452,7 +11452,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I279" s="24">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J279" s="27" t="str">
         <v>PASS</v>
@@ -11487,7 +11487,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I280" s="25">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J280" s="27" t="str">
         <v>PASS</v>
@@ -11522,7 +11522,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I281" s="24">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J281" s="27" t="str">
         <v>PASS</v>
@@ -11557,7 +11557,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I282" s="25">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="J282" s="27" t="str">
         <v>PASS</v>
@@ -11592,7 +11592,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I283" s="24">
-        <v>0.028</v>
+        <v>0.006</v>
       </c>
       <c r="J283" s="27" t="str">
         <v>PASS</v>
@@ -11627,7 +11627,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I284" s="25">
-        <v>0.073</v>
+        <v>0.015</v>
       </c>
       <c r="J284" s="27" t="str">
         <v>PASS</v>
@@ -11662,7 +11662,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I285" s="24">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="J285" s="27" t="str">
         <v>PASS</v>
@@ -11697,7 +11697,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I286" s="25">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="J286" s="27" t="str">
         <v>PASS</v>
@@ -11732,7 +11732,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I287" s="24">
-        <v>0.044</v>
+        <v>0.006</v>
       </c>
       <c r="J287" s="27" t="str">
         <v>PASS</v>
@@ -11767,7 +11767,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I288" s="25">
-        <v>0.712</v>
+        <v>0.648</v>
       </c>
       <c r="J288" s="27" t="str">
         <v>PASS</v>
@@ -11802,7 +11802,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I289" s="24">
-        <v>0.039</v>
+        <v>0.007</v>
       </c>
       <c r="J289" s="27" t="str">
         <v>PASS</v>
@@ -11837,7 +11837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I290" s="25">
-        <v>0.017</v>
+        <v>0.085</v>
       </c>
       <c r="J290" s="27" t="str">
         <v>PASS</v>
@@ -11872,7 +11872,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I291" s="24">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="J291" s="27" t="str">
         <v>PASS</v>
@@ -11907,7 +11907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I292" s="25">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="J292" s="27" t="str">
         <v>PASS</v>
@@ -11942,7 +11942,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I293" s="24">
-        <v>0.034</v>
+        <v>0.016</v>
       </c>
       <c r="J293" s="27" t="str">
         <v>PASS</v>
@@ -11977,7 +11977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I294" s="25">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="J294" s="27" t="str">
         <v>PASS</v>
@@ -12012,7 +12012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I295" s="24">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="J295" s="27" t="str">
         <v>PASS</v>
@@ -12047,7 +12047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I296" s="25">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="J296" s="27" t="str">
         <v>PASS</v>
@@ -12082,7 +12082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I297" s="24">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="J297" s="27" t="str">
         <v>PASS</v>
@@ -12117,7 +12117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I298" s="25">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="J298" s="27" t="str">
         <v>PASS</v>
@@ -12152,7 +12152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I299" s="24">
-        <v>0.018</v>
+        <v>0.001</v>
       </c>
       <c r="J299" s="27" t="str">
         <v>PASS</v>
@@ -12187,7 +12187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I300" s="25">
-        <v>0.084</v>
+        <v>0.048</v>
       </c>
       <c r="J300" s="27" t="str">
         <v>PASS</v>
@@ -12222,7 +12222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I301" s="24">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="J301" s="27" t="str">
         <v>PASS</v>
@@ -12257,7 +12257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I302" s="25">
-        <v>0.024</v>
+        <v>0.009</v>
       </c>
       <c r="J302" s="27" t="str">
         <v>PASS</v>
@@ -12292,7 +12292,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I303" s="24">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="J303" s="27" t="str">
         <v>PASS</v>
@@ -12327,7 +12327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I304" s="25">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="J304" s="27" t="str">
         <v>PASS</v>
@@ -12362,7 +12362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I305" s="24">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="J305" s="27" t="str">
         <v>PASS</v>
@@ -12397,7 +12397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I306" s="25">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="J306" s="27" t="str">
         <v>PASS</v>
@@ -12467,7 +12467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I308" s="25">
-        <v>0.016</v>
+        <v>0.009</v>
       </c>
       <c r="J308" s="27" t="str">
         <v>PASS</v>
@@ -12502,7 +12502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I309" s="24">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="J309" s="27" t="str">
         <v>PASS</v>
@@ -12537,7 +12537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I310" s="25">
-        <v>0.007</v>
+        <v>0.047</v>
       </c>
       <c r="J310" s="27" t="str">
         <v>PASS</v>
@@ -12572,7 +12572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I311" s="24">
-        <v>0.004</v>
+        <v>0.025</v>
       </c>
       <c r="J311" s="27" t="str">
         <v>PASS</v>
@@ -12607,7 +12607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I312" s="25">
-        <v>0.005</v>
+        <v>0.036</v>
       </c>
       <c r="J312" s="27" t="str">
         <v>PASS</v>
@@ -12642,7 +12642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I313" s="24">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="J313" s="27" t="str">
         <v>PASS</v>
@@ -12677,7 +12677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I314" s="25">
-        <v>0.003</v>
+        <v>0.03</v>
       </c>
       <c r="J314" s="27" t="str">
         <v>PASS</v>
@@ -12712,7 +12712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I315" s="24">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="J315" s="27" t="str">
         <v>PASS</v>
@@ -12747,7 +12747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I316" s="25">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J316" s="27" t="str">
         <v>PASS</v>
@@ -12782,7 +12782,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I317" s="24">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="J317" s="27" t="str">
         <v>PASS</v>
@@ -12922,7 +12922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I321" s="24">
-        <v>0.097</v>
+        <v>0.019</v>
       </c>
       <c r="J321" s="27" t="str">
         <v>PASS</v>
@@ -12957,7 +12957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I322" s="25">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="J322" s="27" t="str">
         <v>PASS</v>
@@ -12992,7 +12992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I323" s="24">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="J323" s="27" t="str">
         <v>PASS</v>
@@ -13027,7 +13027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I324" s="25">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="J324" s="27" t="str">
         <v>PASS</v>
@@ -13062,7 +13062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I325" s="24">
-        <v>0.03</v>
+        <v>0.007</v>
       </c>
       <c r="J325" s="27" t="str">
         <v>PASS</v>
@@ -13097,7 +13097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I326" s="25">
-        <v>0.019</v>
+        <v>0.049</v>
       </c>
       <c r="J326" s="27" t="str">
         <v>PASS</v>
@@ -13132,7 +13132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I327" s="24">
-        <v>0.026</v>
+        <v>0.009</v>
       </c>
       <c r="J327" s="27" t="str">
         <v>PASS</v>
@@ -13167,7 +13167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I328" s="25">
-        <v>0.021</v>
+        <v>0.006</v>
       </c>
       <c r="J328" s="27" t="str">
         <v>PASS</v>
@@ -13202,7 +13202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I329" s="24">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="J329" s="27" t="str">
         <v>PASS</v>
@@ -13237,7 +13237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I330" s="25">
-        <v>0.035</v>
+        <v>0.003</v>
       </c>
       <c r="J330" s="27" t="str">
         <v>PASS</v>
@@ -13272,7 +13272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I331" s="24">
-        <v>0.035</v>
+        <v>0.003</v>
       </c>
       <c r="J331" s="27" t="str">
         <v>PASS</v>
@@ -21156,7 +21156,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B6" s="24" t="str">
-        <v>0548411638b357a934d96d6883d9cef9b55ca3ae</v>
+        <v>8074ec16a6cee36e3dc10a7468a963e88b0b0f9f</v>
       </c>
     </row>
     <row r="7">
@@ -21164,7 +21164,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>40364866153</v>
+        <v>40365246107</v>
       </c>
     </row>
     <row r="8">
@@ -21172,7 +21172,7 @@
         <v>Workflow run URL</v>
       </c>
       <c r="B8" s="24" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40364866153</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40365246107</v>
       </c>
     </row>
     <row r="9">
@@ -21228,7 +21228,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B15" s="25" t="str">
-        <v>2026-10-26T17:03:05.783Z</v>
+        <v>2026-10-26T17:05:19.869Z</v>
       </c>
     </row>
     <row r="16">
@@ -21236,7 +21236,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <v>2026-10-26T17:04:02.541Z</v>
+        <v>2026-10-26T17:06:00.782Z</v>
       </c>
     </row>
     <row r="17">
@@ -21244,7 +21244,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B17" s="25">
-        <v>56.76</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="18">

--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -1266,7 +1266,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:06:00</v>
+        <v>26/10/2026, 17:14:26</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1613,7 +1613,7 @@
         <v>Suite duration (s)</v>
       </c>
       <c r="B25" s="5">
-        <v>40.9</v>
+        <v>67.5</v>
       </c>
       <c r="D25" s="25" t="str">
         <v>Responsive viewports</v>
@@ -1664,7 +1664,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B28" s="5" t="str">
-        <v>40365246107</v>
+        <v>40366447604</v>
       </c>
     </row>
     <row r="29">
@@ -1672,7 +1672,7 @@
         <v>Commit</v>
       </c>
       <c r="B29" s="5" t="str">
-        <v>8074ec1</v>
+        <v>a9ce338</v>
       </c>
     </row>
     <row r="30">
@@ -1792,7 +1792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I3" s="24">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="J3" s="27" t="str">
         <v>PASS</v>
@@ -1827,7 +1827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I4" s="25">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="J4" s="27" t="str">
         <v>PASS</v>
@@ -1862,7 +1862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I5" s="24">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="J5" s="27" t="str">
         <v>PASS</v>
@@ -1897,7 +1897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I6" s="25">
-        <v>0.02</v>
+        <v>0.009</v>
       </c>
       <c r="J6" s="27" t="str">
         <v>PASS</v>
@@ -1932,7 +1932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I7" s="24">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="J7" s="27" t="str">
         <v>PASS</v>
@@ -2002,7 +2002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I9" s="24">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="J9" s="27" t="str">
         <v>PASS</v>
@@ -2037,7 +2037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I10" s="25">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="J10" s="27" t="str">
         <v>PASS</v>
@@ -2107,7 +2107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I12" s="25">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="J12" s="27" t="str">
         <v>PASS</v>
@@ -2142,7 +2142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I13" s="24">
-        <v>0.034</v>
+        <v>0.066</v>
       </c>
       <c r="J13" s="27" t="str">
         <v>PASS</v>
@@ -2177,7 +2177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I14" s="25">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="J14" s="27" t="str">
         <v>PASS</v>
@@ -2212,7 +2212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I15" s="24">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J15" s="27" t="str">
         <v>PASS</v>
@@ -2247,7 +2247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I16" s="25">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="J16" s="27" t="str">
         <v>PASS</v>
@@ -2282,7 +2282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I17" s="24">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="J17" s="27" t="str">
         <v>PASS</v>
@@ -2317,7 +2317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I18" s="25">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="J18" s="27" t="str">
         <v>PASS</v>
@@ -2352,7 +2352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I19" s="24">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="J19" s="27" t="str">
         <v>PASS</v>
@@ -2387,7 +2387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I20" s="25">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J20" s="27" t="str">
         <v>PASS</v>
@@ -2422,7 +2422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I21" s="24">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J21" s="27" t="str">
         <v>PASS</v>
@@ -2457,7 +2457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I22" s="25">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="J22" s="27" t="str">
         <v>PASS</v>
@@ -2492,7 +2492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I23" s="24">
-        <v>0.04</v>
+        <v>0.014</v>
       </c>
       <c r="J23" s="27" t="str">
         <v>PASS</v>
@@ -2527,7 +2527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I24" s="25">
-        <v>0.015</v>
+        <v>0.009</v>
       </c>
       <c r="J24" s="27" t="str">
         <v>PASS</v>
@@ -2562,7 +2562,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I25" s="24">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="J25" s="27" t="str">
         <v>PASS</v>
@@ -2597,7 +2597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I26" s="25">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="J26" s="27" t="str">
         <v>PASS</v>
@@ -2632,7 +2632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I27" s="24">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="J27" s="27" t="str">
         <v>PASS</v>
@@ -2667,7 +2667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I28" s="25">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J28" s="27" t="str">
         <v>PASS</v>
@@ -2702,7 +2702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I29" s="24">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="J29" s="27" t="str">
         <v>PASS</v>
@@ -2772,7 +2772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I31" s="24">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="J31" s="27" t="str">
         <v>PASS</v>
@@ -2807,7 +2807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I32" s="25">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="J32" s="27" t="str">
         <v>PASS</v>
@@ -2842,7 +2842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I33" s="24">
-        <v>0.097</v>
+        <v>0.014</v>
       </c>
       <c r="J33" s="27" t="str">
         <v>PASS</v>
@@ -2877,7 +2877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I34" s="25">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="J34" s="27" t="str">
         <v>PASS</v>
@@ -2912,7 +2912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I35" s="24">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="J35" s="27" t="str">
         <v>PASS</v>
@@ -2947,7 +2947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I36" s="25">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="J36" s="27" t="str">
         <v>PASS</v>
@@ -2982,7 +2982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I37" s="24">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="J37" s="27" t="str">
         <v>PASS</v>
@@ -3017,7 +3017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I38" s="25">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="J38" s="27" t="str">
         <v>PASS</v>
@@ -3052,7 +3052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I39" s="24">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J39" s="27" t="str">
         <v>PASS</v>
@@ -3087,7 +3087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I40" s="25">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J40" s="27" t="str">
         <v>PASS</v>
@@ -3122,7 +3122,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I41" s="24">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="J41" s="27" t="str">
         <v>PASS</v>
@@ -3157,7 +3157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I42" s="25">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J42" s="27" t="str">
         <v>PASS</v>
@@ -3192,7 +3192,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I43" s="24">
-        <v>0.03</v>
+        <v>0.078</v>
       </c>
       <c r="J43" s="27" t="str">
         <v>PASS</v>
@@ -3227,7 +3227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I44" s="25">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="J44" s="27" t="str">
         <v>PASS</v>
@@ -3262,7 +3262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I45" s="24">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="J45" s="27" t="str">
         <v>PASS</v>
@@ -3297,7 +3297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I46" s="25">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="J46" s="27" t="str">
         <v>PASS</v>
@@ -3332,7 +3332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I47" s="24">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="J47" s="27" t="str">
         <v>PASS</v>
@@ -3367,7 +3367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I48" s="25">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="J48" s="27" t="str">
         <v>PASS</v>
@@ -3402,7 +3402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I49" s="24">
-        <v>0.011</v>
+        <v>0.043</v>
       </c>
       <c r="J49" s="27" t="str">
         <v>PASS</v>
@@ -3437,7 +3437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I50" s="25">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J50" s="27" t="str">
         <v>PASS</v>
@@ -3472,7 +3472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I51" s="24">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="J51" s="27" t="str">
         <v>PASS</v>
@@ -3507,7 +3507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I52" s="25">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="J52" s="27" t="str">
         <v>PASS</v>
@@ -3542,7 +3542,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I53" s="24">
-        <v>0.066</v>
+        <v>0.005</v>
       </c>
       <c r="J53" s="27" t="str">
         <v>PASS</v>
@@ -3577,7 +3577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I54" s="25">
-        <v>0.023</v>
+        <v>0.007</v>
       </c>
       <c r="J54" s="27" t="str">
         <v>PASS</v>
@@ -3612,7 +3612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I55" s="24">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
       <c r="J55" s="27" t="str">
         <v>PASS</v>
@@ -3647,7 +3647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I56" s="25">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="J56" s="27" t="str">
         <v>PASS</v>
@@ -3682,7 +3682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I57" s="24">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="J57" s="27" t="str">
         <v>PASS</v>
@@ -3717,7 +3717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I58" s="25">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="J58" s="27" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I59" s="24">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="J59" s="27" t="str">
         <v>PASS</v>
@@ -3787,7 +3787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I60" s="25">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J60" s="27" t="str">
         <v>PASS</v>
@@ -3822,7 +3822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I61" s="24">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="J61" s="27" t="str">
         <v>PASS</v>
@@ -3857,7 +3857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I62" s="25">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J62" s="27" t="str">
         <v>PASS</v>
@@ -3892,7 +3892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I63" s="24">
-        <v>0.01</v>
+        <v>0.091</v>
       </c>
       <c r="J63" s="27" t="str">
         <v>PASS</v>
@@ -3927,7 +3927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I64" s="25">
-        <v>0.004</v>
+        <v>0.047</v>
       </c>
       <c r="J64" s="27" t="str">
         <v>PASS</v>
@@ -3962,7 +3962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I65" s="24">
-        <v>0.005</v>
+        <v>0.041</v>
       </c>
       <c r="J65" s="27" t="str">
         <v>PASS</v>
@@ -3997,7 +3997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I66" s="25">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="J66" s="27" t="str">
         <v>PASS</v>
@@ -4032,7 +4032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I67" s="24">
-        <v>0.006</v>
+        <v>0.056</v>
       </c>
       <c r="J67" s="27" t="str">
         <v>PASS</v>
@@ -4067,7 +4067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I68" s="25">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J68" s="27" t="str">
         <v>PASS</v>
@@ -4102,7 +4102,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I69" s="24">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="J69" s="27" t="str">
         <v>PASS</v>
@@ -4172,7 +4172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I71" s="24">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="J71" s="27" t="str">
         <v>PASS</v>
@@ -4207,7 +4207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I72" s="25">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="J72" s="27" t="str">
         <v>PASS</v>
@@ -4242,7 +4242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I73" s="24">
-        <v>0.054</v>
+        <v>0.092</v>
       </c>
       <c r="J73" s="27" t="str">
         <v>PASS</v>
@@ -4277,7 +4277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I74" s="25">
-        <v>0.034</v>
+        <v>0.018</v>
       </c>
       <c r="J74" s="27" t="str">
         <v>PASS</v>
@@ -4312,7 +4312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I75" s="24">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="J75" s="27" t="str">
         <v>PASS</v>
@@ -4347,7 +4347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I76" s="25">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="J76" s="27" t="str">
         <v>PASS</v>
@@ -4382,7 +4382,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I77" s="24">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="J77" s="27" t="str">
         <v>PASS</v>
@@ -4417,7 +4417,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I78" s="25">
-        <v>0.012</v>
+        <v>0.057</v>
       </c>
       <c r="J78" s="27" t="str">
         <v>PASS</v>
@@ -4452,7 +4452,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I79" s="24">
-        <v>0.026</v>
+        <v>0.018</v>
       </c>
       <c r="J79" s="27" t="str">
         <v>PASS</v>
@@ -4487,7 +4487,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I80" s="25">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="J80" s="27" t="str">
         <v>PASS</v>
@@ -4522,7 +4522,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I81" s="24">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="J81" s="27" t="str">
         <v>PASS</v>
@@ -4557,7 +4557,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I82" s="25">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="J82" s="27" t="str">
         <v>PASS</v>
@@ -4592,7 +4592,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I83" s="24">
-        <v>0.074</v>
+        <v>0.012</v>
       </c>
       <c r="J83" s="27" t="str">
         <v>PASS</v>
@@ -4627,7 +4627,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I84" s="25">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="J84" s="27" t="str">
         <v>PASS</v>
@@ -4662,7 +4662,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I85" s="24">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
       <c r="J85" s="27" t="str">
         <v>PASS</v>
@@ -4697,7 +4697,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I86" s="25">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J86" s="27" t="str">
         <v>PASS</v>
@@ -4732,7 +4732,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I87" s="24">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="J87" s="27" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I88" s="25">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
       <c r="J88" s="27" t="str">
         <v>PASS</v>
@@ -4802,7 +4802,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I89" s="24">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="J89" s="27" t="str">
         <v>PASS</v>
@@ -4837,7 +4837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I90" s="25">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="J90" s="27" t="str">
         <v>PASS</v>
@@ -4907,7 +4907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I92" s="25">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="J92" s="27" t="str">
         <v>PASS</v>
@@ -4942,7 +4942,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I93" s="24">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="J93" s="27" t="str">
         <v>PASS</v>
@@ -4977,7 +4977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I94" s="25">
-        <v>0.006</v>
+        <v>0.117</v>
       </c>
       <c r="J94" s="27" t="str">
         <v>PASS</v>
@@ -5012,7 +5012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I95" s="24">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J95" s="27" t="str">
         <v>PASS</v>
@@ -5047,7 +5047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I96" s="25">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="J96" s="27" t="str">
         <v>PASS</v>
@@ -5082,7 +5082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I97" s="24">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="J97" s="27" t="str">
         <v>PASS</v>
@@ -5117,7 +5117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I98" s="25">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="J98" s="27" t="str">
         <v>PASS</v>
@@ -5152,7 +5152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I99" s="24">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="J99" s="27" t="str">
         <v>PASS</v>
@@ -5187,7 +5187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I100" s="25">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="J100" s="27" t="str">
         <v>PASS</v>
@@ -5222,7 +5222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I101" s="24">
-        <v>0.033</v>
+        <v>0.019</v>
       </c>
       <c r="J101" s="27" t="str">
         <v>PASS</v>
@@ -5257,7 +5257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I102" s="25">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="J102" s="27" t="str">
         <v>PASS</v>
@@ -5292,7 +5292,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I103" s="24">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="J103" s="27" t="str">
         <v>PASS</v>
@@ -5327,7 +5327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I104" s="25">
-        <v>0.016</v>
+        <v>0.063</v>
       </c>
       <c r="J104" s="27" t="str">
         <v>PASS</v>
@@ -5362,7 +5362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I105" s="24">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="J105" s="27" t="str">
         <v>PASS</v>
@@ -5397,7 +5397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I106" s="25">
-        <v>0.009</v>
+        <v>0.028</v>
       </c>
       <c r="J106" s="27" t="str">
         <v>PASS</v>
@@ -5432,7 +5432,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I107" s="24">
-        <v>0.08</v>
+        <v>0.021</v>
       </c>
       <c r="J107" s="27" t="str">
         <v>PASS</v>
@@ -5467,7 +5467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I108" s="25">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="J108" s="27" t="str">
         <v>PASS</v>
@@ -5502,7 +5502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I109" s="24">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
       <c r="J109" s="27" t="str">
         <v>PASS</v>
@@ -5537,7 +5537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I110" s="25">
-        <v>0.004</v>
+        <v>0.043</v>
       </c>
       <c r="J110" s="27" t="str">
         <v>PASS</v>
@@ -5572,7 +5572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I111" s="24">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J111" s="27" t="str">
         <v>PASS</v>
@@ -5607,7 +5607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I112" s="25">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="J112" s="27" t="str">
         <v>PASS</v>
@@ -5642,7 +5642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I113" s="24">
-        <v>0.053</v>
+        <v>0.011</v>
       </c>
       <c r="J113" s="27" t="str">
         <v>PASS</v>
@@ -5677,7 +5677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I114" s="25">
-        <v>0.054</v>
+        <v>0.16</v>
       </c>
       <c r="J114" s="27" t="str">
         <v>PASS</v>
@@ -5712,7 +5712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I115" s="24">
-        <v>0.015</v>
+        <v>0.044</v>
       </c>
       <c r="J115" s="27" t="str">
         <v>PASS</v>
@@ -5747,7 +5747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I116" s="25">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
       <c r="J116" s="27" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I117" s="24">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="J117" s="27" t="str">
         <v>PASS</v>
@@ -5817,7 +5817,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I118" s="25">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J118" s="27" t="str">
         <v>PASS</v>
@@ -5852,7 +5852,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I119" s="24">
-        <v>0.062</v>
+        <v>0.023</v>
       </c>
       <c r="J119" s="27" t="str">
         <v>PASS</v>
@@ -5887,7 +5887,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I120" s="25">
-        <v>0.03</v>
+        <v>0.041</v>
       </c>
       <c r="J120" s="27" t="str">
         <v>PASS</v>
@@ -5922,7 +5922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I121" s="24">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
       <c r="J121" s="27" t="str">
         <v>PASS</v>
@@ -5957,7 +5957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I122" s="25">
-        <v>0.049</v>
+        <v>0.024</v>
       </c>
       <c r="J122" s="27" t="str">
         <v>PASS</v>
@@ -5992,7 +5992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I123" s="24">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="J123" s="27" t="str">
         <v>PASS</v>
@@ -6027,7 +6027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I124" s="25">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="J124" s="27" t="str">
         <v>PASS</v>
@@ -6062,7 +6062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I125" s="24">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="J125" s="27" t="str">
         <v>PASS</v>
@@ -6097,7 +6097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I126" s="25">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="J126" s="27" t="str">
         <v>PASS</v>
@@ -6132,7 +6132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I127" s="24">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="J127" s="27" t="str">
         <v>PASS</v>
@@ -6167,7 +6167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I128" s="25">
-        <v>0.004</v>
+        <v>0.041</v>
       </c>
       <c r="J128" s="27" t="str">
         <v>PASS</v>
@@ -6202,7 +6202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I129" s="24">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="J129" s="27" t="str">
         <v>PASS</v>
@@ -6237,7 +6237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I130" s="25">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="J130" s="27" t="str">
         <v>PASS</v>
@@ -6272,7 +6272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I131" s="24">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="J131" s="27" t="str">
         <v>PASS</v>
@@ -6307,7 +6307,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I132" s="25">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="J132" s="27" t="str">
         <v>PASS</v>
@@ -6342,7 +6342,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I133" s="24">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J133" s="27" t="str">
         <v>PASS</v>
@@ -6377,7 +6377,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I134" s="25">
-        <v>0.098</v>
+        <v>0.053</v>
       </c>
       <c r="J134" s="27" t="str">
         <v>PASS</v>
@@ -6412,7 +6412,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I135" s="24">
-        <v>0.054</v>
+        <v>0.028</v>
       </c>
       <c r="J135" s="27" t="str">
         <v>PASS</v>
@@ -6447,7 +6447,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I136" s="25">
-        <v>0.072</v>
+        <v>0.044</v>
       </c>
       <c r="J136" s="27" t="str">
         <v>PASS</v>
@@ -6482,7 +6482,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I137" s="24">
-        <v>0.048</v>
+        <v>0.029</v>
       </c>
       <c r="J137" s="27" t="str">
         <v>PASS</v>
@@ -6517,7 +6517,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I138" s="25">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="J138" s="27" t="str">
         <v>PASS</v>
@@ -6552,7 +6552,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I139" s="24">
-        <v>0.013</v>
+        <v>0.101</v>
       </c>
       <c r="J139" s="27" t="str">
         <v>PASS</v>
@@ -6587,7 +6587,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I140" s="25">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="J140" s="27" t="str">
         <v>PASS</v>
@@ -6622,7 +6622,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I141" s="24">
-        <v>0.029</v>
+        <v>0.067</v>
       </c>
       <c r="J141" s="27" t="str">
         <v>PASS</v>
@@ -6657,7 +6657,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I142" s="25">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="J142" s="27" t="str">
         <v>PASS</v>
@@ -6692,7 +6692,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I143" s="24">
-        <v>0.036</v>
+        <v>0.025</v>
       </c>
       <c r="J143" s="27" t="str">
         <v>PASS</v>
@@ -6727,7 +6727,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I144" s="25">
-        <v>0.02</v>
+        <v>0.124</v>
       </c>
       <c r="J144" s="27" t="str">
         <v>PASS</v>
@@ -6762,7 +6762,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I145" s="24">
-        <v>0.043</v>
+        <v>0.035</v>
       </c>
       <c r="J145" s="27" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I146" s="25">
-        <v>0.01</v>
+        <v>0.048</v>
       </c>
       <c r="J146" s="27" t="str">
         <v>PASS</v>
@@ -6832,7 +6832,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I147" s="24">
-        <v>0.027</v>
+        <v>0.076</v>
       </c>
       <c r="J147" s="27" t="str">
         <v>PASS</v>
@@ -6867,7 +6867,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I148" s="25">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="J148" s="27" t="str">
         <v>PASS</v>
@@ -6902,7 +6902,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I149" s="24">
-        <v>0.048</v>
+        <v>0.128</v>
       </c>
       <c r="J149" s="27" t="str">
         <v>PASS</v>
@@ -6937,7 +6937,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I150" s="25">
-        <v>0.044</v>
+        <v>0.074</v>
       </c>
       <c r="J150" s="27" t="str">
         <v>PASS</v>
@@ -6972,7 +6972,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I151" s="24">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="J151" s="27" t="str">
         <v>PASS</v>
@@ -7007,7 +7007,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I152" s="25">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
       <c r="J152" s="27" t="str">
         <v>PASS</v>
@@ -7042,7 +7042,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I153" s="24">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="J153" s="27" t="str">
         <v>PASS</v>
@@ -7077,7 +7077,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I154" s="25">
-        <v>0.064</v>
+        <v>0.301</v>
       </c>
       <c r="J154" s="27" t="str">
         <v>PASS</v>
@@ -7112,7 +7112,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I155" s="24">
-        <v>0.067</v>
+        <v>0.253</v>
       </c>
       <c r="J155" s="27" t="str">
         <v>PASS</v>
@@ -7147,7 +7147,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I156" s="25">
-        <v>0.062</v>
+        <v>0.151</v>
       </c>
       <c r="J156" s="27" t="str">
         <v>PASS</v>
@@ -7182,7 +7182,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I157" s="24">
-        <v>0.043</v>
+        <v>0.119</v>
       </c>
       <c r="J157" s="27" t="str">
         <v>PASS</v>
@@ -7217,7 +7217,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I158" s="25">
-        <v>0.084</v>
+        <v>0.09</v>
       </c>
       <c r="J158" s="27" t="str">
         <v>PASS</v>
@@ -7252,7 +7252,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I159" s="24">
-        <v>0.224</v>
+        <v>0.039</v>
       </c>
       <c r="J159" s="27" t="str">
         <v>PASS</v>
@@ -7287,7 +7287,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I160" s="25">
-        <v>0.006</v>
+        <v>0.027</v>
       </c>
       <c r="J160" s="27" t="str">
         <v>PASS</v>
@@ -7322,7 +7322,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I161" s="24">
-        <v>0.056</v>
+        <v>0.021</v>
       </c>
       <c r="J161" s="27" t="str">
         <v>PASS</v>
@@ -7357,7 +7357,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I162" s="25">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
       <c r="J162" s="27" t="str">
         <v>PASS</v>
@@ -7392,7 +7392,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I163" s="24">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="J163" s="27" t="str">
         <v>PASS</v>
@@ -7427,7 +7427,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I164" s="25">
-        <v>0.097</v>
+        <v>0.051</v>
       </c>
       <c r="J164" s="27" t="str">
         <v>PASS</v>
@@ -7497,7 +7497,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I166" s="25">
-        <v>0.064</v>
+        <v>0.026</v>
       </c>
       <c r="J166" s="27" t="str">
         <v>PASS</v>
@@ -7532,7 +7532,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I167" s="24">
-        <v>0.041</v>
+        <v>0.023</v>
       </c>
       <c r="J167" s="27" t="str">
         <v>PASS</v>
@@ -7567,7 +7567,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I168" s="25">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="J168" s="27" t="str">
         <v>PASS</v>
@@ -7602,7 +7602,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I169" s="24">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="J169" s="27" t="str">
         <v>PASS</v>
@@ -7637,7 +7637,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I170" s="25">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="J170" s="27" t="str">
         <v>PASS</v>
@@ -7672,7 +7672,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I171" s="24">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J171" s="27" t="str">
         <v>PASS</v>
@@ -7742,7 +7742,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I173" s="24">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J173" s="27" t="str">
         <v>PASS</v>
@@ -7777,7 +7777,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I174" s="25">
-        <v>0.021</v>
+        <v>0.066</v>
       </c>
       <c r="J174" s="27" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I175" s="24">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="J175" s="27" t="str">
         <v>PASS</v>
@@ -7847,7 +7847,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I176" s="25">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="J176" s="27" t="str">
         <v>PASS</v>
@@ -7882,7 +7882,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I177" s="24">
-        <v>0.006</v>
+        <v>0.024</v>
       </c>
       <c r="J177" s="27" t="str">
         <v>PASS</v>
@@ -7917,7 +7917,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I178" s="25">
-        <v>0.009</v>
+        <v>0.017</v>
       </c>
       <c r="J178" s="27" t="str">
         <v>PASS</v>
@@ -7952,7 +7952,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I179" s="24">
-        <v>0.072</v>
+        <v>0.02</v>
       </c>
       <c r="J179" s="27" t="str">
         <v>PASS</v>
@@ -7987,7 +7987,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I180" s="25">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="J180" s="27" t="str">
         <v>PASS</v>
@@ -8022,7 +8022,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I181" s="24">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="J181" s="27" t="str">
         <v>PASS</v>
@@ -8057,7 +8057,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I182" s="25">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="J182" s="27" t="str">
         <v>PASS</v>
@@ -8092,7 +8092,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I183" s="24">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="J183" s="27" t="str">
         <v>PASS</v>
@@ -8127,7 +8127,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I184" s="25">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="J184" s="27" t="str">
         <v>PASS</v>
@@ -8162,7 +8162,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I185" s="24">
-        <v>0.496</v>
+        <v>0.605</v>
       </c>
       <c r="J185" s="27" t="str">
         <v>PASS</v>
@@ -8197,7 +8197,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I186" s="25">
-        <v>0.866</v>
+        <v>0.96</v>
       </c>
       <c r="J186" s="27" t="str">
         <v>PASS</v>
@@ -8232,7 +8232,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I187" s="24">
-        <v>0.881</v>
+        <v>0.92</v>
       </c>
       <c r="J187" s="27" t="str">
         <v>PASS</v>
@@ -8267,7 +8267,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I188" s="25">
-        <v>0.506</v>
+        <v>0.53</v>
       </c>
       <c r="J188" s="27" t="str">
         <v>PASS</v>
@@ -8302,7 +8302,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I189" s="24">
-        <v>0.779</v>
+        <v>0.495</v>
       </c>
       <c r="J189" s="27" t="str">
         <v>PASS</v>
@@ -8337,7 +8337,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I190" s="25">
-        <v>0.636</v>
+        <v>0.746</v>
       </c>
       <c r="J190" s="27" t="str">
         <v>PASS</v>
@@ -8372,7 +8372,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I191" s="24">
-        <v>0.97</v>
+        <v>1.133</v>
       </c>
       <c r="J191" s="27" t="str">
         <v>PASS</v>
@@ -8407,7 +8407,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I192" s="25">
-        <v>0.925</v>
+        <v>1.364</v>
       </c>
       <c r="J192" s="27" t="str">
         <v>PASS</v>
@@ -8442,7 +8442,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I193" s="24">
-        <v>0.807</v>
+        <v>0.97</v>
       </c>
       <c r="J193" s="27" t="str">
         <v>PASS</v>
@@ -8477,7 +8477,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I194" s="25">
-        <v>0.004</v>
+        <v>0.078</v>
       </c>
       <c r="J194" s="27" t="str">
         <v>PASS</v>
@@ -8512,7 +8512,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I195" s="24">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J195" s="27" t="str">
         <v>PASS</v>
@@ -8547,7 +8547,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I196" s="25">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="J196" s="27" t="str">
         <v>PASS</v>
@@ -8582,7 +8582,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I197" s="24">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J197" s="27" t="str">
         <v>PASS</v>
@@ -8617,7 +8617,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I198" s="25">
-        <v>1.177</v>
+        <v>1.114</v>
       </c>
       <c r="J198" s="27" t="str">
         <v>PASS</v>
@@ -8652,7 +8652,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I199" s="24">
-        <v>1.476</v>
+        <v>1.169</v>
       </c>
       <c r="J199" s="27" t="str">
         <v>PASS</v>
@@ -8687,7 +8687,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I200" s="25">
-        <v>1.54</v>
+        <v>1.711</v>
       </c>
       <c r="J200" s="27" t="str">
         <v>PASS</v>
@@ -8722,7 +8722,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I201" s="24">
-        <v>1.275</v>
+        <v>1.524</v>
       </c>
       <c r="J201" s="27" t="str">
         <v>PASS</v>
@@ -8757,7 +8757,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I202" s="25">
-        <v>1.832</v>
+        <v>1.919</v>
       </c>
       <c r="J202" s="27" t="str">
         <v>PASS</v>
@@ -8792,7 +8792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I203" s="24">
-        <v>1.699</v>
+        <v>1.946</v>
       </c>
       <c r="J203" s="27" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I204" s="25">
-        <v>0.738</v>
+        <v>0.905</v>
       </c>
       <c r="J204" s="27" t="str">
         <v>PASS</v>
@@ -8862,7 +8862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I205" s="24">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="J205" s="27" t="str">
         <v>PASS</v>
@@ -8897,7 +8897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I206" s="25">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="J206" s="27" t="str">
         <v>PASS</v>
@@ -8932,7 +8932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I207" s="24">
-        <v>0.055</v>
+        <v>0.022</v>
       </c>
       <c r="J207" s="27" t="str">
         <v>PASS</v>
@@ -8967,7 +8967,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I208" s="25">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="J208" s="27" t="str">
         <v>PASS</v>
@@ -9002,7 +9002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I209" s="24">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="J209" s="27" t="str">
         <v>PASS</v>
@@ -9037,7 +9037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I210" s="25">
-        <v>0.028</v>
+        <v>0.022</v>
       </c>
       <c r="J210" s="27" t="str">
         <v>PASS</v>
@@ -9072,7 +9072,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I211" s="24">
-        <v>0.104</v>
+        <v>0.053</v>
       </c>
       <c r="J211" s="27" t="str">
         <v>PASS</v>
@@ -9107,7 +9107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I212" s="25">
-        <v>1.377</v>
+        <v>2</v>
       </c>
       <c r="J212" s="27" t="str">
         <v>PASS</v>
@@ -9142,7 +9142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I213" s="24">
-        <v>0.679</v>
+        <v>0.892</v>
       </c>
       <c r="J213" s="27" t="str">
         <v>PASS</v>
@@ -9177,7 +9177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I214" s="25">
-        <v>1.357</v>
+        <v>2.254</v>
       </c>
       <c r="J214" s="27" t="str">
         <v>PASS</v>
@@ -9212,7 +9212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I215" s="24">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="J215" s="27" t="str">
         <v>PASS</v>
@@ -9247,7 +9247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I216" s="25">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="J216" s="27" t="str">
         <v>PASS</v>
@@ -9282,7 +9282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I217" s="24">
-        <v>0.003</v>
+        <v>0.034</v>
       </c>
       <c r="J217" s="27" t="str">
         <v>PASS</v>
@@ -9317,7 +9317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I218" s="25">
-        <v>0.001</v>
+        <v>0.021</v>
       </c>
       <c r="J218" s="27" t="str">
         <v>PASS</v>
@@ -9352,7 +9352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I219" s="24">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="J219" s="27" t="str">
         <v>PASS</v>
@@ -9387,7 +9387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I220" s="25">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="J220" s="27" t="str">
         <v>PASS</v>
@@ -9422,7 +9422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I221" s="24">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="J221" s="27" t="str">
         <v>PASS</v>
@@ -9457,7 +9457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I222" s="25">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="J222" s="27" t="str">
         <v>PASS</v>
@@ -9492,7 +9492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I223" s="24">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="J223" s="27" t="str">
         <v>PASS</v>
@@ -9527,7 +9527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I224" s="25">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="J224" s="27" t="str">
         <v>PASS</v>
@@ -9562,7 +9562,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I225" s="24">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="J225" s="27" t="str">
         <v>PASS</v>
@@ -9597,7 +9597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I226" s="25">
-        <v>0.074</v>
+        <v>0.053</v>
       </c>
       <c r="J226" s="27" t="str">
         <v>PASS</v>
@@ -9632,7 +9632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I227" s="24">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
       <c r="J227" s="27" t="str">
         <v>PASS</v>
@@ -9667,7 +9667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I228" s="25">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="J228" s="27" t="str">
         <v>PASS</v>
@@ -9702,7 +9702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I229" s="24">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="J229" s="27" t="str">
         <v>PASS</v>
@@ -9737,7 +9737,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I230" s="25">
-        <v>0.008</v>
+        <v>0.064</v>
       </c>
       <c r="J230" s="27" t="str">
         <v>PASS</v>
@@ -9772,7 +9772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I231" s="24">
-        <v>0.004</v>
+        <v>0.038</v>
       </c>
       <c r="J231" s="27" t="str">
         <v>PASS</v>
@@ -9807,7 +9807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I232" s="25">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="J232" s="27" t="str">
         <v>PASS</v>
@@ -9842,7 +9842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I233" s="24">
-        <v>0.022</v>
+        <v>0.051</v>
       </c>
       <c r="J233" s="27" t="str">
         <v>PASS</v>
@@ -9877,7 +9877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I234" s="25">
-        <v>0.022</v>
+        <v>0.056</v>
       </c>
       <c r="J234" s="27" t="str">
         <v>PASS</v>
@@ -9912,7 +9912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I235" s="24">
-        <v>0.017</v>
+        <v>0.029</v>
       </c>
       <c r="J235" s="27" t="str">
         <v>PASS</v>
@@ -9947,7 +9947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I236" s="25">
-        <v>0.057</v>
+        <v>0.186</v>
       </c>
       <c r="J236" s="27" t="str">
         <v>PASS</v>
@@ -9982,7 +9982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I237" s="24">
-        <v>0.003</v>
+        <v>0.055</v>
       </c>
       <c r="J237" s="27" t="str">
         <v>PASS</v>
@@ -10017,7 +10017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I238" s="25">
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
       <c r="J238" s="27" t="str">
         <v>PASS</v>
@@ -10052,7 +10052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I239" s="24">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="J239" s="27" t="str">
         <v>PASS</v>
@@ -10087,7 +10087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I240" s="25">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="J240" s="27" t="str">
         <v>PASS</v>
@@ -10157,7 +10157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I242" s="25">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="J242" s="27" t="str">
         <v>PASS</v>
@@ -10192,7 +10192,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I243" s="24">
-        <v>0.002</v>
+        <v>0.024</v>
       </c>
       <c r="J243" s="27" t="str">
         <v>PASS</v>
@@ -10227,7 +10227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I244" s="25">
-        <v>0.006</v>
+        <v>0.038</v>
       </c>
       <c r="J244" s="27" t="str">
         <v>PASS</v>
@@ -10262,7 +10262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I245" s="24">
-        <v>0.003</v>
+        <v>0.016</v>
       </c>
       <c r="J245" s="27" t="str">
         <v>PASS</v>
@@ -10297,7 +10297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I246" s="25">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
       <c r="J246" s="27" t="str">
         <v>PASS</v>
@@ -10332,7 +10332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I247" s="24">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J247" s="27" t="str">
         <v>PASS</v>
@@ -10367,7 +10367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I248" s="25">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="J248" s="27" t="str">
         <v>PASS</v>
@@ -10402,7 +10402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I249" s="24">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="J249" s="27" t="str">
         <v>PASS</v>
@@ -10437,7 +10437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I250" s="25">
-        <v>0.009</v>
+        <v>0.02</v>
       </c>
       <c r="J250" s="27" t="str">
         <v>PASS</v>
@@ -10472,7 +10472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I251" s="24">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="J251" s="27" t="str">
         <v>PASS</v>
@@ -10507,7 +10507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I252" s="25">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="J252" s="27" t="str">
         <v>PASS</v>
@@ -10577,7 +10577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I254" s="25">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="J254" s="27" t="str">
         <v>PASS</v>
@@ -10612,7 +10612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I255" s="24">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="J255" s="27" t="str">
         <v>PASS</v>
@@ -10647,7 +10647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I256" s="25">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="J256" s="27" t="str">
         <v>PASS</v>
@@ -10682,7 +10682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I257" s="24">
-        <v>0.01</v>
+        <v>0.187</v>
       </c>
       <c r="J257" s="27" t="str">
         <v>PASS</v>
@@ -10717,7 +10717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I258" s="25">
-        <v>0.009</v>
+        <v>0.026</v>
       </c>
       <c r="J258" s="27" t="str">
         <v>PASS</v>
@@ -10752,7 +10752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I259" s="24">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J259" s="27" t="str">
         <v>PASS</v>
@@ -10787,7 +10787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I260" s="25">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J260" s="27" t="str">
         <v>PASS</v>
@@ -10822,7 +10822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I261" s="24">
-        <v>0.011</v>
+        <v>0.027</v>
       </c>
       <c r="J261" s="27" t="str">
         <v>PASS</v>
@@ -10857,7 +10857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I262" s="25">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="J262" s="27" t="str">
         <v>PASS</v>
@@ -10892,7 +10892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I263" s="24">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="J263" s="27" t="str">
         <v>PASS</v>
@@ -10927,7 +10927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I264" s="25">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="J264" s="27" t="str">
         <v>PASS</v>
@@ -10962,7 +10962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I265" s="24">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J265" s="27" t="str">
         <v>PASS</v>
@@ -10997,7 +10997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I266" s="25">
-        <v>0.002</v>
+        <v>0.033</v>
       </c>
       <c r="J266" s="27" t="str">
         <v>PASS</v>
@@ -11032,7 +11032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I267" s="24">
-        <v>0.183</v>
+        <v>0.018</v>
       </c>
       <c r="J267" s="27" t="str">
         <v>PASS</v>
@@ -11067,7 +11067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I268" s="25">
-        <v>0.024</v>
+        <v>0.041</v>
       </c>
       <c r="J268" s="27" t="str">
         <v>PASS</v>
@@ -11137,7 +11137,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I270" s="25">
-        <v>0.028</v>
+        <v>0.084</v>
       </c>
       <c r="J270" s="27" t="str">
         <v>PASS</v>
@@ -11172,7 +11172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I271" s="24">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="J271" s="27" t="str">
         <v>PASS</v>
@@ -11207,7 +11207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I272" s="25">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="J272" s="27" t="str">
         <v>PASS</v>
@@ -11242,7 +11242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I273" s="24">
-        <v>0.025</v>
+        <v>0.037</v>
       </c>
       <c r="J273" s="27" t="str">
         <v>PASS</v>
@@ -11277,7 +11277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I274" s="25">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="J274" s="27" t="str">
         <v>PASS</v>
@@ -11312,7 +11312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I275" s="24">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="J275" s="27" t="str">
         <v>PASS</v>
@@ -11347,7 +11347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I276" s="25">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="J276" s="27" t="str">
         <v>PASS</v>
@@ -11382,7 +11382,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I277" s="24">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="J277" s="27" t="str">
         <v>PASS</v>
@@ -11417,7 +11417,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I278" s="25">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J278" s="27" t="str">
         <v>PASS</v>
@@ -11452,7 +11452,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I279" s="24">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J279" s="27" t="str">
         <v>PASS</v>
@@ -11522,7 +11522,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I281" s="24">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="J281" s="27" t="str">
         <v>PASS</v>
@@ -11557,7 +11557,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I282" s="25">
-        <v>0.028</v>
+        <v>0.072</v>
       </c>
       <c r="J282" s="27" t="str">
         <v>PASS</v>
@@ -11592,7 +11592,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I283" s="24">
-        <v>0.006</v>
+        <v>0.025</v>
       </c>
       <c r="J283" s="27" t="str">
         <v>PASS</v>
@@ -11627,7 +11627,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I284" s="25">
-        <v>0.015</v>
+        <v>0.033</v>
       </c>
       <c r="J284" s="27" t="str">
         <v>PASS</v>
@@ -11662,7 +11662,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I285" s="24">
-        <v>0.011</v>
+        <v>0.03</v>
       </c>
       <c r="J285" s="27" t="str">
         <v>PASS</v>
@@ -11697,7 +11697,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I286" s="25">
-        <v>0.012</v>
+        <v>0.098</v>
       </c>
       <c r="J286" s="27" t="str">
         <v>PASS</v>
@@ -11732,7 +11732,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I287" s="24">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="J287" s="27" t="str">
         <v>PASS</v>
@@ -11767,7 +11767,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I288" s="25">
-        <v>0.648</v>
+        <v>0.664</v>
       </c>
       <c r="J288" s="27" t="str">
         <v>PASS</v>
@@ -11802,7 +11802,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I289" s="24">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="J289" s="27" t="str">
         <v>PASS</v>
@@ -11837,7 +11837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I290" s="25">
-        <v>0.085</v>
+        <v>0.118</v>
       </c>
       <c r="J290" s="27" t="str">
         <v>PASS</v>
@@ -11872,7 +11872,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I291" s="24">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="J291" s="27" t="str">
         <v>PASS</v>
@@ -11907,7 +11907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I292" s="25">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="J292" s="27" t="str">
         <v>PASS</v>
@@ -11942,7 +11942,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I293" s="24">
-        <v>0.016</v>
+        <v>0.025</v>
       </c>
       <c r="J293" s="27" t="str">
         <v>PASS</v>
@@ -11977,7 +11977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I294" s="25">
-        <v>0.007</v>
+        <v>0.048</v>
       </c>
       <c r="J294" s="27" t="str">
         <v>PASS</v>
@@ -12012,7 +12012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I295" s="24">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="J295" s="27" t="str">
         <v>PASS</v>
@@ -12047,7 +12047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I296" s="25">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
       <c r="J296" s="27" t="str">
         <v>PASS</v>
@@ -12082,7 +12082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I297" s="24">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="J297" s="27" t="str">
         <v>PASS</v>
@@ -12117,7 +12117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I298" s="25">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="J298" s="27" t="str">
         <v>PASS</v>
@@ -12152,7 +12152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I299" s="24">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="J299" s="27" t="str">
         <v>PASS</v>
@@ -12187,7 +12187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I300" s="25">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
       <c r="J300" s="27" t="str">
         <v>PASS</v>
@@ -12222,7 +12222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I301" s="24">
-        <v>0.007</v>
+        <v>0.022</v>
       </c>
       <c r="J301" s="27" t="str">
         <v>PASS</v>
@@ -12257,7 +12257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I302" s="25">
-        <v>0.009</v>
+        <v>0.023</v>
       </c>
       <c r="J302" s="27" t="str">
         <v>PASS</v>
@@ -12292,7 +12292,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I303" s="24">
-        <v>0.014</v>
+        <v>0.033</v>
       </c>
       <c r="J303" s="27" t="str">
         <v>PASS</v>
@@ -12327,7 +12327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I304" s="25">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="J304" s="27" t="str">
         <v>PASS</v>
@@ -12362,7 +12362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I305" s="24">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="J305" s="27" t="str">
         <v>PASS</v>
@@ -12397,7 +12397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I306" s="25">
-        <v>0.023</v>
+        <v>0.041</v>
       </c>
       <c r="J306" s="27" t="str">
         <v>PASS</v>
@@ -12432,7 +12432,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I307" s="24">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="J307" s="27" t="str">
         <v>PASS</v>
@@ -12467,7 +12467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I308" s="25">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="J308" s="27" t="str">
         <v>PASS</v>
@@ -12502,7 +12502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I309" s="24">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="J309" s="27" t="str">
         <v>PASS</v>
@@ -12537,7 +12537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I310" s="25">
-        <v>0.047</v>
+        <v>0.016</v>
       </c>
       <c r="J310" s="27" t="str">
         <v>PASS</v>
@@ -12572,7 +12572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I311" s="24">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="J311" s="27" t="str">
         <v>PASS</v>
@@ -12607,7 +12607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I312" s="25">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="J312" s="27" t="str">
         <v>PASS</v>
@@ -12642,7 +12642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I313" s="24">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="J313" s="27" t="str">
         <v>PASS</v>
@@ -12677,7 +12677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I314" s="25">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="J314" s="27" t="str">
         <v>PASS</v>
@@ -12712,7 +12712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I315" s="24">
-        <v>0.009</v>
+        <v>0.02</v>
       </c>
       <c r="J315" s="27" t="str">
         <v>PASS</v>
@@ -12747,7 +12747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I316" s="25">
-        <v>0.007</v>
+        <v>0.036</v>
       </c>
       <c r="J316" s="27" t="str">
         <v>PASS</v>
@@ -12782,7 +12782,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I317" s="24">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="J317" s="27" t="str">
         <v>PASS</v>
@@ -12817,7 +12817,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I318" s="25">
-        <v>0.004</v>
+        <v>0.031</v>
       </c>
       <c r="J318" s="27" t="str">
         <v>PASS</v>
@@ -12852,7 +12852,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I319" s="24">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="J319" s="27" t="str">
         <v>PASS</v>
@@ -12887,7 +12887,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I320" s="25">
-        <v>0.004</v>
+        <v>0.024</v>
       </c>
       <c r="J320" s="27" t="str">
         <v>PASS</v>
@@ -12922,7 +12922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I321" s="24">
-        <v>0.019</v>
+        <v>0.047</v>
       </c>
       <c r="J321" s="27" t="str">
         <v>PASS</v>
@@ -12957,7 +12957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I322" s="25">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="J322" s="27" t="str">
         <v>PASS</v>
@@ -12992,7 +12992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I323" s="24">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="J323" s="27" t="str">
         <v>PASS</v>
@@ -13027,7 +13027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I324" s="25">
-        <v>0.029</v>
+        <v>0.023</v>
       </c>
       <c r="J324" s="27" t="str">
         <v>PASS</v>
@@ -13062,7 +13062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I325" s="24">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="J325" s="27" t="str">
         <v>PASS</v>
@@ -13097,7 +13097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I326" s="25">
-        <v>0.049</v>
+        <v>0.012</v>
       </c>
       <c r="J326" s="27" t="str">
         <v>PASS</v>
@@ -13132,7 +13132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I327" s="24">
-        <v>0.009</v>
+        <v>0.03</v>
       </c>
       <c r="J327" s="27" t="str">
         <v>PASS</v>
@@ -13167,7 +13167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I328" s="25">
-        <v>0.006</v>
+        <v>0.021</v>
       </c>
       <c r="J328" s="27" t="str">
         <v>PASS</v>
@@ -13202,7 +13202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I329" s="24">
-        <v>0.003</v>
+        <v>0.057</v>
       </c>
       <c r="J329" s="27" t="str">
         <v>PASS</v>
@@ -13237,7 +13237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I330" s="25">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="J330" s="27" t="str">
         <v>PASS</v>
@@ -13272,7 +13272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I331" s="24">
-        <v>0.003</v>
+        <v>0.016</v>
       </c>
       <c r="J331" s="27" t="str">
         <v>PASS</v>
@@ -21156,7 +21156,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B6" s="24" t="str">
-        <v>8074ec16a6cee36e3dc10a7468a963e88b0b0f9f</v>
+        <v>a9ce338dbdf85acc3bff13761404a7384b4ca9c2</v>
       </c>
     </row>
     <row r="7">
@@ -21164,7 +21164,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>40365246107</v>
+        <v>40366447604</v>
       </c>
     </row>
     <row r="8">
@@ -21172,7 +21172,7 @@
         <v>Workflow run URL</v>
       </c>
       <c r="B8" s="24" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40365246107</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40366447604</v>
       </c>
     </row>
     <row r="9">
@@ -21228,7 +21228,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B15" s="25" t="str">
-        <v>2026-10-26T17:05:19.869Z</v>
+        <v>2026-10-26T17:13:18.915Z</v>
       </c>
     </row>
     <row r="16">
@@ -21236,7 +21236,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <v>2026-10-26T17:06:00.782Z</v>
+        <v>2026-10-26T17:14:26.459Z</v>
       </c>
     </row>
     <row r="17">
@@ -21244,7 +21244,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B17" s="25">
-        <v>40.91</v>
+        <v>67.54</v>
       </c>
     </row>
     <row r="18">

--- a/reports/selenium-e2e-report.xlsx
+++ b/reports/selenium-e2e-report.xlsx
@@ -1266,7 +1266,7 @@
         <v>Test Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:14:26</v>
+        <v>26/10/2026, 17:35:39</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Status:</v>
@@ -1613,7 +1613,7 @@
         <v>Suite duration (s)</v>
       </c>
       <c r="B25" s="5">
-        <v>67.5</v>
+        <v>44.6</v>
       </c>
       <c r="D25" s="25" t="str">
         <v>Responsive viewports</v>
@@ -1664,7 +1664,7 @@
         <v>Workflow run</v>
       </c>
       <c r="B28" s="5" t="str">
-        <v>40366447604</v>
+        <v>40369854303</v>
       </c>
     </row>
     <row r="29">
@@ -1672,7 +1672,7 @@
         <v>Commit</v>
       </c>
       <c r="B29" s="5" t="str">
-        <v>a9ce338</v>
+        <v>0cee3c6</v>
       </c>
     </row>
     <row r="30">
@@ -1792,7 +1792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I3" s="24">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="J3" s="27" t="str">
         <v>PASS</v>
@@ -1827,7 +1827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I4" s="25">
-        <v>0.013</v>
+        <v>0.021</v>
       </c>
       <c r="J4" s="27" t="str">
         <v>PASS</v>
@@ -1862,7 +1862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I5" s="24">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="J5" s="27" t="str">
         <v>PASS</v>
@@ -1897,7 +1897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I6" s="25">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="J6" s="27" t="str">
         <v>PASS</v>
@@ -1932,7 +1932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I7" s="24">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="J7" s="27" t="str">
         <v>PASS</v>
@@ -1967,7 +1967,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I8" s="25">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="J8" s="27" t="str">
         <v>PASS</v>
@@ -2002,7 +2002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I9" s="24">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="J9" s="27" t="str">
         <v>PASS</v>
@@ -2037,7 +2037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I10" s="25">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="J10" s="27" t="str">
         <v>PASS</v>
@@ -2072,7 +2072,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I11" s="24">
-        <v>0.009</v>
+        <v>0.015</v>
       </c>
       <c r="J11" s="27" t="str">
         <v>PASS</v>
@@ -2107,7 +2107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I12" s="25">
-        <v>0.007</v>
+        <v>0.048</v>
       </c>
       <c r="J12" s="27" t="str">
         <v>PASS</v>
@@ -2142,7 +2142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I13" s="24">
-        <v>0.066</v>
+        <v>0.076</v>
       </c>
       <c r="J13" s="27" t="str">
         <v>PASS</v>
@@ -2177,7 +2177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I14" s="25">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="J14" s="27" t="str">
         <v>PASS</v>
@@ -2212,7 +2212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I15" s="24">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="J15" s="27" t="str">
         <v>PASS</v>
@@ -2247,7 +2247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I16" s="25">
-        <v>0.008</v>
+        <v>0.033</v>
       </c>
       <c r="J16" s="27" t="str">
         <v>PASS</v>
@@ -2282,7 +2282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I17" s="24">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="J17" s="27" t="str">
         <v>PASS</v>
@@ -2317,7 +2317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I18" s="25">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="J18" s="27" t="str">
         <v>PASS</v>
@@ -2352,7 +2352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I19" s="24">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="J19" s="27" t="str">
         <v>PASS</v>
@@ -2387,7 +2387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I20" s="25">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J20" s="27" t="str">
         <v>PASS</v>
@@ -2422,7 +2422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I21" s="24">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J21" s="27" t="str">
         <v>PASS</v>
@@ -2457,7 +2457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I22" s="25">
-        <v>0.006</v>
+        <v>0.032</v>
       </c>
       <c r="J22" s="27" t="str">
         <v>PASS</v>
@@ -2492,7 +2492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I23" s="24">
-        <v>0.014</v>
+        <v>0.056</v>
       </c>
       <c r="J23" s="27" t="str">
         <v>PASS</v>
@@ -2527,7 +2527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I24" s="25">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="J24" s="27" t="str">
         <v>PASS</v>
@@ -2562,7 +2562,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I25" s="24">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J25" s="27" t="str">
         <v>PASS</v>
@@ -2597,7 +2597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I26" s="25">
-        <v>0.004</v>
+        <v>0.042</v>
       </c>
       <c r="J26" s="27" t="str">
         <v>PASS</v>
@@ -2632,7 +2632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I27" s="24">
-        <v>0.005</v>
+        <v>0.048</v>
       </c>
       <c r="J27" s="27" t="str">
         <v>PASS</v>
@@ -2667,7 +2667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I28" s="25">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="J28" s="27" t="str">
         <v>PASS</v>
@@ -2702,7 +2702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I29" s="24">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="J29" s="27" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I30" s="25">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="J30" s="27" t="str">
         <v>PASS</v>
@@ -2772,7 +2772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I31" s="24">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="J31" s="27" t="str">
         <v>PASS</v>
@@ -2807,7 +2807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I32" s="25">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J32" s="27" t="str">
         <v>PASS</v>
@@ -2842,7 +2842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I33" s="24">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="J33" s="27" t="str">
         <v>PASS</v>
@@ -2877,7 +2877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I34" s="25">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="J34" s="27" t="str">
         <v>PASS</v>
@@ -2912,7 +2912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I35" s="24">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="J35" s="27" t="str">
         <v>PASS</v>
@@ -2947,7 +2947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I36" s="25">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="J36" s="27" t="str">
         <v>PASS</v>
@@ -2982,7 +2982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I37" s="24">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="J37" s="27" t="str">
         <v>PASS</v>
@@ -3017,7 +3017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I38" s="25">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="J38" s="27" t="str">
         <v>PASS</v>
@@ -3052,7 +3052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I39" s="24">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="J39" s="27" t="str">
         <v>PASS</v>
@@ -3087,7 +3087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I40" s="25">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="J40" s="27" t="str">
         <v>PASS</v>
@@ -3122,7 +3122,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I41" s="24">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="J41" s="27" t="str">
         <v>PASS</v>
@@ -3157,7 +3157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I42" s="25">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J42" s="27" t="str">
         <v>PASS</v>
@@ -3227,7 +3227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I44" s="25">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="J44" s="27" t="str">
         <v>PASS</v>
@@ -3262,7 +3262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I45" s="24">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="J45" s="27" t="str">
         <v>PASS</v>
@@ -3297,7 +3297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I46" s="25">
-        <v>0.017</v>
+        <v>0.033</v>
       </c>
       <c r="J46" s="27" t="str">
         <v>PASS</v>
@@ -3332,7 +3332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I47" s="24">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="J47" s="27" t="str">
         <v>PASS</v>
@@ -3367,7 +3367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I48" s="25">
-        <v>0.009</v>
+        <v>0.03</v>
       </c>
       <c r="J48" s="27" t="str">
         <v>PASS</v>
@@ -3402,7 +3402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I49" s="24">
-        <v>0.043</v>
+        <v>0.021</v>
       </c>
       <c r="J49" s="27" t="str">
         <v>PASS</v>
@@ -3437,7 +3437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I50" s="25">
-        <v>0.01</v>
+        <v>0.038</v>
       </c>
       <c r="J50" s="27" t="str">
         <v>PASS</v>
@@ -3472,7 +3472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I51" s="24">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="J51" s="27" t="str">
         <v>PASS</v>
@@ -3507,7 +3507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I52" s="25">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="J52" s="27" t="str">
         <v>PASS</v>
@@ -3542,7 +3542,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I53" s="24">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="J53" s="27" t="str">
         <v>PASS</v>
@@ -3577,7 +3577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I54" s="25">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="J54" s="27" t="str">
         <v>PASS</v>
@@ -3612,7 +3612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I55" s="24">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="J55" s="27" t="str">
         <v>PASS</v>
@@ -3647,7 +3647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I56" s="25">
-        <v>0.005</v>
+        <v>0.038</v>
       </c>
       <c r="J56" s="27" t="str">
         <v>PASS</v>
@@ -3682,7 +3682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I57" s="24">
-        <v>0.016</v>
+        <v>0.009</v>
       </c>
       <c r="J57" s="27" t="str">
         <v>PASS</v>
@@ -3717,7 +3717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I58" s="25">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="J58" s="27" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I59" s="24">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="J59" s="27" t="str">
         <v>PASS</v>
@@ -3787,7 +3787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I60" s="25">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J60" s="27" t="str">
         <v>PASS</v>
@@ -3822,7 +3822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I61" s="24">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="J61" s="27" t="str">
         <v>PASS</v>
@@ -3857,7 +3857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I62" s="25">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="J62" s="27" t="str">
         <v>PASS</v>
@@ -3892,7 +3892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I63" s="24">
-        <v>0.091</v>
+        <v>0.033</v>
       </c>
       <c r="J63" s="27" t="str">
         <v>PASS</v>
@@ -3927,7 +3927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I64" s="25">
-        <v>0.047</v>
+        <v>0.008</v>
       </c>
       <c r="J64" s="27" t="str">
         <v>PASS</v>
@@ -3962,7 +3962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I65" s="24">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
       <c r="J65" s="27" t="str">
         <v>PASS</v>
@@ -3997,7 +3997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I66" s="25">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="J66" s="27" t="str">
         <v>PASS</v>
@@ -4032,7 +4032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I67" s="24">
-        <v>0.056</v>
+        <v>0.017</v>
       </c>
       <c r="J67" s="27" t="str">
         <v>PASS</v>
@@ -4067,7 +4067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I68" s="25">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="J68" s="27" t="str">
         <v>PASS</v>
@@ -4102,7 +4102,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I69" s="24">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="J69" s="27" t="str">
         <v>PASS</v>
@@ -4137,7 +4137,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I70" s="25">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J70" s="27" t="str">
         <v>PASS</v>
@@ -4172,7 +4172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I71" s="24">
-        <v>0.009</v>
+        <v>0.019</v>
       </c>
       <c r="J71" s="27" t="str">
         <v>PASS</v>
@@ -4207,7 +4207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I72" s="25">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="J72" s="27" t="str">
         <v>PASS</v>
@@ -4242,7 +4242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I73" s="24">
-        <v>0.092</v>
+        <v>0.047</v>
       </c>
       <c r="J73" s="27" t="str">
         <v>PASS</v>
@@ -4277,7 +4277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I74" s="25">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="J74" s="27" t="str">
         <v>PASS</v>
@@ -4312,7 +4312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I75" s="24">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="J75" s="27" t="str">
         <v>PASS</v>
@@ -4347,7 +4347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I76" s="25">
-        <v>0.025</v>
+        <v>0.009</v>
       </c>
       <c r="J76" s="27" t="str">
         <v>PASS</v>
@@ -4382,7 +4382,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I77" s="24">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="J77" s="27" t="str">
         <v>PASS</v>
@@ -4417,7 +4417,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I78" s="25">
-        <v>0.057</v>
+        <v>0.007</v>
       </c>
       <c r="J78" s="27" t="str">
         <v>PASS</v>
@@ -4452,7 +4452,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I79" s="24">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="J79" s="27" t="str">
         <v>PASS</v>
@@ -4487,7 +4487,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I80" s="25">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="J80" s="27" t="str">
         <v>PASS</v>
@@ -4522,7 +4522,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I81" s="24">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="J81" s="27" t="str">
         <v>PASS</v>
@@ -4557,7 +4557,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I82" s="25">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="J82" s="27" t="str">
         <v>PASS</v>
@@ -4592,7 +4592,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I83" s="24">
-        <v>0.012</v>
+        <v>0.096</v>
       </c>
       <c r="J83" s="27" t="str">
         <v>PASS</v>
@@ -4627,7 +4627,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I84" s="25">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="J84" s="27" t="str">
         <v>PASS</v>
@@ -4662,7 +4662,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I85" s="24">
-        <v>0.004</v>
+        <v>0.032</v>
       </c>
       <c r="J85" s="27" t="str">
         <v>PASS</v>
@@ -4697,7 +4697,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I86" s="25">
-        <v>0.004</v>
+        <v>0.041</v>
       </c>
       <c r="J86" s="27" t="str">
         <v>PASS</v>
@@ -4732,7 +4732,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I87" s="24">
-        <v>0.004</v>
+        <v>0.032</v>
       </c>
       <c r="J87" s="27" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I88" s="25">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="J88" s="27" t="str">
         <v>PASS</v>
@@ -4802,7 +4802,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I89" s="24">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J89" s="27" t="str">
         <v>PASS</v>
@@ -4837,7 +4837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I90" s="25">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="J90" s="27" t="str">
         <v>PASS</v>
@@ -4872,7 +4872,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I91" s="24">
-        <v>0.006</v>
+        <v>0.031</v>
       </c>
       <c r="J91" s="27" t="str">
         <v>PASS</v>
@@ -4907,7 +4907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I92" s="25">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="J92" s="27" t="str">
         <v>PASS</v>
@@ -4942,7 +4942,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I93" s="24">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="J93" s="27" t="str">
         <v>PASS</v>
@@ -4977,7 +4977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I94" s="25">
-        <v>0.117</v>
+        <v>0.024</v>
       </c>
       <c r="J94" s="27" t="str">
         <v>PASS</v>
@@ -5012,7 +5012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I95" s="24">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="J95" s="27" t="str">
         <v>PASS</v>
@@ -5047,7 +5047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I96" s="25">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="J96" s="27" t="str">
         <v>PASS</v>
@@ -5082,7 +5082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I97" s="24">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="J97" s="27" t="str">
         <v>PASS</v>
@@ -5117,7 +5117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I98" s="25">
-        <v>0.019</v>
+        <v>0.009</v>
       </c>
       <c r="J98" s="27" t="str">
         <v>PASS</v>
@@ -5152,7 +5152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I99" s="24">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="J99" s="27" t="str">
         <v>PASS</v>
@@ -5187,7 +5187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I100" s="25">
-        <v>0.023</v>
+        <v>0.005</v>
       </c>
       <c r="J100" s="27" t="str">
         <v>PASS</v>
@@ -5222,7 +5222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I101" s="24">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="J101" s="27" t="str">
         <v>PASS</v>
@@ -5257,7 +5257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I102" s="25">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="J102" s="27" t="str">
         <v>PASS</v>
@@ -5292,7 +5292,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I103" s="24">
-        <v>0.021</v>
+        <v>0.009</v>
       </c>
       <c r="J103" s="27" t="str">
         <v>PASS</v>
@@ -5327,7 +5327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I104" s="25">
-        <v>0.063</v>
+        <v>0.071</v>
       </c>
       <c r="J104" s="27" t="str">
         <v>PASS</v>
@@ -5362,7 +5362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I105" s="24">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="J105" s="27" t="str">
         <v>PASS</v>
@@ -5397,7 +5397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I106" s="25">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="J106" s="27" t="str">
         <v>PASS</v>
@@ -5432,7 +5432,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I107" s="24">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="J107" s="27" t="str">
         <v>PASS</v>
@@ -5467,7 +5467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I108" s="25">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="J108" s="27" t="str">
         <v>PASS</v>
@@ -5502,7 +5502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I109" s="24">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
       <c r="J109" s="27" t="str">
         <v>PASS</v>
@@ -5537,7 +5537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I110" s="25">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="J110" s="27" t="str">
         <v>PASS</v>
@@ -5572,7 +5572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I111" s="24">
-        <v>0.009</v>
+        <v>0.03</v>
       </c>
       <c r="J111" s="27" t="str">
         <v>PASS</v>
@@ -5607,7 +5607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I112" s="25">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J112" s="27" t="str">
         <v>PASS</v>
@@ -5642,7 +5642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I113" s="24">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="J113" s="27" t="str">
         <v>PASS</v>
@@ -5677,7 +5677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I114" s="25">
-        <v>0.16</v>
+        <v>0.116</v>
       </c>
       <c r="J114" s="27" t="str">
         <v>PASS</v>
@@ -5712,7 +5712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I115" s="24">
-        <v>0.044</v>
+        <v>0.013</v>
       </c>
       <c r="J115" s="27" t="str">
         <v>PASS</v>
@@ -5747,7 +5747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I116" s="25">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="J116" s="27" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I117" s="24">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="J117" s="27" t="str">
         <v>PASS</v>
@@ -5817,7 +5817,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I118" s="25">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J118" s="27" t="str">
         <v>PASS</v>
@@ -5852,7 +5852,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I119" s="24">
-        <v>0.023</v>
+        <v>0.009</v>
       </c>
       <c r="J119" s="27" t="str">
         <v>PASS</v>
@@ -5887,7 +5887,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I120" s="25">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="J120" s="27" t="str">
         <v>PASS</v>
@@ -5922,7 +5922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I121" s="24">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="J121" s="27" t="str">
         <v>PASS</v>
@@ -5957,7 +5957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I122" s="25">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="J122" s="27" t="str">
         <v>PASS</v>
@@ -5992,7 +5992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I123" s="24">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="J123" s="27" t="str">
         <v>PASS</v>
@@ -6027,7 +6027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I124" s="25">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="J124" s="27" t="str">
         <v>PASS</v>
@@ -6062,7 +6062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I125" s="24">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="J125" s="27" t="str">
         <v>PASS</v>
@@ -6097,7 +6097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I126" s="25">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="J126" s="27" t="str">
         <v>PASS</v>
@@ -6132,7 +6132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I127" s="24">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="J127" s="27" t="str">
         <v>PASS</v>
@@ -6167,7 +6167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I128" s="25">
-        <v>0.041</v>
+        <v>0.021</v>
       </c>
       <c r="J128" s="27" t="str">
         <v>PASS</v>
@@ -6202,7 +6202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I129" s="24">
-        <v>0.019</v>
+        <v>0.009</v>
       </c>
       <c r="J129" s="27" t="str">
         <v>PASS</v>
@@ -6237,7 +6237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I130" s="25">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="J130" s="27" t="str">
         <v>PASS</v>
@@ -6272,7 +6272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I131" s="24">
-        <v>0.01</v>
+        <v>0.051</v>
       </c>
       <c r="J131" s="27" t="str">
         <v>PASS</v>
@@ -6307,7 +6307,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I132" s="25">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="J132" s="27" t="str">
         <v>PASS</v>
@@ -6342,7 +6342,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I133" s="24">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="J133" s="27" t="str">
         <v>PASS</v>
@@ -6377,7 +6377,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I134" s="25">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="J134" s="27" t="str">
         <v>PASS</v>
@@ -6412,7 +6412,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I135" s="24">
-        <v>0.028</v>
+        <v>0.072</v>
       </c>
       <c r="J135" s="27" t="str">
         <v>PASS</v>
@@ -6447,7 +6447,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I136" s="25">
-        <v>0.044</v>
+        <v>0.024</v>
       </c>
       <c r="J136" s="27" t="str">
         <v>PASS</v>
@@ -6482,7 +6482,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I137" s="24">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="J137" s="27" t="str">
         <v>PASS</v>
@@ -6517,7 +6517,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I138" s="25">
-        <v>0.056</v>
+        <v>0.021</v>
       </c>
       <c r="J138" s="27" t="str">
         <v>PASS</v>
@@ -6552,7 +6552,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I139" s="24">
-        <v>0.101</v>
+        <v>0.044</v>
       </c>
       <c r="J139" s="27" t="str">
         <v>PASS</v>
@@ -6587,7 +6587,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I140" s="25">
-        <v>0.038</v>
+        <v>0.021</v>
       </c>
       <c r="J140" s="27" t="str">
         <v>PASS</v>
@@ -6622,7 +6622,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I141" s="24">
-        <v>0.067</v>
+        <v>0.026</v>
       </c>
       <c r="J141" s="27" t="str">
         <v>PASS</v>
@@ -6657,7 +6657,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I142" s="25">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="J142" s="27" t="str">
         <v>PASS</v>
@@ -6692,7 +6692,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I143" s="24">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="J143" s="27" t="str">
         <v>PASS</v>
@@ -6727,7 +6727,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I144" s="25">
-        <v>0.124</v>
+        <v>0.075</v>
       </c>
       <c r="J144" s="27" t="str">
         <v>PASS</v>
@@ -6762,7 +6762,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I145" s="24">
-        <v>0.035</v>
+        <v>0.101</v>
       </c>
       <c r="J145" s="27" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I146" s="25">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="J146" s="27" t="str">
         <v>PASS</v>
@@ -6832,7 +6832,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I147" s="24">
-        <v>0.076</v>
+        <v>0.039</v>
       </c>
       <c r="J147" s="27" t="str">
         <v>PASS</v>
@@ -6867,7 +6867,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I148" s="25">
-        <v>0.027</v>
+        <v>0.045</v>
       </c>
       <c r="J148" s="27" t="str">
         <v>PASS</v>
@@ -6902,7 +6902,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I149" s="24">
-        <v>0.128</v>
+        <v>0.076</v>
       </c>
       <c r="J149" s="27" t="str">
         <v>PASS</v>
@@ -6937,7 +6937,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I150" s="25">
-        <v>0.074</v>
+        <v>0.047</v>
       </c>
       <c r="J150" s="27" t="str">
         <v>PASS</v>
@@ -6972,7 +6972,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I151" s="24">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="J151" s="27" t="str">
         <v>PASS</v>
@@ -7007,7 +7007,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I152" s="25">
-        <v>0.034</v>
+        <v>0.105</v>
       </c>
       <c r="J152" s="27" t="str">
         <v>PASS</v>
@@ -7042,7 +7042,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I153" s="24">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="J153" s="27" t="str">
         <v>PASS</v>
@@ -7077,7 +7077,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I154" s="25">
-        <v>0.301</v>
+        <v>0.02</v>
       </c>
       <c r="J154" s="27" t="str">
         <v>PASS</v>
@@ -7112,7 +7112,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I155" s="24">
-        <v>0.253</v>
+        <v>0.032</v>
       </c>
       <c r="J155" s="27" t="str">
         <v>PASS</v>
@@ -7147,7 +7147,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I156" s="25">
-        <v>0.151</v>
+        <v>0.01</v>
       </c>
       <c r="J156" s="27" t="str">
         <v>PASS</v>
@@ -7182,7 +7182,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I157" s="24">
-        <v>0.119</v>
+        <v>0.024</v>
       </c>
       <c r="J157" s="27" t="str">
         <v>PASS</v>
@@ -7217,7 +7217,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I158" s="25">
-        <v>0.09</v>
+        <v>0.014</v>
       </c>
       <c r="J158" s="27" t="str">
         <v>PASS</v>
@@ -7252,7 +7252,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I159" s="24">
-        <v>0.039</v>
+        <v>0.05</v>
       </c>
       <c r="J159" s="27" t="str">
         <v>PASS</v>
@@ -7287,7 +7287,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I160" s="25">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="J160" s="27" t="str">
         <v>PASS</v>
@@ -7322,7 +7322,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I161" s="24">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="J161" s="27" t="str">
         <v>PASS</v>
@@ -7357,7 +7357,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I162" s="25">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="J162" s="27" t="str">
         <v>PASS</v>
@@ -7392,7 +7392,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I163" s="24">
-        <v>0.049</v>
+        <v>0.037</v>
       </c>
       <c r="J163" s="27" t="str">
         <v>PASS</v>
@@ -7427,7 +7427,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I164" s="25">
-        <v>0.051</v>
+        <v>0.028</v>
       </c>
       <c r="J164" s="27" t="str">
         <v>PASS</v>
@@ -7462,7 +7462,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I165" s="24">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="J165" s="27" t="str">
         <v>PASS</v>
@@ -7497,7 +7497,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I166" s="25">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="J166" s="27" t="str">
         <v>PASS</v>
@@ -7532,7 +7532,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I167" s="24">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="J167" s="27" t="str">
         <v>PASS</v>
@@ -7567,7 +7567,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I168" s="25">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="J168" s="27" t="str">
         <v>PASS</v>
@@ -7602,7 +7602,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I169" s="24">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="J169" s="27" t="str">
         <v>PASS</v>
@@ -7637,7 +7637,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I170" s="25">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="J170" s="27" t="str">
         <v>PASS</v>
@@ -7672,7 +7672,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I171" s="24">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="J171" s="27" t="str">
         <v>PASS</v>
@@ -7707,7 +7707,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I172" s="25">
-        <v>0.008</v>
+        <v>0.072</v>
       </c>
       <c r="J172" s="27" t="str">
         <v>PASS</v>
@@ -7742,7 +7742,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I173" s="24">
-        <v>0.005</v>
+        <v>0.026</v>
       </c>
       <c r="J173" s="27" t="str">
         <v>PASS</v>
@@ -7777,7 +7777,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I174" s="25">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
       <c r="J174" s="27" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I175" s="24">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="J175" s="27" t="str">
         <v>PASS</v>
@@ -7847,7 +7847,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I176" s="25">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="J176" s="27" t="str">
         <v>PASS</v>
@@ -7882,7 +7882,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I177" s="24">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="J177" s="27" t="str">
         <v>PASS</v>
@@ -7917,7 +7917,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I178" s="25">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="J178" s="27" t="str">
         <v>PASS</v>
@@ -7952,7 +7952,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I179" s="24">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="J179" s="27" t="str">
         <v>PASS</v>
@@ -7987,7 +7987,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I180" s="25">
-        <v>0.011</v>
+        <v>0.034</v>
       </c>
       <c r="J180" s="27" t="str">
         <v>PASS</v>
@@ -8022,7 +8022,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I181" s="24">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="J181" s="27" t="str">
         <v>PASS</v>
@@ -8057,7 +8057,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I182" s="25">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="J182" s="27" t="str">
         <v>PASS</v>
@@ -8092,7 +8092,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I183" s="24">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="J183" s="27" t="str">
         <v>PASS</v>
@@ -8127,7 +8127,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I184" s="25">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="J184" s="27" t="str">
         <v>PASS</v>
@@ -8162,7 +8162,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I185" s="24">
-        <v>0.605</v>
+        <v>0.515</v>
       </c>
       <c r="J185" s="27" t="str">
         <v>PASS</v>
@@ -8197,7 +8197,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I186" s="25">
-        <v>0.96</v>
+        <v>0.933</v>
       </c>
       <c r="J186" s="27" t="str">
         <v>PASS</v>
@@ -8232,7 +8232,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I187" s="24">
-        <v>0.92</v>
+        <v>0.942</v>
       </c>
       <c r="J187" s="27" t="str">
         <v>PASS</v>
@@ -8267,7 +8267,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I188" s="25">
-        <v>0.53</v>
+        <v>0.512</v>
       </c>
       <c r="J188" s="27" t="str">
         <v>PASS</v>
@@ -8302,7 +8302,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I189" s="24">
-        <v>0.495</v>
+        <v>0.862</v>
       </c>
       <c r="J189" s="27" t="str">
         <v>PASS</v>
@@ -8337,7 +8337,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I190" s="25">
-        <v>0.746</v>
+        <v>1.257</v>
       </c>
       <c r="J190" s="27" t="str">
         <v>PASS</v>
@@ -8372,7 +8372,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I191" s="24">
-        <v>1.133</v>
+        <v>0.982</v>
       </c>
       <c r="J191" s="27" t="str">
         <v>PASS</v>
@@ -8407,7 +8407,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I192" s="25">
-        <v>1.364</v>
+        <v>1.412</v>
       </c>
       <c r="J192" s="27" t="str">
         <v>PASS</v>
@@ -8442,7 +8442,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I193" s="24">
-        <v>0.97</v>
+        <v>1.554</v>
       </c>
       <c r="J193" s="27" t="str">
         <v>PASS</v>
@@ -8477,7 +8477,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I194" s="25">
-        <v>0.078</v>
+        <v>0.048</v>
       </c>
       <c r="J194" s="27" t="str">
         <v>PASS</v>
@@ -8512,7 +8512,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I195" s="24">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
       <c r="J195" s="27" t="str">
         <v>PASS</v>
@@ -8547,7 +8547,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I196" s="25">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="J196" s="27" t="str">
         <v>PASS</v>
@@ -8617,7 +8617,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I198" s="25">
-        <v>1.114</v>
+        <v>1.203</v>
       </c>
       <c r="J198" s="27" t="str">
         <v>PASS</v>
@@ -8652,7 +8652,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I199" s="24">
-        <v>1.169</v>
+        <v>1.343</v>
       </c>
       <c r="J199" s="27" t="str">
         <v>PASS</v>
@@ -8687,7 +8687,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I200" s="25">
-        <v>1.711</v>
+        <v>1.829</v>
       </c>
       <c r="J200" s="27" t="str">
         <v>PASS</v>
@@ -8722,7 +8722,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I201" s="24">
-        <v>1.524</v>
+        <v>1.476</v>
       </c>
       <c r="J201" s="27" t="str">
         <v>PASS</v>
@@ -8757,7 +8757,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I202" s="25">
-        <v>1.919</v>
+        <v>1.946</v>
       </c>
       <c r="J202" s="27" t="str">
         <v>PASS</v>
@@ -8792,7 +8792,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I203" s="24">
-        <v>1.946</v>
+        <v>1.863</v>
       </c>
       <c r="J203" s="27" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I204" s="25">
-        <v>0.905</v>
+        <v>0.803</v>
       </c>
       <c r="J204" s="27" t="str">
         <v>PASS</v>
@@ -8862,7 +8862,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I205" s="24">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="J205" s="27" t="str">
         <v>PASS</v>
@@ -8897,7 +8897,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I206" s="25">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="J206" s="27" t="str">
         <v>PASS</v>
@@ -8932,7 +8932,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I207" s="24">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="J207" s="27" t="str">
         <v>PASS</v>
@@ -8967,7 +8967,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I208" s="25">
-        <v>0.009</v>
+        <v>0.022</v>
       </c>
       <c r="J208" s="27" t="str">
         <v>PASS</v>
@@ -9002,7 +9002,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I209" s="24">
-        <v>0.014</v>
+        <v>0.035</v>
       </c>
       <c r="J209" s="27" t="str">
         <v>PASS</v>
@@ -9037,7 +9037,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I210" s="25">
-        <v>0.022</v>
+        <v>0.035</v>
       </c>
       <c r="J210" s="27" t="str">
         <v>PASS</v>
@@ -9072,7 +9072,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I211" s="24">
-        <v>0.053</v>
+        <v>0.11</v>
       </c>
       <c r="J211" s="27" t="str">
         <v>PASS</v>
@@ -9107,7 +9107,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I212" s="25">
-        <v>2</v>
+        <v>1.941</v>
       </c>
       <c r="J212" s="27" t="str">
         <v>PASS</v>
@@ -9142,7 +9142,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I213" s="24">
-        <v>0.892</v>
+        <v>1.019</v>
       </c>
       <c r="J213" s="27" t="str">
         <v>PASS</v>
@@ -9177,7 +9177,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I214" s="25">
-        <v>2.254</v>
+        <v>1.99</v>
       </c>
       <c r="J214" s="27" t="str">
         <v>PASS</v>
@@ -9212,7 +9212,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I215" s="24">
-        <v>0.009</v>
+        <v>0.046</v>
       </c>
       <c r="J215" s="27" t="str">
         <v>PASS</v>
@@ -9247,7 +9247,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I216" s="25">
-        <v>0.023</v>
+        <v>0.047</v>
       </c>
       <c r="J216" s="27" t="str">
         <v>PASS</v>
@@ -9282,7 +9282,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I217" s="24">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
       <c r="J217" s="27" t="str">
         <v>PASS</v>
@@ -9317,7 +9317,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I218" s="25">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="J218" s="27" t="str">
         <v>PASS</v>
@@ -9352,7 +9352,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I219" s="24">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J219" s="27" t="str">
         <v>PASS</v>
@@ -9387,7 +9387,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I220" s="25">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="J220" s="27" t="str">
         <v>PASS</v>
@@ -9422,7 +9422,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I221" s="24">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="J221" s="27" t="str">
         <v>PASS</v>
@@ -9457,7 +9457,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I222" s="25">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="J222" s="27" t="str">
         <v>PASS</v>
@@ -9492,7 +9492,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I223" s="24">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="J223" s="27" t="str">
         <v>PASS</v>
@@ -9527,7 +9527,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I224" s="25">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="J224" s="27" t="str">
         <v>PASS</v>
@@ -9562,7 +9562,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I225" s="24">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="J225" s="27" t="str">
         <v>PASS</v>
@@ -9597,7 +9597,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I226" s="25">
-        <v>0.053</v>
+        <v>0.08</v>
       </c>
       <c r="J226" s="27" t="str">
         <v>PASS</v>
@@ -9632,7 +9632,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I227" s="24">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="J227" s="27" t="str">
         <v>PASS</v>
@@ -9667,7 +9667,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I228" s="25">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="J228" s="27" t="str">
         <v>PASS</v>
@@ -9702,7 +9702,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I229" s="24">
-        <v>0.024</v>
+        <v>0.046</v>
       </c>
       <c r="J229" s="27" t="str">
         <v>PASS</v>
@@ -9737,7 +9737,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I230" s="25">
-        <v>0.064</v>
+        <v>0.024</v>
       </c>
       <c r="J230" s="27" t="str">
         <v>PASS</v>
@@ -9772,7 +9772,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I231" s="24">
-        <v>0.038</v>
+        <v>0.025</v>
       </c>
       <c r="J231" s="27" t="str">
         <v>PASS</v>
@@ -9807,7 +9807,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I232" s="25">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="J232" s="27" t="str">
         <v>PASS</v>
@@ -9842,7 +9842,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I233" s="24">
-        <v>0.051</v>
+        <v>0.02</v>
       </c>
       <c r="J233" s="27" t="str">
         <v>PASS</v>
@@ -9877,7 +9877,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I234" s="25">
-        <v>0.056</v>
+        <v>0.027</v>
       </c>
       <c r="J234" s="27" t="str">
         <v>PASS</v>
@@ -9912,7 +9912,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I235" s="24">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="J235" s="27" t="str">
         <v>PASS</v>
@@ -9947,7 +9947,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I236" s="25">
-        <v>0.186</v>
+        <v>0.125</v>
       </c>
       <c r="J236" s="27" t="str">
         <v>PASS</v>
@@ -9982,7 +9982,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I237" s="24">
-        <v>0.055</v>
+        <v>0.037</v>
       </c>
       <c r="J237" s="27" t="str">
         <v>PASS</v>
@@ -10017,7 +10017,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I238" s="25">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="J238" s="27" t="str">
         <v>PASS</v>
@@ -10052,7 +10052,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I239" s="24">
-        <v>0.022</v>
+        <v>0.038</v>
       </c>
       <c r="J239" s="27" t="str">
         <v>PASS</v>
@@ -10087,7 +10087,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I240" s="25">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="J240" s="27" t="str">
         <v>PASS</v>
@@ -10122,7 +10122,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I241" s="24">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J241" s="27" t="str">
         <v>PASS</v>
@@ -10157,7 +10157,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I242" s="25">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="J242" s="27" t="str">
         <v>PASS</v>
@@ -10192,7 +10192,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I243" s="24">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="J243" s="27" t="str">
         <v>PASS</v>
@@ -10227,7 +10227,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I244" s="25">
-        <v>0.038</v>
+        <v>0.015</v>
       </c>
       <c r="J244" s="27" t="str">
         <v>PASS</v>
@@ -10262,7 +10262,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I245" s="24">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="J245" s="27" t="str">
         <v>PASS</v>
@@ -10297,7 +10297,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I246" s="25">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="J246" s="27" t="str">
         <v>PASS</v>
@@ -10332,7 +10332,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I247" s="24">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="J247" s="27" t="str">
         <v>PASS</v>
@@ -10367,7 +10367,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I248" s="25">
-        <v>0.013</v>
+        <v>0.041</v>
       </c>
       <c r="J248" s="27" t="str">
         <v>PASS</v>
@@ -10402,7 +10402,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I249" s="24">
-        <v>0.017</v>
+        <v>0.033</v>
       </c>
       <c r="J249" s="27" t="str">
         <v>PASS</v>
@@ -10437,7 +10437,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I250" s="25">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J250" s="27" t="str">
         <v>PASS</v>
@@ -10472,7 +10472,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I251" s="24">
-        <v>0.015</v>
+        <v>0.029</v>
       </c>
       <c r="J251" s="27" t="str">
         <v>PASS</v>
@@ -10507,7 +10507,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I252" s="25">
-        <v>0.016</v>
+        <v>0.033</v>
       </c>
       <c r="J252" s="27" t="str">
         <v>PASS</v>
@@ -10542,7 +10542,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I253" s="24">
-        <v>0.01</v>
+        <v>0.032</v>
       </c>
       <c r="J253" s="27" t="str">
         <v>PASS</v>
@@ -10577,7 +10577,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I254" s="25">
-        <v>0.005</v>
+        <v>0.028</v>
       </c>
       <c r="J254" s="27" t="str">
         <v>PASS</v>
@@ -10612,7 +10612,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I255" s="24">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="J255" s="27" t="str">
         <v>PASS</v>
@@ -10647,7 +10647,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I256" s="25">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="J256" s="27" t="str">
         <v>PASS</v>
@@ -10682,7 +10682,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I257" s="24">
-        <v>0.187</v>
+        <v>0.088</v>
       </c>
       <c r="J257" s="27" t="str">
         <v>PASS</v>
@@ -10717,7 +10717,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I258" s="25">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="J258" s="27" t="str">
         <v>PASS</v>
@@ -10752,7 +10752,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I259" s="24">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="J259" s="27" t="str">
         <v>PASS</v>
@@ -10787,7 +10787,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I260" s="25">
-        <v>0.015</v>
+        <v>0.009</v>
       </c>
       <c r="J260" s="27" t="str">
         <v>PASS</v>
@@ -10822,7 +10822,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I261" s="24">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="J261" s="27" t="str">
         <v>PASS</v>
@@ -10857,7 +10857,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I262" s="25">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="J262" s="27" t="str">
         <v>PASS</v>
@@ -10892,7 +10892,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I263" s="24">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="J263" s="27" t="str">
         <v>PASS</v>
@@ -10927,7 +10927,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I264" s="25">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="J264" s="27" t="str">
         <v>PASS</v>
@@ -10962,7 +10962,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I265" s="24">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="J265" s="27" t="str">
         <v>PASS</v>
@@ -10997,7 +10997,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I266" s="25">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="J266" s="27" t="str">
         <v>PASS</v>
@@ -11032,7 +11032,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I267" s="24">
-        <v>0.018</v>
+        <v>0.214</v>
       </c>
       <c r="J267" s="27" t="str">
         <v>PASS</v>
@@ -11067,7 +11067,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I268" s="25">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="J268" s="27" t="str">
         <v>PASS</v>
@@ -11102,7 +11102,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I269" s="24">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="J269" s="27" t="str">
         <v>PASS</v>
@@ -11137,7 +11137,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I270" s="25">
-        <v>0.084</v>
+        <v>0.016</v>
       </c>
       <c r="J270" s="27" t="str">
         <v>PASS</v>
@@ -11172,7 +11172,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I271" s="24">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="J271" s="27" t="str">
         <v>PASS</v>
@@ -11207,7 +11207,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I272" s="25">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="J272" s="27" t="str">
         <v>PASS</v>
@@ -11242,7 +11242,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I273" s="24">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="J273" s="27" t="str">
         <v>PASS</v>
@@ -11277,7 +11277,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I274" s="25">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="J274" s="27" t="str">
         <v>PASS</v>
@@ -11312,7 +11312,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I275" s="24">
-        <v>0.028</v>
+        <v>0.062</v>
       </c>
       <c r="J275" s="27" t="str">
         <v>PASS</v>
@@ -11347,7 +11347,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I276" s="25">
-        <v>0.045</v>
+        <v>0.019</v>
       </c>
       <c r="J276" s="27" t="str">
         <v>PASS</v>
@@ -11382,7 +11382,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I277" s="24">
-        <v>0.004</v>
+        <v>0.026</v>
       </c>
       <c r="J277" s="27" t="str">
         <v>PASS</v>
@@ -11417,7 +11417,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I278" s="25">
-        <v>0.005</v>
+        <v>0.046</v>
       </c>
       <c r="J278" s="27" t="str">
         <v>PASS</v>
@@ -11452,7 +11452,7 @@
         <v>Tablet 768x1024</v>
       </c>
       <c r="I279" s="24">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="J279" s="27" t="str">
         <v>PASS</v>
@@ -11487,7 +11487,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I280" s="25">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="J280" s="27" t="str">
         <v>PASS</v>
@@ -11522,7 +11522,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I281" s="24">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="J281" s="27" t="str">
         <v>PASS</v>
@@ -11557,7 +11557,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I282" s="25">
-        <v>0.072</v>
+        <v>0.004</v>
       </c>
       <c r="J282" s="27" t="str">
         <v>PASS</v>
@@ -11592,7 +11592,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I283" s="24">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="J283" s="27" t="str">
         <v>PASS</v>
@@ -11627,7 +11627,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I284" s="25">
-        <v>0.033</v>
+        <v>0.005</v>
       </c>
       <c r="J284" s="27" t="str">
         <v>PASS</v>
@@ -11662,7 +11662,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I285" s="24">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="J285" s="27" t="str">
         <v>PASS</v>
@@ -11697,7 +11697,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I286" s="25">
-        <v>0.098</v>
+        <v>0.086</v>
       </c>
       <c r="J286" s="27" t="str">
         <v>PASS</v>
@@ -11732,7 +11732,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I287" s="24">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="J287" s="27" t="str">
         <v>PASS</v>
@@ -11767,7 +11767,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I288" s="25">
-        <v>0.664</v>
+        <v>0.657</v>
       </c>
       <c r="J288" s="27" t="str">
         <v>PASS</v>
@@ -11802,7 +11802,7 @@
         <v>Mobile 390x844</v>
       </c>
       <c r="I289" s="24">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="J289" s="27" t="str">
         <v>PASS</v>
@@ -11837,7 +11837,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I290" s="25">
-        <v>0.118</v>
+        <v>0.1</v>
       </c>
       <c r="J290" s="27" t="str">
         <v>PASS</v>
@@ -11872,7 +11872,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I291" s="24">
-        <v>0.011</v>
+        <v>0.046</v>
       </c>
       <c r="J291" s="27" t="str">
         <v>PASS</v>
@@ -11907,7 +11907,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I292" s="25">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="J292" s="27" t="str">
         <v>PASS</v>
@@ -11977,7 +11977,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I294" s="25">
-        <v>0.048</v>
+        <v>0.023</v>
       </c>
       <c r="J294" s="27" t="str">
         <v>PASS</v>
@@ -12012,7 +12012,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I295" s="24">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="J295" s="27" t="str">
         <v>PASS</v>
@@ -12047,7 +12047,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I296" s="25">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="J296" s="27" t="str">
         <v>PASS</v>
@@ -12082,7 +12082,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I297" s="24">
-        <v>0.009</v>
+        <v>0.021</v>
       </c>
       <c r="J297" s="27" t="str">
         <v>PASS</v>
@@ -12117,7 +12117,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I298" s="25">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="J298" s="27" t="str">
         <v>PASS</v>
@@ -12152,7 +12152,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I299" s="24">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="J299" s="27" t="str">
         <v>PASS</v>
@@ -12187,7 +12187,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I300" s="25">
-        <v>0.044</v>
+        <v>0.01</v>
       </c>
       <c r="J300" s="27" t="str">
         <v>PASS</v>
@@ -12222,7 +12222,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I301" s="24">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="J301" s="27" t="str">
         <v>PASS</v>
@@ -12257,7 +12257,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I302" s="25">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="J302" s="27" t="str">
         <v>PASS</v>
@@ -12292,7 +12292,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I303" s="24">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="J303" s="27" t="str">
         <v>PASS</v>
@@ -12327,7 +12327,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I304" s="25">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="J304" s="27" t="str">
         <v>PASS</v>
@@ -12362,7 +12362,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I305" s="24">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="J305" s="27" t="str">
         <v>PASS</v>
@@ -12397,7 +12397,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I306" s="25">
-        <v>0.041</v>
+        <v>0.01</v>
       </c>
       <c r="J306" s="27" t="str">
         <v>PASS</v>
@@ -12432,7 +12432,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I307" s="24">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="J307" s="27" t="str">
         <v>PASS</v>
@@ -12467,7 +12467,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I308" s="25">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="J308" s="27" t="str">
         <v>PASS</v>
@@ -12502,7 +12502,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I309" s="24">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="J309" s="27" t="str">
         <v>PASS</v>
@@ -12537,7 +12537,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I310" s="25">
-        <v>0.016</v>
+        <v>0.042</v>
       </c>
       <c r="J310" s="27" t="str">
         <v>PASS</v>
@@ -12572,7 +12572,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I311" s="24">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="J311" s="27" t="str">
         <v>PASS</v>
@@ -12607,7 +12607,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I312" s="25">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="J312" s="27" t="str">
         <v>PASS</v>
@@ -12642,7 +12642,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I313" s="24">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="J313" s="27" t="str">
         <v>PASS</v>
@@ -12677,7 +12677,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I314" s="25">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="J314" s="27" t="str">
         <v>PASS</v>
@@ -12712,7 +12712,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I315" s="24">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="J315" s="27" t="str">
         <v>PASS</v>
@@ -12747,7 +12747,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I316" s="25">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="J316" s="27" t="str">
         <v>PASS</v>
@@ -12817,7 +12817,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I318" s="25">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
       <c r="J318" s="27" t="str">
         <v>PASS</v>
@@ -12852,7 +12852,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I319" s="24">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="J319" s="27" t="str">
         <v>PASS</v>
@@ -12887,7 +12887,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I320" s="25">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="J320" s="27" t="str">
         <v>PASS</v>
@@ -12922,7 +12922,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I321" s="24">
-        <v>0.047</v>
+        <v>0.065</v>
       </c>
       <c r="J321" s="27" t="str">
         <v>PASS</v>
@@ -12957,7 +12957,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I322" s="25">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="J322" s="27" t="str">
         <v>PASS</v>
@@ -12992,7 +12992,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I323" s="24">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="J323" s="27" t="str">
         <v>PASS</v>
@@ -13027,7 +13027,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I324" s="25">
-        <v>0.023</v>
+        <v>0.035</v>
       </c>
       <c r="J324" s="27" t="str">
         <v>PASS</v>
@@ -13062,7 +13062,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I325" s="24">
-        <v>0.019</v>
+        <v>0.035</v>
       </c>
       <c r="J325" s="27" t="str">
         <v>PASS</v>
@@ -13097,7 +13097,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I326" s="25">
-        <v>0.012</v>
+        <v>0.039</v>
       </c>
       <c r="J326" s="27" t="str">
         <v>PASS</v>
@@ -13132,7 +13132,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I327" s="24">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="J327" s="27" t="str">
         <v>PASS</v>
@@ -13167,7 +13167,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I328" s="25">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="J328" s="27" t="str">
         <v>PASS</v>
@@ -13202,7 +13202,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I329" s="24">
-        <v>0.057</v>
+        <v>0.029</v>
       </c>
       <c r="J329" s="27" t="str">
         <v>PASS</v>
@@ -13237,7 +13237,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I330" s="25">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="J330" s="27" t="str">
         <v>PASS</v>
@@ -13272,7 +13272,7 @@
         <v>Desktop 1440x900</v>
       </c>
       <c r="I331" s="24">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="J331" s="27" t="str">
         <v>PASS</v>
@@ -21156,7 +21156,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B6" s="24" t="str">
-        <v>a9ce338dbdf85acc3bff13761404a7384b4ca9c2</v>
+        <v>0cee3c6ca348c3ff59a063340774eb0d9782a291</v>
       </c>
     </row>
     <row r="7">
@@ -21164,7 +21164,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>40366447604</v>
+        <v>40369854303</v>
       </c>
     </row>
     <row r="8">
@@ -21172,7 +21172,7 @@
         <v>Workflow run URL</v>
       </c>
       <c r="B8" s="24" t="str">
-        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40366447604</v>
+        <v>https://github.com/hareshbharadwaj/abet/actions/runs/40369854303</v>
       </c>
     </row>
     <row r="9">
@@ -21228,7 +21228,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B15" s="25" t="str">
-        <v>2026-10-26T17:13:18.915Z</v>
+        <v>2026-10-26T17:34:54.701Z</v>
       </c>
     </row>
     <row r="16">
@@ -21236,7 +21236,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <v>2026-10-26T17:14:26.459Z</v>
+        <v>2026-10-26T17:35:39.350Z</v>
       </c>
     </row>
     <row r="17">
@@ -21244,7 +21244,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B17" s="25">
-        <v>67.54</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="18">
